--- a/metadata/MIAFPE/MIAFPE_template_v1.1.xlsx
+++ b/metadata/MIAFPE/MIAFPE_template_v1.1.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="359">
   <si>
     <t xml:space="preserve">Sheet Name</t>
   </si>
@@ -64,6 +64,9 @@
     <t xml:space="preserve">Notes</t>
   </si>
   <si>
+    <t xml:space="preserve">MIAPPE v1.2</t>
+  </si>
+  <si>
     <t xml:space="preserve">Investigation</t>
   </si>
   <si>
@@ -76,42 +79,63 @@
     <t xml:space="preserve">http://purl.org/ppeo/ppeo.owl#</t>
   </si>
   <si>
+    <t xml:space="preserve">investigation</t>
+  </si>
+  <si>
     <t xml:space="preserve">Investigation Unique Identifier</t>
   </si>
   <si>
     <t xml:space="preserve">Identifier comprising the unique name of the institution/database hosting the submission of the investigation data, and the accession number of the investigation in that institution.</t>
   </si>
   <si>
+    <t xml:space="preserve">EBI:12345678</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unique Identifier</t>
   </si>
   <si>
     <t xml:space="preserve">hasIdentifier</t>
   </si>
   <si>
+    <t xml:space="preserve">investigationId</t>
+  </si>
+  <si>
     <t xml:space="preserve">Investigation Title</t>
   </si>
   <si>
     <t xml:space="preserve">Human-readable string summarizing the investigation.</t>
   </si>
   <si>
+    <t xml:space="preserve">Adaptation of Maize to Temperate Climates: Mid-Density Genome-Wide Association Genetics and Diversity Patterns Reveal Key Genomic Regions, with a Major Contribution of the Vgt2 (ZCN8) Locus.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Free Text</t>
   </si>
   <si>
     <t xml:space="preserve">hasName</t>
   </si>
   <si>
+    <t xml:space="preserve">investigationTitle</t>
+  </si>
+  <si>
     <t xml:space="preserve">Investigation Description</t>
   </si>
   <si>
     <t xml:space="preserve">Human-readable text describing the investigation in more detail.</t>
   </si>
   <si>
+    <t xml:space="preserve">The migration of maize from tropical to temperate climates was accompanied by a dramatic evolution in flowering time. To gain insight into the genetic architecture of this adaptive trait, we conducted a 50K SNP-based genome-wide association and diversity investigation on a panel of tropical and temperate American and European representatives.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Max(1)</t>
   </si>
   <si>
     <t xml:space="preserve">hasDescription</t>
   </si>
   <si>
+    <t xml:space="preserve">investigationDescription</t>
+  </si>
+  <si>
     <t xml:space="preserve">Submission Date</t>
   </si>
   <si>
@@ -124,6 +148,9 @@
     <t xml:space="preserve">hasSubmissionDate</t>
   </si>
   <si>
+    <t xml:space="preserve">submissionDate</t>
+  </si>
+  <si>
     <t xml:space="preserve">Public Release Date</t>
   </si>
   <si>
@@ -133,21 +160,33 @@
     <t xml:space="preserve">hasPublicReleaseDate</t>
   </si>
   <si>
+    <t xml:space="preserve">publicReleaseDate</t>
+  </si>
+  <si>
     <t xml:space="preserve">License</t>
   </si>
   <si>
     <t xml:space="preserve">License for the reuse of the data associated with this investigation. The Creative Commons licenses cover most use cases and are recommended.</t>
   </si>
   <si>
+    <t xml:space="preserve">CC BY-SA 4.0 </t>
+  </si>
+  <si>
     <t xml:space="preserve">hasLicense</t>
   </si>
   <si>
+    <t xml:space="preserve">license</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dataset Version</t>
   </si>
   <si>
     <t xml:space="preserve">The version of the Dataset.</t>
   </si>
   <si>
+    <t xml:space="preserve">V1.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">hasVersion</t>
   </si>
   <si>
@@ -157,7 +196,7 @@
     <t xml:space="preserve">The version of MIAFPE used. Different MIAFPE Versions are compatible with different MIAPPE Versions.</t>
   </si>
   <si>
-    <t xml:space="preserve">Beta 0.1</t>
+    <t xml:space="preserve">Beta v1.1</t>
   </si>
   <si>
     <t xml:space="preserve">hasMIAFPEVersion</t>
@@ -169,12 +208,18 @@
     <t xml:space="preserve">An identifier for a literature publication where the investigation is described. Use of DOIs is recommended (In case of more than 1 use semicolon-separated format).</t>
   </si>
   <si>
+    <t xml:space="preserve">doi:10.1371/journal.pone.0071377</t>
+  </si>
+  <si>
     <t xml:space="preserve">some</t>
   </si>
   <si>
     <t xml:space="preserve">hasAssociatedPublication</t>
   </si>
   <si>
+    <t xml:space="preserve">associatedPublication</t>
+  </si>
+  <si>
     <t xml:space="preserve">Investigation Level Files</t>
   </si>
   <si>
@@ -202,6 +247,9 @@
     <t xml:space="preserve">partOf (Domain Invstigation)</t>
   </si>
   <si>
+    <t xml:space="preserve">study</t>
+  </si>
+  <si>
     <t xml:space="preserve">Study Unique Identifier</t>
   </si>
   <si>
@@ -211,18 +259,27 @@
     <t xml:space="preserve">Identifier will have the feature to be autofilled</t>
   </si>
   <si>
+    <t xml:space="preserve">studyId</t>
+  </si>
+  <si>
     <t xml:space="preserve">Study Title</t>
   </si>
   <si>
     <t xml:space="preserve">Title of the Study.</t>
   </si>
   <si>
+    <t xml:space="preserve">studyTitle</t>
+  </si>
+  <si>
     <t xml:space="preserve">Study Description</t>
   </si>
   <si>
     <t xml:space="preserve">Human-readable text describing the study in more detail.</t>
   </si>
   <si>
+    <t xml:space="preserve">studyDescription</t>
+  </si>
+  <si>
     <t xml:space="preserve">Start Date</t>
   </si>
   <si>
@@ -772,15 +829,30 @@
     <t xml:space="preserve">ObservationUnit</t>
   </si>
   <si>
+    <t xml:space="preserve">Observation ID</t>
+  </si>
+  <si>
     <t xml:space="preserve">ID from Observation Table (optional to guarantee compatibility with MIAPPE)</t>
   </si>
   <si>
+    <t xml:space="preserve">Either Observation or Study needs to be given with Min(1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID from Study Table</t>
+  </si>
+  <si>
     <t xml:space="preserve">Observation Unit Description</t>
   </si>
   <si>
+    <t xml:space="preserve">General description of the observation units in the study.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Observation Unit external ID</t>
   </si>
   <si>
+    <t xml:space="preserve">Identifier for the observation unit in a persistent repository, comprises the name of the repository and the identifier of the observation unit therein. The EBI Biosamples repository can be used. URI are recommended when possible.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Spatial Distribution</t>
   </si>
   <si>
@@ -797,6 +869,12 @@
   </si>
   <si>
     <t xml:space="preserve">Observation Unit Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type of observation unit in textual form, usually one of the following: study, block, sub-block, plot, sub-plot, pot, plant. Use of other observation unit types is possible but not recommended. The observation unit type cannot be used to indicate sub-plant levels. However, observations can still be made on the sub-plant level, as long as the details are indicated in the associated observed variable (see observed variables). Alternatively, it is possible to use samples for more detailed tracing of sub-plant units, attaching the observations to them instead.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">plot</t>
   </si>
   <si>
     <t xml:space="preserve">Experimental Factor</t>
@@ -1034,11 +1112,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="General"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1080,6 +1159,11 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b val="true"/>
@@ -1233,7 +1317,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1274,11 +1358,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1294,6 +1378,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1302,7 +1390,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1310,7 +1398,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1330,11 +1418,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1346,7 +1434,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1362,7 +1450,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1370,11 +1458,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1398,15 +1486,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1599,16 +1687,18 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21.21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="29.46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="65.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="21.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="39.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="21.56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="26.08"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="25.97"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="43.47"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="30.37"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="21.91"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="12" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="23.1"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="13" style="1" width="11.53"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="30.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1642,25 +1732,28 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="47.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="4"/>
       <c r="F2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I2" s="5" t="str">
         <f aca="false">_xlfn.CONCAT(H2, LOWER(G2))</f>
@@ -1671,27 +1764,32 @@
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#Investigation</v>
       </c>
       <c r="K2" s="4"/>
-    </row>
-    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L2" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="36.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7"/>
       <c r="B3" s="8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="9"/>
+        <v>18</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>19</v>
+      </c>
       <c r="E3" s="9" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I3" s="9" t="str">
         <f aca="false">_xlfn.CONCAT(H3, G3)</f>
@@ -1702,27 +1800,32 @@
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasIdentifier</v>
       </c>
       <c r="K3" s="9"/>
-    </row>
-    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L3" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="59.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7"/>
-      <c r="B4" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="11"/>
+      <c r="B4" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>25</v>
+      </c>
       <c r="E4" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I4" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H4, G4)</f>
@@ -1733,27 +1836,32 @@
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasName</v>
       </c>
       <c r="K4" s="12"/>
-    </row>
-    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L4" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="105.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7"/>
-      <c r="B5" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="11"/>
+      <c r="B5" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>31</v>
+      </c>
       <c r="E5" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I5" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H5, G5)</f>
@@ -1764,26 +1872,32 @@
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasDescription</v>
       </c>
       <c r="K5" s="12"/>
-    </row>
-    <row r="6" customFormat="false" ht="46" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L5" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="47.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7"/>
-      <c r="B6" s="10" t="s">
-        <v>27</v>
+      <c r="B6" s="11" t="s">
+        <v>35</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>41260</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I6" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H6, G6)</f>
@@ -1794,27 +1908,32 @@
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasSubmissionDate</v>
       </c>
       <c r="K6" s="12"/>
-    </row>
-    <row r="7" customFormat="false" ht="46" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L6" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="47.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7"/>
-      <c r="B7" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" s="11" t="s">
+      <c r="B7" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>41330</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="11"/>
-      <c r="E7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="G7" s="1" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I7" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H7, G7)</f>
@@ -1825,26 +1944,32 @@
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasPublicReleaseDate</v>
       </c>
       <c r="K7" s="12"/>
-    </row>
-    <row r="8" customFormat="false" ht="34.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L7" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="36.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7"/>
-      <c r="B8" s="10" t="s">
-        <v>34</v>
+      <c r="B8" s="11" t="s">
+        <v>44</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>46</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I8" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H8, G8)</f>
@@ -1855,26 +1980,32 @@
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasLicense</v>
       </c>
       <c r="K8" s="12"/>
+      <c r="L8" s="1" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="34.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7"/>
       <c r="B9" s="14" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>38</v>
+        <v>50</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I9" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H9, G9)</f>
@@ -1889,22 +2020,22 @@
     <row r="10" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7"/>
       <c r="B10" s="14" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="J10" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G10)</f>
@@ -1912,25 +2043,28 @@
       </c>
       <c r="K10" s="12"/>
     </row>
-    <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="47.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7"/>
       <c r="B11" s="14" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>45</v>
+        <v>58</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>59</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I11" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H11, G11)</f>
@@ -1941,89 +2075,95 @@
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasAssociatedPublication</v>
       </c>
       <c r="K11" s="12"/>
+      <c r="L11" s="1" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7"/>
-      <c r="B12" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="F12" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="G12" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="H12" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="I12" s="16" t="str">
+      <c r="B12" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" s="17"/>
+      <c r="E12" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="H12" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="17" t="str">
         <f aca="false">_xlfn.CONCAT(H12, G12)</f>
         <v>http://purl.org/ppeo/ppeo.owl#hasDataFile</v>
       </c>
-      <c r="J12" s="19" t="str">
+      <c r="J12" s="20" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G12)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasDataFile</v>
       </c>
-      <c r="K12" s="19"/>
-    </row>
-    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="B13" s="21"/>
-      <c r="C13" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="D13" s="22"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="G13" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="H13" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" s="22" t="str">
+      <c r="K12" s="20"/>
+    </row>
+    <row r="13" customFormat="false" ht="36.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" s="22"/>
+      <c r="C13" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13" s="23"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="G13" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="H13" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" s="23" t="str">
         <f aca="false">_xlfn.CONCAT(H13, LOWER(G13))</f>
         <v>http://purl.org/ppeo/ppeo.owl#study</v>
       </c>
-      <c r="J13" s="21" t="str">
+      <c r="J13" s="22" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G13)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#Study</v>
       </c>
-      <c r="K13" s="22" t="s">
-        <v>56</v>
+      <c r="K13" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="L13" s="23" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="23"/>
+      <c r="A14" s="24"/>
       <c r="B14" s="8" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="D14" s="9"/>
       <c r="E14" s="9" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I14" s="9" t="str">
         <f aca="false">_xlfn.CONCAT(H14, G14)</f>
@@ -2034,28 +2174,31 @@
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasIdentifier</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>59</v>
+        <v>75</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="23"/>
-      <c r="B15" s="10" t="s">
-        <v>60</v>
+      <c r="A15" s="24"/>
+      <c r="B15" s="11" t="s">
+        <v>77</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I15" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H15, G15)</f>
@@ -2066,26 +2209,29 @@
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasName</v>
       </c>
       <c r="K15" s="12"/>
+      <c r="L15" s="1" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="23"/>
-      <c r="B16" s="10" t="s">
-        <v>62</v>
+      <c r="A16" s="24"/>
+      <c r="B16" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I16" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H16, G16)</f>
@@ -2096,26 +2242,29 @@
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasDescription</v>
       </c>
       <c r="K16" s="12"/>
+      <c r="L16" s="1" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="23"/>
-      <c r="B17" s="10" t="s">
-        <v>64</v>
+      <c r="A17" s="24"/>
+      <c r="B17" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I17" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H17, G17)</f>
@@ -2128,24 +2277,24 @@
       <c r="K17" s="12"/>
     </row>
     <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="23"/>
-      <c r="B18" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>68</v>
+      <c r="A18" s="24"/>
+      <c r="B18" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>87</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I18" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H18, G18)</f>
@@ -2158,24 +2307,24 @@
       <c r="K18" s="12"/>
     </row>
     <row r="19" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="23"/>
-      <c r="B19" s="10" t="s">
+      <c r="A19" s="24"/>
+      <c r="B19" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E19" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C19" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="E19" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="G19" s="1" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I19" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H19, G19)</f>
@@ -2188,24 +2337,24 @@
       <c r="K19" s="12"/>
     </row>
     <row r="20" customFormat="false" ht="34.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="23"/>
+      <c r="A20" s="24"/>
       <c r="B20" s="14" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="E20" s="24" t="s">
-        <v>74</v>
+        <v>94</v>
+      </c>
+      <c r="E20" s="25" t="s">
+        <v>93</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I20" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H20, G20)</f>
@@ -2218,24 +2367,24 @@
       <c r="K20" s="12"/>
     </row>
     <row r="21" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="23"/>
+      <c r="A21" s="24"/>
       <c r="B21" s="14" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E21" s="24" t="s">
-        <v>79</v>
+        <v>97</v>
+      </c>
+      <c r="E21" s="25" t="s">
+        <v>98</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I21" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H21, G21)</f>
@@ -2248,52 +2397,52 @@
       <c r="K21" s="12"/>
     </row>
     <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="23"/>
-      <c r="B22" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="C22" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="D22" s="16"/>
-      <c r="E22" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="F22" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="G22" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="H22" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="I22" s="16" t="str">
+      <c r="A22" s="24"/>
+      <c r="B22" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="D22" s="17"/>
+      <c r="E22" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="F22" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="G22" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="H22" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="I22" s="17" t="str">
         <f aca="false">_xlfn.CONCAT(H22, G22)</f>
         <v>http://purl.org/ppeo/ppeo.owl#hasDataFile</v>
       </c>
-      <c r="J22" s="19" t="str">
+      <c r="J22" s="20" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G22)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasDataFile</v>
       </c>
-      <c r="K22" s="19"/>
-    </row>
-    <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="25" t="s">
-        <v>74</v>
+      <c r="K22" s="20"/>
+    </row>
+    <row r="23" customFormat="false" ht="36.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="26" t="s">
+        <v>93</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="5" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I23" s="5" t="str">
         <f aca="false">_xlfn.CONCAT(H23, LOWER(G23))</f>
@@ -2304,27 +2453,28 @@
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#Location</v>
       </c>
       <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
     </row>
     <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7"/>
       <c r="B24" s="8" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="9" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I24" s="9" t="str">
         <f aca="false">_xlfn.CONCAT(H24, G24)</f>
@@ -2335,28 +2485,28 @@
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasIdentifier</v>
       </c>
       <c r="K24" s="9" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7"/>
-      <c r="B25" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>87</v>
+      <c r="B25" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>106</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I25" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H25, G25)</f>
@@ -2370,91 +2520,91 @@
     </row>
     <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7"/>
-      <c r="B26" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="C26" s="27" t="s">
-        <v>89</v>
-      </c>
-      <c r="D26" s="27"/>
-      <c r="E26" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="F26" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="G26" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="H26" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="I26" s="27" t="str">
+      <c r="B26" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="C26" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="D26" s="28"/>
+      <c r="E26" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="F26" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="G26" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="H26" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="I26" s="28" t="str">
         <f aca="false">_xlfn.CONCAT(H26, G26)</f>
         <v>http://purl.org/ppeo/ppeo.owl#hasName</v>
       </c>
-      <c r="J26" s="27" t="str">
+      <c r="J26" s="28" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G26)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasName</v>
       </c>
-      <c r="K26" s="29"/>
+      <c r="K26" s="30"/>
       <c r="L26" s="1" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7"/>
-      <c r="B27" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="C27" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="D27" s="27"/>
-      <c r="E27" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="G27" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="H27" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="I27" s="27" t="str">
+      <c r="B27" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="C27" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="F27" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="G27" s="28" t="s">
+        <v>113</v>
+      </c>
+      <c r="H27" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="I27" s="28" t="str">
         <f aca="false">_xlfn.CONCAT(H27, G27)</f>
         <v>http://purl.org/ppeo/ppeo.owl#hasCountryCode</v>
       </c>
-      <c r="J27" s="27" t="str">
+      <c r="J27" s="28" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G27)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasCountryCode</v>
       </c>
-      <c r="K27" s="29"/>
+      <c r="K27" s="30"/>
     </row>
     <row r="28" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7"/>
-      <c r="B28" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>96</v>
+      <c r="B28" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>115</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I28" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H28, G28)</f>
@@ -2465,28 +2615,28 @@
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasLatitude</v>
       </c>
       <c r="K28" s="12" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7"/>
-      <c r="B29" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>101</v>
+      <c r="B29" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>120</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I29" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H29, G29)</f>
@@ -2497,28 +2647,28 @@
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasLongitude</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7"/>
       <c r="B30" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>105</v>
+        <v>123</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>124</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I30" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H30, G30)</f>
@@ -2529,191 +2679,191 @@
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasAltitude</v>
       </c>
       <c r="K30" s="12" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7"/>
-      <c r="B31" s="26" t="s">
-        <v>108</v>
-      </c>
-      <c r="C31" s="27" t="s">
-        <v>109</v>
-      </c>
-      <c r="D31" s="27"/>
-      <c r="E31" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="G31" s="27" t="s">
+      <c r="B31" s="27" t="s">
+        <v>127</v>
+      </c>
+      <c r="C31" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="H31" s="27" t="s">
+      <c r="F31" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="I31" s="27" t="str">
+      <c r="G31" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="H31" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="I31" s="28" t="str">
         <f aca="false">_xlfn.CONCAT(H31,G31)</f>
         <v>http://purl.org/ppeo/ppeo.owl#hasDescription</v>
       </c>
-      <c r="J31" s="27" t="str">
+      <c r="J31" s="28" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G31)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasDescription</v>
       </c>
-      <c r="K31" s="27" t="s">
-        <v>110</v>
+      <c r="K31" s="28" t="s">
+        <v>129</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="32" s="30" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="32" s="31" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7"/>
-      <c r="B32" s="26" t="s">
-        <v>113</v>
-      </c>
-      <c r="C32" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="D32" s="27"/>
-      <c r="E32" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="F32" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="G32" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="H32" s="27" t="s">
+      <c r="B32" s="27" t="s">
+        <v>132</v>
+      </c>
+      <c r="C32" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="F32" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="I32" s="27" t="str">
+      <c r="G32" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="H32" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="I32" s="28" t="str">
         <f aca="false">_xlfn.CONCAT(H32,G32)</f>
         <v>http://purl.org/ppeo/ppeo.owl#hasGrowthFacilityType</v>
       </c>
-      <c r="J32" s="27" t="str">
+      <c r="J32" s="28" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G32)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasGrowthFacilityType</v>
       </c>
-      <c r="K32" s="27" t="s">
-        <v>110</v>
+      <c r="K32" s="28" t="s">
+        <v>129</v>
       </c>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
     </row>
     <row r="33" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7"/>
-      <c r="B33" s="26" t="s">
-        <v>116</v>
-      </c>
-      <c r="C33" s="27" t="s">
-        <v>117</v>
-      </c>
-      <c r="D33" s="27"/>
-      <c r="E33" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="F33" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="G33" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="H33" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="I33" s="27" t="str">
+      <c r="B33" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="C33" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="D33" s="28"/>
+      <c r="E33" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="F33" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="G33" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="H33" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="I33" s="28" t="str">
         <f aca="false">_xlfn.CONCAT(H33,G33)</f>
         <v>http://purl.org/ppeo/ppeo.owl#hasExternalIdentifier</v>
       </c>
-      <c r="J33" s="27" t="str">
+      <c r="J33" s="28" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G33)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasExternalIdentifier</v>
       </c>
-      <c r="K33" s="27"/>
+      <c r="K33" s="28"/>
     </row>
     <row r="34" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7"/>
-      <c r="B34" s="31" t="s">
-        <v>119</v>
-      </c>
-      <c r="C34" s="19" t="s">
-        <v>120</v>
-      </c>
-      <c r="D34" s="19"/>
-      <c r="E34" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="F34" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="G34" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="H34" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="I34" s="16" t="str">
+      <c r="B34" s="32" t="s">
+        <v>138</v>
+      </c>
+      <c r="C34" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="D34" s="20"/>
+      <c r="E34" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="F34" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="G34" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H34" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="I34" s="17" t="str">
         <f aca="false">_xlfn.CONCAT(H34, G34)</f>
         <v>http://purl.org/ppeo/ppeo.owl#hasDataFile</v>
       </c>
-      <c r="J34" s="19" t="str">
+      <c r="J34" s="20" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G34)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasDataFile</v>
       </c>
-      <c r="K34" s="19"/>
+      <c r="K34" s="20"/>
     </row>
     <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="32" t="s">
-        <v>72</v>
-      </c>
-      <c r="B35" s="21"/>
-      <c r="C35" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="D35" s="22"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="21"/>
-      <c r="G35" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="H35" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="I35" s="22" t="str">
+      <c r="A35" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="B35" s="22"/>
+      <c r="C35" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="D35" s="23"/>
+      <c r="E35" s="22"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="H35" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="I35" s="23" t="str">
         <f aca="false">_xlfn.CONCAT(H35, LOWER(G35))</f>
         <v>http://purl.org/ppeo/ppeo.owl#institution</v>
       </c>
-      <c r="J35" s="21" t="str">
+      <c r="J35" s="22" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G35)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#Institution</v>
       </c>
-      <c r="K35" s="21"/>
+      <c r="K35" s="22"/>
     </row>
     <row r="36" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="23"/>
-      <c r="B36" s="10" t="s">
-        <v>17</v>
+      <c r="A36" s="24"/>
+      <c r="B36" s="11" t="s">
+        <v>20</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I36" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H36, G36)</f>
@@ -2724,28 +2874,28 @@
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasIdentifier</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="23"/>
-      <c r="B37" s="10" t="s">
-        <v>123</v>
+      <c r="A37" s="24"/>
+      <c r="B37" s="11" t="s">
+        <v>142</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I37" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H37, G37)</f>
@@ -2757,24 +2907,24 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="23"/>
-      <c r="B38" s="10" t="s">
-        <v>125</v>
+      <c r="A38" s="24"/>
+      <c r="B38" s="11" t="s">
+        <v>144</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I38" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H38, G38)</f>
@@ -2786,89 +2936,89 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="23"/>
-      <c r="B39" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="C39" s="27" t="s">
-        <v>89</v>
-      </c>
-      <c r="D39" s="27"/>
-      <c r="E39" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="F39" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="G39" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="H39" s="27" t="s">
+      <c r="A39" s="24"/>
+      <c r="B39" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="C39" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="D39" s="28"/>
+      <c r="E39" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="F39" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="I39" s="27" t="str">
+      <c r="G39" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="H39" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="I39" s="28" t="str">
         <f aca="false">_xlfn.CONCAT(H39,G39)</f>
         <v>http://purl.org/ppeo/ppeo.owl#hasName</v>
       </c>
-      <c r="J39" s="27" t="str">
+      <c r="J39" s="28" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G39)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasName</v>
       </c>
-      <c r="K39" s="27"/>
+      <c r="K39" s="28"/>
       <c r="L39" s="1" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="23"/>
-      <c r="B40" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="C40" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="D40" s="27"/>
-      <c r="E40" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="F40" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="G40" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="H40" s="27" t="s">
+      <c r="A40" s="24"/>
+      <c r="B40" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="C40" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="D40" s="28"/>
+      <c r="E40" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="F40" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="I40" s="27" t="str">
+      <c r="G40" s="28" t="s">
+        <v>113</v>
+      </c>
+      <c r="H40" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="I40" s="28" t="str">
         <f aca="false">_xlfn.CONCAT(H40,G40)</f>
         <v>http://purl.org/ppeo/ppeo.owl#hasCountryCode</v>
       </c>
-      <c r="J40" s="27" t="str">
+      <c r="J40" s="28" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G40)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasCountryCode</v>
       </c>
-      <c r="K40" s="27"/>
+      <c r="K40" s="28"/>
     </row>
     <row r="41" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="23"/>
-      <c r="B41" s="10" t="s">
-        <v>128</v>
+      <c r="A41" s="24"/>
+      <c r="B41" s="11" t="s">
+        <v>147</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I41" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H41, G41)</f>
@@ -2880,21 +3030,21 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="23"/>
-      <c r="B42" s="10" t="s">
-        <v>131</v>
+      <c r="A42" s="24"/>
+      <c r="B42" s="11" t="s">
+        <v>150</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="J42" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G42)</f>
@@ -2902,21 +3052,21 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="23"/>
-      <c r="B43" s="10" t="s">
-        <v>133</v>
+      <c r="A43" s="24"/>
+      <c r="B43" s="11" t="s">
+        <v>152</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="J43" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G43)</f>
@@ -2924,21 +3074,21 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="23"/>
-      <c r="B44" s="10" t="s">
-        <v>135</v>
+      <c r="A44" s="24"/>
+      <c r="B44" s="11" t="s">
+        <v>154</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="J44" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G44)</f>
@@ -2946,21 +3096,21 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="23"/>
-      <c r="B45" s="10" t="s">
-        <v>137</v>
+      <c r="A45" s="24"/>
+      <c r="B45" s="11" t="s">
+        <v>156</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="J45" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G45)</f>
@@ -2968,21 +3118,21 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="23"/>
-      <c r="B46" s="10" t="s">
-        <v>139</v>
+      <c r="A46" s="24"/>
+      <c r="B46" s="11" t="s">
+        <v>158</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G46" s="13" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="J46" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G46)</f>
@@ -2990,24 +3140,24 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="23"/>
-      <c r="B47" s="10" t="s">
-        <v>141</v>
+      <c r="A47" s="24"/>
+      <c r="B47" s="11" t="s">
+        <v>160</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I47" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H47, G47)</f>
@@ -3018,22 +3168,22 @@
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasExternalIdentifier</v>
       </c>
     </row>
-    <row r="48" s="30" customFormat="true" ht="45.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="25" t="s">
-        <v>77</v>
+    <row r="48" s="31" customFormat="true" ht="45.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="26" t="s">
+        <v>96</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="5" t="s">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
       <c r="G48" s="4" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I48" s="5" t="str">
         <f aca="false">_xlfn.CONCAT(H48, "experimental_design")</f>
@@ -3047,23 +3197,23 @@
     </row>
     <row r="49" customFormat="false" ht="34.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="7"/>
-      <c r="B49" s="10" t="s">
-        <v>144</v>
+      <c r="B49" s="11" t="s">
+        <v>163</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I49" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H49, G49)</f>
@@ -3076,23 +3226,23 @@
     </row>
     <row r="50" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="7"/>
-      <c r="B50" s="10" t="s">
-        <v>145</v>
+      <c r="B50" s="11" t="s">
+        <v>164</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I50" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H50, G50)</f>
@@ -3105,23 +3255,23 @@
     </row>
     <row r="51" customFormat="false" ht="34.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="7"/>
-      <c r="B51" s="10" t="s">
-        <v>147</v>
+      <c r="B51" s="11" t="s">
+        <v>166</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="E51" s="24" t="s">
-        <v>50</v>
+        <v>167</v>
+      </c>
+      <c r="E51" s="25" t="s">
+        <v>65</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I51" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H51, G51)</f>
@@ -3134,23 +3284,23 @@
     </row>
     <row r="52" customFormat="false" ht="46" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="7"/>
-      <c r="B52" s="10" t="s">
-        <v>149</v>
+      <c r="B52" s="11" t="s">
+        <v>168</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I52" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H52, G52)</f>
@@ -3163,23 +3313,23 @@
     </row>
     <row r="53" customFormat="false" ht="46" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="7"/>
-      <c r="B53" s="10" t="s">
-        <v>152</v>
+      <c r="B53" s="11" t="s">
+        <v>171</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I53" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H53, G53)</f>
@@ -3191,51 +3341,51 @@
       </c>
     </row>
     <row r="54" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="32" t="s">
-        <v>155</v>
-      </c>
-      <c r="B54" s="21"/>
-      <c r="C54" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="D54" s="22"/>
-      <c r="E54" s="21"/>
-      <c r="F54" s="21"/>
-      <c r="G54" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="H54" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="I54" s="22" t="str">
+      <c r="A54" s="33" t="s">
+        <v>174</v>
+      </c>
+      <c r="B54" s="22"/>
+      <c r="C54" s="23" t="s">
+        <v>175</v>
+      </c>
+      <c r="D54" s="23"/>
+      <c r="E54" s="22"/>
+      <c r="F54" s="22"/>
+      <c r="G54" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="H54" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="I54" s="23" t="str">
         <f aca="false">_xlfn.CONCAT(H54,"data_file")</f>
         <v>http://purl.org/ppeo/ppeo.owl#data_file</v>
       </c>
-      <c r="J54" s="21" t="str">
+      <c r="J54" s="22" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G54)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#DataFile</v>
       </c>
-      <c r="K54" s="21"/>
+      <c r="K54" s="22"/>
     </row>
     <row r="55" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="33"/>
+      <c r="A55" s="34"/>
       <c r="B55" s="14" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G55" s="13" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H55" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I55" s="13" t="str">
         <f aca="false">_xlfn.CONCAT(H55, G55)</f>
@@ -3247,24 +3397,24 @@
       </c>
     </row>
     <row r="56" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="33"/>
+      <c r="A56" s="34"/>
       <c r="B56" s="14" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G56" s="13" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="H56" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I56" s="13" t="str">
         <f aca="false">_xlfn.CONCAT(H56, G56)</f>
@@ -3276,24 +3426,24 @@
       </c>
     </row>
     <row r="57" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="33"/>
+      <c r="A57" s="34"/>
       <c r="B57" s="14" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G57" s="13" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="H57" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I57" s="13" t="str">
         <f aca="false">_xlfn.CONCAT(H57, G57)</f>
@@ -3305,24 +3455,24 @@
       </c>
     </row>
     <row r="58" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="33"/>
+      <c r="A58" s="34"/>
       <c r="B58" s="14" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G58" s="13" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="H58" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I58" s="13" t="str">
         <f aca="false">_xlfn.CONCAT(H58, G58)</f>
@@ -3334,24 +3484,24 @@
       </c>
     </row>
     <row r="59" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="33"/>
+      <c r="A59" s="34"/>
       <c r="B59" s="14" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G59" s="13" t="s">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="H59" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I59" s="13" t="str">
         <f aca="false">_xlfn.CONCAT(H59, G59)</f>
@@ -3363,24 +3513,24 @@
       </c>
     </row>
     <row r="60" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="33"/>
+      <c r="A60" s="34"/>
       <c r="B60" s="14" t="s">
-        <v>168</v>
+        <v>187</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="E60" s="34" t="s">
-        <v>170</v>
+        <v>188</v>
+      </c>
+      <c r="E60" s="35" t="s">
+        <v>189</v>
       </c>
       <c r="F60" s="13" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="G60" s="13" t="s">
-        <v>171</v>
+        <v>190</v>
       </c>
       <c r="H60" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I60" s="13" t="str">
         <f aca="false">_xlfn.CONCAT(H60, G60)</f>
@@ -3392,21 +3542,21 @@
       </c>
     </row>
     <row r="61" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="25" t="s">
-        <v>172</v>
+      <c r="A61" s="26" t="s">
+        <v>191</v>
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="5" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="D61" s="5"/>
       <c r="E61" s="4"/>
       <c r="F61" s="4"/>
       <c r="G61" s="4" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="I61" s="5" t="str">
         <f aca="false">_xlfn.CONCAT(H61, G61)</f>
@@ -3417,23 +3567,29 @@
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#System</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="7"/>
-      <c r="B62" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C62" s="35" t="s">
-        <v>122</v>
-      </c>
-      <c r="D62" s="35"/>
+      <c r="B62" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C62" s="36" t="s">
+        <v>141</v>
+      </c>
+      <c r="D62" s="36"/>
+      <c r="E62" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="G62" s="13" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I62" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H62, G62)</f>
@@ -3446,16 +3602,16 @@
     </row>
     <row r="63" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="7"/>
-      <c r="B63" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="C63" s="35"/>
-      <c r="D63" s="35"/>
+      <c r="B63" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C63" s="36"/>
+      <c r="D63" s="36"/>
       <c r="G63" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I63" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H63, G63)</f>
@@ -3468,16 +3624,16 @@
     </row>
     <row r="64" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="7"/>
-      <c r="B64" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="C64" s="35"/>
-      <c r="D64" s="35"/>
+      <c r="B64" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="C64" s="36"/>
+      <c r="D64" s="36"/>
       <c r="G64" s="13" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I64" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H64, G64)</f>
@@ -3490,15 +3646,15 @@
     </row>
     <row r="65" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="7"/>
-      <c r="B65" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="C65" s="35" t="s">
-        <v>179</v>
-      </c>
-      <c r="D65" s="35"/>
-      <c r="G65" s="35" t="s">
-        <v>180</v>
+      <c r="B65" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="C65" s="36" t="s">
+        <v>198</v>
+      </c>
+      <c r="D65" s="36"/>
+      <c r="G65" s="36" t="s">
+        <v>199</v>
       </c>
       <c r="J65" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G65)</f>
@@ -3507,19 +3663,19 @@
     </row>
     <row r="66" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="7"/>
-      <c r="B66" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="C66" s="35"/>
-      <c r="D66" s="35"/>
+      <c r="B66" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="C66" s="36"/>
+      <c r="D66" s="36"/>
       <c r="E66" s="1" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="G66" s="13" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="I66" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H66, G66)</f>
@@ -3532,19 +3688,19 @@
     </row>
     <row r="67" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="7"/>
-      <c r="B67" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="C67" s="35"/>
-      <c r="D67" s="35"/>
+      <c r="B67" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="C67" s="36"/>
+      <c r="D67" s="36"/>
       <c r="E67" s="1" t="s">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="G67" s="13" t="s">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="I67" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H67, G67)</f>
@@ -3557,21 +3713,21 @@
     </row>
     <row r="68" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="7"/>
-      <c r="B68" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="C68" s="35" t="s">
-        <v>187</v>
-      </c>
-      <c r="D68" s="35"/>
+      <c r="B68" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="C68" s="36" t="s">
+        <v>206</v>
+      </c>
+      <c r="D68" s="36"/>
       <c r="E68" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="G68" s="35" t="s">
-        <v>189</v>
-      </c>
-      <c r="H68" s="35" t="s">
-        <v>185</v>
+        <v>207</v>
+      </c>
+      <c r="G68" s="36" t="s">
+        <v>208</v>
+      </c>
+      <c r="H68" s="36" t="s">
+        <v>204</v>
       </c>
       <c r="I68" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H68, G68)</f>
@@ -3584,19 +3740,19 @@
     </row>
     <row r="69" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="7"/>
-      <c r="B69" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C69" s="35"/>
-      <c r="D69" s="35"/>
+      <c r="B69" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="C69" s="36"/>
+      <c r="D69" s="36"/>
       <c r="E69" s="1" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="G69" s="13" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="I69" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H69, G69)</f>
@@ -3609,18 +3765,18 @@
     </row>
     <row r="70" customFormat="false" ht="46" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="7"/>
-      <c r="B70" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="C70" s="35" t="s">
-        <v>191</v>
-      </c>
-      <c r="D70" s="35"/>
+      <c r="B70" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="C70" s="36" t="s">
+        <v>210</v>
+      </c>
+      <c r="D70" s="36"/>
       <c r="E70" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="G70" s="35" t="s">
-        <v>193</v>
+        <v>211</v>
+      </c>
+      <c r="G70" s="36" t="s">
+        <v>212</v>
       </c>
       <c r="I70" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H70, G70)</f>
@@ -3633,18 +3789,18 @@
     </row>
     <row r="71" customFormat="false" ht="46" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="7"/>
-      <c r="B71" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="C71" s="35" t="s">
-        <v>195</v>
-      </c>
-      <c r="D71" s="35"/>
+      <c r="B71" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="C71" s="36" t="s">
+        <v>214</v>
+      </c>
+      <c r="D71" s="36"/>
       <c r="E71" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="G71" s="35" t="s">
-        <v>196</v>
+        <v>211</v>
+      </c>
+      <c r="G71" s="36" t="s">
+        <v>215</v>
       </c>
       <c r="I71" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H71, G71)</f>
@@ -3657,14 +3813,14 @@
     </row>
     <row r="72" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="7"/>
-      <c r="B72" s="10" t="s">
-        <v>197</v>
+      <c r="B72" s="11" t="s">
+        <v>216</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="J72" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G72)</f>
@@ -3673,17 +3829,17 @@
     </row>
     <row r="73" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="7"/>
-      <c r="B73" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="C73" s="35" t="s">
-        <v>201</v>
-      </c>
-      <c r="D73" s="35"/>
+      <c r="B73" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="C73" s="36" t="s">
+        <v>220</v>
+      </c>
+      <c r="D73" s="36"/>
       <c r="E73" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="G73" s="35"/>
+        <v>221</v>
+      </c>
+      <c r="G73" s="36"/>
       <c r="J73" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G73)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
@@ -3691,8 +3847,8 @@
     </row>
     <row r="74" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="7"/>
-      <c r="B74" s="10" t="s">
-        <v>203</v>
+      <c r="B74" s="11" t="s">
+        <v>222</v>
       </c>
       <c r="J74" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G74)</f>
@@ -3701,8 +3857,8 @@
     </row>
     <row r="75" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="7"/>
-      <c r="B75" s="10" t="s">
-        <v>204</v>
+      <c r="B75" s="11" t="s">
+        <v>223</v>
       </c>
       <c r="J75" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G75)</f>
@@ -3711,8 +3867,8 @@
     </row>
     <row r="76" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="7"/>
-      <c r="B76" s="10" t="s">
-        <v>205</v>
+      <c r="B76" s="11" t="s">
+        <v>224</v>
       </c>
       <c r="J76" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G76)</f>
@@ -3721,8 +3877,8 @@
     </row>
     <row r="77" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="7"/>
-      <c r="B77" s="10" t="s">
-        <v>206</v>
+      <c r="B77" s="11" t="s">
+        <v>225</v>
       </c>
       <c r="J77" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G77)</f>
@@ -3731,8 +3887,8 @@
     </row>
     <row r="78" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="7"/>
-      <c r="B78" s="10" t="s">
-        <v>207</v>
+      <c r="B78" s="11" t="s">
+        <v>226</v>
       </c>
       <c r="J78" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G78)</f>
@@ -3741,8 +3897,8 @@
     </row>
     <row r="79" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="7"/>
-      <c r="B79" s="10" t="s">
-        <v>208</v>
+      <c r="B79" s="11" t="s">
+        <v>227</v>
       </c>
       <c r="J79" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G79)</f>
@@ -3751,8 +3907,8 @@
     </row>
     <row r="80" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="7"/>
-      <c r="B80" s="10" t="s">
-        <v>209</v>
+      <c r="B80" s="11" t="s">
+        <v>228</v>
       </c>
       <c r="J80" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G80)</f>
@@ -3761,8 +3917,8 @@
     </row>
     <row r="81" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="7"/>
-      <c r="B81" s="10" t="s">
-        <v>210</v>
+      <c r="B81" s="11" t="s">
+        <v>229</v>
       </c>
       <c r="J81" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G81)</f>
@@ -3771,8 +3927,8 @@
     </row>
     <row r="82" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="7"/>
-      <c r="B82" s="10" t="s">
-        <v>211</v>
+      <c r="B82" s="11" t="s">
+        <v>230</v>
       </c>
       <c r="J82" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G82)</f>
@@ -3781,8 +3937,8 @@
     </row>
     <row r="83" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="7"/>
-      <c r="B83" s="10" t="s">
-        <v>212</v>
+      <c r="B83" s="11" t="s">
+        <v>231</v>
       </c>
       <c r="J83" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G83)</f>
@@ -3790,45 +3946,51 @@
       </c>
     </row>
     <row r="84" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="B84" s="21"/>
-      <c r="C84" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="D84" s="22"/>
-      <c r="E84" s="21"/>
-      <c r="F84" s="21"/>
-      <c r="G84" s="21" t="s">
-        <v>183</v>
-      </c>
-      <c r="H84" s="22" t="s">
-        <v>174</v>
-      </c>
-      <c r="I84" s="22" t="str">
+      <c r="A84" s="33" t="s">
+        <v>202</v>
+      </c>
+      <c r="B84" s="22"/>
+      <c r="C84" s="23" t="s">
+        <v>232</v>
+      </c>
+      <c r="D84" s="23"/>
+      <c r="E84" s="22"/>
+      <c r="F84" s="22"/>
+      <c r="G84" s="22" t="s">
+        <v>202</v>
+      </c>
+      <c r="H84" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="I84" s="23" t="str">
         <f aca="false">_xlfn.CONCAT(H84, G84)</f>
         <v>http://www.w3.org/ns/ssn/Platform</v>
       </c>
-      <c r="J84" s="21" t="str">
+      <c r="J84" s="22" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G84)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#Platform</v>
       </c>
-      <c r="K84" s="21"/>
+      <c r="K84" s="22"/>
     </row>
     <row r="85" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="23"/>
-      <c r="B85" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="C85" s="11" t="s">
-        <v>122</v>
+      <c r="A85" s="24"/>
+      <c r="B85" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="C85" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I85" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H85, G85)</f>
@@ -3840,15 +4002,15 @@
       </c>
     </row>
     <row r="86" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="23"/>
-      <c r="B86" s="10" t="s">
-        <v>215</v>
+      <c r="A86" s="24"/>
+      <c r="B86" s="11" t="s">
+        <v>234</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I86" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H86, G86)</f>
@@ -3860,15 +4022,15 @@
       </c>
     </row>
     <row r="87" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="23"/>
-      <c r="B87" s="10" t="s">
-        <v>216</v>
+      <c r="A87" s="24"/>
+      <c r="B87" s="11" t="s">
+        <v>235</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I87" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H87, G87)</f>
@@ -3880,12 +4042,12 @@
       </c>
     </row>
     <row r="88" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="23"/>
-      <c r="B88" s="10" t="s">
-        <v>217</v>
+      <c r="A88" s="24"/>
+      <c r="B88" s="11" t="s">
+        <v>236</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="J88" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G88)</f>
@@ -3893,12 +4055,12 @@
       </c>
     </row>
     <row r="89" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="23"/>
-      <c r="B89" s="10" t="s">
-        <v>219</v>
+      <c r="A89" s="24"/>
+      <c r="B89" s="11" t="s">
+        <v>238</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="J89" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G89)</f>
@@ -3906,15 +4068,15 @@
       </c>
     </row>
     <row r="90" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="23"/>
-      <c r="B90" s="10" t="s">
-        <v>221</v>
+      <c r="A90" s="24"/>
+      <c r="B90" s="11" t="s">
+        <v>240</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I90" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H90, G90)</f>
@@ -3926,12 +4088,12 @@
       </c>
     </row>
     <row r="91" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="23"/>
-      <c r="B91" s="10" t="s">
-        <v>222</v>
+      <c r="A91" s="24"/>
+      <c r="B91" s="11" t="s">
+        <v>241</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="J91" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G91)</f>
@@ -3939,21 +4101,21 @@
       </c>
     </row>
     <row r="92" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="25" t="s">
-        <v>186</v>
+      <c r="A92" s="26" t="s">
+        <v>205</v>
       </c>
       <c r="B92" s="4"/>
       <c r="C92" s="5" t="s">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="D92" s="5"/>
       <c r="E92" s="4"/>
       <c r="F92" s="4"/>
       <c r="G92" s="4" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="H92" s="5" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="I92" s="5" t="str">
         <f aca="false">_xlfn.CONCAT(H92, G92)</f>
@@ -3967,17 +4129,17 @@
     </row>
     <row r="93" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="7"/>
-      <c r="B93" s="10" t="s">
-        <v>224</v>
-      </c>
-      <c r="C93" s="11" t="s">
-        <v>122</v>
+      <c r="B93" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="C93" s="10" t="s">
+        <v>141</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I93" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H93, G93)</f>
@@ -3990,14 +4152,14 @@
     </row>
     <row r="94" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="7"/>
-      <c r="B94" s="10" t="s">
-        <v>225</v>
+      <c r="B94" s="11" t="s">
+        <v>244</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I94" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H94, G94)</f>
@@ -4010,14 +4172,14 @@
     </row>
     <row r="95" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="7"/>
-      <c r="B95" s="10" t="s">
-        <v>226</v>
+      <c r="B95" s="11" t="s">
+        <v>245</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I95" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H95, G95)</f>
@@ -4030,11 +4192,11 @@
     </row>
     <row r="96" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="7"/>
-      <c r="B96" s="10" t="s">
-        <v>227</v>
+      <c r="B96" s="11" t="s">
+        <v>246</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
       <c r="J96" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G96)</f>
@@ -4043,11 +4205,11 @@
     </row>
     <row r="97" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="7"/>
-      <c r="B97" s="10" t="s">
-        <v>219</v>
+      <c r="B97" s="11" t="s">
+        <v>238</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="J97" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G97)</f>
@@ -4056,14 +4218,14 @@
     </row>
     <row r="98" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="7"/>
-      <c r="B98" s="10" t="s">
-        <v>221</v>
+      <c r="B98" s="11" t="s">
+        <v>240</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I98" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H98, G98)</f>
@@ -4076,14 +4238,14 @@
     </row>
     <row r="99" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="7"/>
-      <c r="B99" s="10" t="s">
-        <v>229</v>
+      <c r="B99" s="11" t="s">
+        <v>248</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="I99" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H99, G99)</f>
@@ -4096,11 +4258,11 @@
     </row>
     <row r="100" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="7"/>
-      <c r="B100" s="10" t="s">
-        <v>222</v>
+      <c r="B100" s="11" t="s">
+        <v>241</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="J100" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G100)</f>
@@ -4108,57 +4270,69 @@
       </c>
     </row>
     <row r="101" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="32" t="s">
-        <v>229</v>
-      </c>
-      <c r="B101" s="21"/>
-      <c r="C101" s="22" t="s">
-        <v>231</v>
-      </c>
-      <c r="D101" s="22"/>
-      <c r="E101" s="21"/>
-      <c r="F101" s="21"/>
-      <c r="G101" s="21" t="s">
-        <v>232</v>
-      </c>
-      <c r="H101" s="22" t="s">
-        <v>185</v>
-      </c>
-      <c r="I101" s="22" t="str">
+      <c r="A101" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="B101" s="22"/>
+      <c r="C101" s="23" t="s">
+        <v>250</v>
+      </c>
+      <c r="D101" s="23"/>
+      <c r="E101" s="22"/>
+      <c r="F101" s="22"/>
+      <c r="G101" s="22" t="s">
+        <v>251</v>
+      </c>
+      <c r="H101" s="23" t="s">
+        <v>204</v>
+      </c>
+      <c r="I101" s="23" t="str">
         <f aca="false">_xlfn.CONCAT(H101, G101)</f>
         <v>http://www.w3.org/ns/sosa/Observation </v>
       </c>
-      <c r="J101" s="21" t="str">
+      <c r="J101" s="22" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G101)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#Observation </v>
       </c>
-      <c r="K101" s="21" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="23"/>
-      <c r="B102" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C102" s="11" t="s">
-        <v>122</v>
+      <c r="K101" s="22" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="36.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="24"/>
+      <c r="B102" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C102" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
+      </c>
+      <c r="H102" s="15" t="s">
+        <v>15</v>
       </c>
       <c r="J102" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G102)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasIdentifier</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="23"/>
-      <c r="B103" s="10" t="s">
-        <v>233</v>
+    <row r="103" customFormat="false" ht="36.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="24"/>
+      <c r="B103" s="11" t="s">
+        <v>252</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>234</v>
+        <v>253</v>
+      </c>
+      <c r="H103" s="15" t="s">
+        <v>15</v>
       </c>
       <c r="J103" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G103)</f>
@@ -4166,18 +4340,18 @@
       </c>
     </row>
     <row r="104" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="23"/>
-      <c r="B104" s="10" t="s">
-        <v>235</v>
+      <c r="A104" s="24"/>
+      <c r="B104" s="11" t="s">
+        <v>254</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="H104" s="11" t="s">
-        <v>185</v>
+        <v>256</v>
+      </c>
+      <c r="H104" s="10" t="s">
+        <v>204</v>
       </c>
       <c r="J104" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G104)</f>
@@ -4185,15 +4359,15 @@
       </c>
     </row>
     <row r="105" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="23"/>
-      <c r="B105" s="10" t="s">
-        <v>238</v>
+      <c r="A105" s="24"/>
+      <c r="B105" s="11" t="s">
+        <v>257</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="H105" s="11" t="s">
-        <v>185</v>
+        <v>258</v>
+      </c>
+      <c r="H105" s="10" t="s">
+        <v>204</v>
       </c>
       <c r="J105" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G105)</f>
@@ -4201,15 +4375,15 @@
       </c>
     </row>
     <row r="106" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="23"/>
-      <c r="B106" s="10" t="s">
-        <v>240</v>
+      <c r="A106" s="24"/>
+      <c r="B106" s="11" t="s">
+        <v>259</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="J106" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G106)</f>
@@ -4217,15 +4391,15 @@
       </c>
     </row>
     <row r="107" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="23"/>
-      <c r="B107" s="10" t="s">
-        <v>242</v>
+      <c r="A107" s="24"/>
+      <c r="B107" s="11" t="s">
+        <v>261</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="H107" s="11" t="s">
-        <v>185</v>
+        <v>262</v>
+      </c>
+      <c r="H107" s="10" t="s">
+        <v>204</v>
       </c>
       <c r="J107" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G107)</f>
@@ -4233,21 +4407,21 @@
       </c>
     </row>
     <row r="108" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="25" t="s">
-        <v>244</v>
+      <c r="A108" s="26" t="s">
+        <v>263</v>
       </c>
       <c r="B108" s="4"/>
       <c r="C108" s="5" t="s">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="D108" s="5"/>
       <c r="E108" s="4"/>
       <c r="F108" s="4"/>
       <c r="G108" s="4" t="s">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="H108" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I108" s="5" t="str">
         <f aca="false">_xlfn.CONCAT(H108, "observation_unit")</f>
@@ -4261,17 +4435,20 @@
     </row>
     <row r="109" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="7"/>
-      <c r="B109" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C109" s="11" t="s">
-        <v>122</v>
+      <c r="B109" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C109" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H109" s="11" t="s">
-        <v>14</v>
+        <v>21</v>
+      </c>
+      <c r="H109" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="I109" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H109,G109)</f>
@@ -4284,20 +4461,20 @@
     </row>
     <row r="110" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="7"/>
-      <c r="B110" s="10" t="s">
-        <v>229</v>
+      <c r="B110" s="11" t="s">
+        <v>266</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="H110" s="11" t="s">
-        <v>14</v>
+        <v>190</v>
+      </c>
+      <c r="H110" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="I110" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H110,G110)</f>
@@ -4307,30 +4484,49 @@
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G110)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#partOf</v>
       </c>
+      <c r="K110" s="1" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="111" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="7"/>
-      <c r="B111" s="10" t="s">
-        <v>233</v>
+      <c r="B111" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>234</v>
+        <v>253</v>
+      </c>
+      <c r="H111" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="I111" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT(H111,G111)</f>
+        <v>http://purl.org/ppeo/ppeo.owl#partOf </v>
       </c>
       <c r="J111" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G111)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#partOf </v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="7"/>
-      <c r="B112" s="10" t="s">
-        <v>248</v>
+      <c r="B112" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="C112" s="15" t="s">
+        <v>271</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H112" s="11" t="s">
-        <v>14</v>
+        <v>33</v>
+      </c>
+      <c r="H112" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="I112" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H112,G112)</f>
@@ -4341,16 +4537,19 @@
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasDescription</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="47.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="7"/>
-      <c r="B113" s="10" t="s">
-        <v>249</v>
+      <c r="B113" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="C113" s="15" t="s">
+        <v>273</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="H113" s="11" t="s">
-        <v>14</v>
+        <v>137</v>
+      </c>
+      <c r="H113" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="I113" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H113,G113)</f>
@@ -4363,67 +4562,73 @@
     </row>
     <row r="114" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="7"/>
-      <c r="B114" s="26" t="s">
-        <v>250</v>
-      </c>
-      <c r="C114" s="27"/>
-      <c r="D114" s="27"/>
-      <c r="E114" s="27"/>
-      <c r="F114" s="27"/>
-      <c r="G114" s="27" t="s">
-        <v>251</v>
-      </c>
-      <c r="H114" s="27" t="s">
-        <v>14</v>
+      <c r="B114" s="27" t="s">
+        <v>274</v>
+      </c>
+      <c r="C114" s="28"/>
+      <c r="D114" s="28"/>
+      <c r="E114" s="28"/>
+      <c r="F114" s="28"/>
+      <c r="G114" s="28" t="s">
+        <v>275</v>
+      </c>
+      <c r="H114" s="28" t="s">
+        <v>15</v>
       </c>
       <c r="I114" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H114,G114)</f>
         <v>http://purl.org/ppeo/ppeo.owl#hasSpatialDistribution</v>
       </c>
-      <c r="J114" s="27" t="str">
+      <c r="J114" s="28" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G114)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasSpatialDistribution</v>
       </c>
-      <c r="K114" s="27"/>
+      <c r="K114" s="28"/>
       <c r="L114" s="1" t="s">
-        <v>252</v>
+        <v>276</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="7"/>
-      <c r="B115" s="26" t="s">
-        <v>253</v>
-      </c>
-      <c r="C115" s="27"/>
-      <c r="D115" s="27"/>
-      <c r="E115" s="27"/>
-      <c r="F115" s="27"/>
-      <c r="G115" s="27" t="s">
-        <v>254</v>
-      </c>
-      <c r="H115" s="27" t="s">
-        <v>14</v>
+      <c r="B115" s="27" t="s">
+        <v>277</v>
+      </c>
+      <c r="C115" s="28"/>
+      <c r="D115" s="28"/>
+      <c r="E115" s="28"/>
+      <c r="F115" s="28"/>
+      <c r="G115" s="28" t="s">
+        <v>278</v>
+      </c>
+      <c r="H115" s="28" t="s">
+        <v>15</v>
       </c>
       <c r="I115" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H115,G115)</f>
         <v>http://purl.org/ppeo/ppeo.owl#hasSpatialDistributionType</v>
       </c>
-      <c r="J115" s="27" t="str">
+      <c r="J115" s="28" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G115)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasSpatialDistributionType</v>
       </c>
-      <c r="K115" s="27"/>
-    </row>
-    <row r="116" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K115" s="28"/>
+    </row>
+    <row r="116" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="7"/>
-      <c r="B116" s="10" t="s">
-        <v>255</v>
+      <c r="B116" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>281</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="H116" s="11" t="s">
-        <v>14</v>
+        <v>186</v>
+      </c>
+      <c r="H116" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="I116" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H116,G116)</f>
@@ -4436,11 +4641,11 @@
     </row>
     <row r="117" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="7"/>
-      <c r="B117" s="10" t="s">
-        <v>256</v>
-      </c>
-      <c r="H117" s="11" t="s">
-        <v>14</v>
+      <c r="B117" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="H117" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="I117" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H117,G117)</f>
@@ -4452,47 +4657,47 @@
       </c>
     </row>
     <row r="118" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="32" t="s">
-        <v>257</v>
-      </c>
-      <c r="B118" s="21"/>
-      <c r="C118" s="22" t="s">
-        <v>258</v>
-      </c>
-      <c r="D118" s="22"/>
-      <c r="E118" s="21"/>
-      <c r="F118" s="21"/>
-      <c r="G118" s="21" t="s">
-        <v>259</v>
-      </c>
-      <c r="H118" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="I118" s="22" t="str">
+      <c r="A118" s="33" t="s">
+        <v>283</v>
+      </c>
+      <c r="B118" s="22"/>
+      <c r="C118" s="23" t="s">
+        <v>284</v>
+      </c>
+      <c r="D118" s="23"/>
+      <c r="E118" s="22"/>
+      <c r="F118" s="22"/>
+      <c r="G118" s="22" t="s">
+        <v>285</v>
+      </c>
+      <c r="H118" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="I118" s="23" t="str">
         <f aca="false">_xlfn.CONCAT(H118,"observed_variable")</f>
         <v>http://purl.org/ppeo/ppeo.owl#observed_variable</v>
       </c>
-      <c r="J118" s="21" t="str">
+      <c r="J118" s="22" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G118)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#ObservedVariable</v>
       </c>
-      <c r="K118" s="21" t="s">
-        <v>260</v>
+      <c r="K118" s="22" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="23"/>
-      <c r="B119" s="10" t="s">
-        <v>261</v>
-      </c>
-      <c r="C119" s="11" t="s">
-        <v>122</v>
+      <c r="A119" s="24"/>
+      <c r="B119" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="C119" s="10" t="s">
+        <v>141</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H119" s="11" t="s">
-        <v>14</v>
+        <v>21</v>
+      </c>
+      <c r="H119" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J119" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G119)</f>
@@ -4500,12 +4705,12 @@
       </c>
     </row>
     <row r="120" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="23"/>
-      <c r="B120" s="10" t="s">
-        <v>262</v>
-      </c>
-      <c r="H120" s="11" t="s">
-        <v>14</v>
+      <c r="A120" s="24"/>
+      <c r="B120" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="H120" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J120" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G120)</f>
@@ -4513,9 +4718,9 @@
       </c>
     </row>
     <row r="121" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="23"/>
-      <c r="B121" s="10" t="s">
-        <v>263</v>
+      <c r="A121" s="24"/>
+      <c r="B121" s="11" t="s">
+        <v>289</v>
       </c>
       <c r="J121" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G121)</f>
@@ -4523,9 +4728,9 @@
       </c>
     </row>
     <row r="122" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="23"/>
-      <c r="B122" s="10" t="s">
-        <v>264</v>
+      <c r="A122" s="24"/>
+      <c r="B122" s="11" t="s">
+        <v>290</v>
       </c>
       <c r="J122" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G122)</f>
@@ -4533,45 +4738,45 @@
       </c>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="23"/>
-      <c r="B123" s="10" t="s">
-        <v>265</v>
+      <c r="A123" s="24"/>
+      <c r="B123" s="11" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="23"/>
-      <c r="B124" s="10" t="s">
-        <v>266</v>
+      <c r="A124" s="24"/>
+      <c r="B124" s="11" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="23"/>
-      <c r="B125" s="10"/>
+      <c r="A125" s="24"/>
+      <c r="B125" s="11"/>
     </row>
     <row r="126" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="23"/>
-      <c r="B126" s="10"/>
+      <c r="A126" s="24"/>
+      <c r="B126" s="11"/>
       <c r="J126" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G126)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="25" t="s">
-        <v>256</v>
+      <c r="A127" s="26" t="s">
+        <v>282</v>
       </c>
       <c r="B127" s="4"/>
       <c r="C127" s="5" t="s">
-        <v>267</v>
+        <v>293</v>
       </c>
       <c r="D127" s="5"/>
       <c r="E127" s="4"/>
       <c r="F127" s="4"/>
       <c r="G127" s="4" t="s">
-        <v>268</v>
+        <v>294</v>
       </c>
       <c r="H127" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I127" s="5" t="str">
         <f aca="false">_xlfn.CONCAT(H127,LOWER(G127))</f>
@@ -4585,17 +4790,17 @@
     </row>
     <row r="128" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="7"/>
-      <c r="B128" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C128" s="11" t="s">
-        <v>122</v>
+      <c r="B128" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C128" s="10" t="s">
+        <v>141</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H128" s="11" t="s">
-        <v>14</v>
+        <v>21</v>
+      </c>
+      <c r="H128" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J128" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G128)</f>
@@ -4604,11 +4809,11 @@
     </row>
     <row r="129" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="7"/>
-      <c r="B129" s="10" t="s">
-        <v>233</v>
+      <c r="B129" s="11" t="s">
+        <v>252</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>234</v>
+        <v>253</v>
       </c>
       <c r="J129" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G129)</f>
@@ -4617,8 +4822,8 @@
     </row>
     <row r="130" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="7"/>
-      <c r="B130" s="10" t="s">
-        <v>269</v>
+      <c r="B130" s="11" t="s">
+        <v>295</v>
       </c>
       <c r="J130" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G130)</f>
@@ -4627,62 +4832,62 @@
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="7"/>
-      <c r="B131" s="10" t="s">
-        <v>270</v>
+      <c r="B131" s="11" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="7"/>
-      <c r="B132" s="10" t="s">
-        <v>271</v>
+      <c r="B132" s="11" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="7"/>
-      <c r="B133" s="10" t="s">
-        <v>272</v>
+      <c r="B133" s="11" t="s">
+        <v>298</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>273</v>
+        <v>299</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="32" t="s">
-        <v>274</v>
-      </c>
-      <c r="B134" s="21"/>
-      <c r="C134" s="22" t="s">
-        <v>275</v>
-      </c>
-      <c r="D134" s="22"/>
-      <c r="E134" s="21"/>
-      <c r="F134" s="21"/>
-      <c r="G134" s="21" t="s">
-        <v>274</v>
-      </c>
-      <c r="H134" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="I134" s="22"/>
-      <c r="J134" s="21" t="str">
+      <c r="A134" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="B134" s="22"/>
+      <c r="C134" s="23" t="s">
+        <v>301</v>
+      </c>
+      <c r="D134" s="23"/>
+      <c r="E134" s="22"/>
+      <c r="F134" s="22"/>
+      <c r="G134" s="22" t="s">
+        <v>300</v>
+      </c>
+      <c r="H134" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="I134" s="23"/>
+      <c r="J134" s="22" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G134)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#Sample</v>
       </c>
-      <c r="K134" s="21"/>
+      <c r="K134" s="22"/>
     </row>
     <row r="135" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="23"/>
-      <c r="B135" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C135" s="11" t="s">
-        <v>122</v>
+      <c r="A135" s="24"/>
+      <c r="B135" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C135" s="10" t="s">
+        <v>141</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H135" s="11" t="s">
-        <v>14</v>
+        <v>21</v>
+      </c>
+      <c r="H135" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J135" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G135)</f>
@@ -4690,34 +4895,34 @@
       </c>
     </row>
     <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="23"/>
-      <c r="B136" s="10"/>
-      <c r="C136" s="11"/>
+      <c r="A136" s="24"/>
+      <c r="B136" s="11"/>
+      <c r="C136" s="10"/>
     </row>
     <row r="137" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="23"/>
-      <c r="B137" s="10"/>
+      <c r="A137" s="24"/>
+      <c r="B137" s="11"/>
       <c r="J137" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G137)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="25" t="s">
-        <v>276</v>
+      <c r="A138" s="26" t="s">
+        <v>302</v>
       </c>
       <c r="B138" s="4"/>
       <c r="C138" s="5" t="s">
-        <v>277</v>
+        <v>303</v>
       </c>
       <c r="D138" s="5"/>
       <c r="E138" s="4"/>
       <c r="F138" s="4"/>
       <c r="G138" s="4" t="s">
-        <v>278</v>
+        <v>304</v>
       </c>
       <c r="H138" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I138" s="5"/>
       <c r="J138" s="4" t="str">
@@ -4728,17 +4933,17 @@
     </row>
     <row r="139" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="7"/>
-      <c r="B139" s="10" t="s">
-        <v>279</v>
-      </c>
-      <c r="C139" s="11" t="s">
-        <v>280</v>
+      <c r="B139" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="C139" s="10" t="s">
+        <v>306</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H139" s="11" t="s">
-        <v>14</v>
+        <v>21</v>
+      </c>
+      <c r="H139" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J139" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G139)</f>
@@ -4747,11 +4952,11 @@
     </row>
     <row r="140" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="7"/>
-      <c r="B140" s="10" t="s">
-        <v>281</v>
+      <c r="B140" s="11" t="s">
+        <v>307</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>282</v>
+        <v>308</v>
       </c>
       <c r="J140" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G140)</f>
@@ -4760,100 +4965,100 @@
     </row>
     <row r="141" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="7"/>
-      <c r="B141" s="10" t="s">
-        <v>283</v>
+      <c r="B141" s="11" t="s">
+        <v>309</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>284</v>
+        <v>310</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="7"/>
-      <c r="B142" s="10" t="s">
-        <v>285</v>
+      <c r="B142" s="11" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="7"/>
-      <c r="B143" s="10" t="s">
-        <v>286</v>
+      <c r="B143" s="11" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="7"/>
-      <c r="B144" s="10" t="s">
-        <v>287</v>
+      <c r="B144" s="11" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="7"/>
-      <c r="B145" s="10"/>
+      <c r="B145" s="11"/>
     </row>
     <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="7"/>
-      <c r="B146" s="10"/>
+      <c r="B146" s="11"/>
     </row>
     <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="7"/>
-      <c r="B147" s="10"/>
+      <c r="B147" s="11"/>
     </row>
     <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="7"/>
-      <c r="B148" s="10"/>
+      <c r="B148" s="11"/>
     </row>
     <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="7"/>
-      <c r="B149" s="10"/>
+      <c r="B149" s="11"/>
     </row>
     <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="7"/>
-      <c r="B150" s="10"/>
+      <c r="B150" s="11"/>
     </row>
     <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="7"/>
-      <c r="B151" s="10"/>
+      <c r="B151" s="11"/>
     </row>
     <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="7"/>
-      <c r="B152" s="10"/>
+      <c r="B152" s="11"/>
     </row>
     <row r="153" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="32" t="s">
-        <v>288</v>
-      </c>
-      <c r="B153" s="21"/>
-      <c r="C153" s="22" t="s">
-        <v>289</v>
-      </c>
-      <c r="D153" s="22"/>
-      <c r="E153" s="21"/>
-      <c r="F153" s="21"/>
-      <c r="G153" s="21" t="s">
-        <v>288</v>
-      </c>
-      <c r="H153" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="I153" s="22"/>
-      <c r="J153" s="21" t="str">
+      <c r="A153" s="33" t="s">
+        <v>314</v>
+      </c>
+      <c r="B153" s="22"/>
+      <c r="C153" s="23" t="s">
+        <v>315</v>
+      </c>
+      <c r="D153" s="23"/>
+      <c r="E153" s="22"/>
+      <c r="F153" s="22"/>
+      <c r="G153" s="22" t="s">
+        <v>314</v>
+      </c>
+      <c r="H153" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="I153" s="23"/>
+      <c r="J153" s="22" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G153)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#Event</v>
       </c>
-      <c r="K153" s="21"/>
+      <c r="K153" s="22"/>
     </row>
     <row r="154" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="23"/>
-      <c r="B154" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C154" s="11" t="s">
-        <v>122</v>
+      <c r="A154" s="24"/>
+      <c r="B154" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C154" s="10" t="s">
+        <v>141</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H154" s="11" t="s">
-        <v>14</v>
+        <v>21</v>
+      </c>
+      <c r="H154" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J154" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G154)</f>
@@ -4861,43 +5066,43 @@
       </c>
     </row>
     <row r="155" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="23"/>
-      <c r="B155" s="10"/>
+      <c r="A155" s="24"/>
+      <c r="B155" s="11"/>
       <c r="J155" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G155)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="23"/>
-      <c r="B156" s="10"/>
+      <c r="A156" s="24"/>
+      <c r="B156" s="11"/>
       <c r="J156" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G156)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="23"/>
-      <c r="B157" s="10"/>
+      <c r="A157" s="24"/>
+      <c r="B157" s="11"/>
       <c r="J157" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G157)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="25" t="s">
-        <v>290</v>
+      <c r="A158" s="26" t="s">
+        <v>316</v>
       </c>
       <c r="B158" s="4"/>
       <c r="C158" s="5" t="s">
-        <v>291</v>
+        <v>317</v>
       </c>
       <c r="D158" s="5"/>
       <c r="E158" s="4"/>
       <c r="F158" s="4"/>
       <c r="G158" s="4"/>
       <c r="H158" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I158" s="5"/>
       <c r="J158" s="4" t="str">
@@ -4908,17 +5113,17 @@
     </row>
     <row r="159" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="7"/>
-      <c r="B159" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C159" s="11" t="s">
-        <v>122</v>
+      <c r="B159" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C159" s="10" t="s">
+        <v>141</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H159" s="11" t="s">
-        <v>14</v>
+        <v>21</v>
+      </c>
+      <c r="H159" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J159" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G159)</f>
@@ -4927,41 +5132,41 @@
     </row>
     <row r="160" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="7"/>
-      <c r="B160" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="C160" s="11" t="s">
-        <v>292</v>
+      <c r="B160" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C160" s="10" t="s">
+        <v>318</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>293</v>
+        <v>319</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="H160" s="11" t="s">
-        <v>14</v>
+        <v>190</v>
+      </c>
+      <c r="H160" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="K160" s="1" t="s">
-        <v>294</v>
+        <v>320</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="7"/>
-      <c r="B161" s="10" t="s">
-        <v>295</v>
+      <c r="B161" s="11" t="s">
+        <v>321</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>296</v>
+        <v>322</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="H161" s="11" t="s">
-        <v>14</v>
+        <v>323</v>
+      </c>
+      <c r="H161" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J161" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G161)</f>
@@ -4970,138 +5175,138 @@
     </row>
     <row r="162" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="7"/>
-      <c r="B162" s="10" t="s">
-        <v>298</v>
+      <c r="B162" s="11" t="s">
+        <v>324</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>299</v>
+        <v>325</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="H162" s="11" t="s">
-        <v>14</v>
+        <v>326</v>
+      </c>
+      <c r="H162" s="10" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="7"/>
-      <c r="B163" s="10" t="s">
-        <v>272</v>
+      <c r="B163" s="11" t="s">
+        <v>298</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>273</v>
+        <v>299</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="H163" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="32" t="s">
-        <v>301</v>
-      </c>
-      <c r="B164" s="21"/>
-      <c r="C164" s="22" t="s">
-        <v>302</v>
-      </c>
-      <c r="D164" s="22"/>
-      <c r="E164" s="21"/>
-      <c r="F164" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="G164" s="21" t="s">
-        <v>301</v>
-      </c>
-      <c r="H164" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="I164" s="22"/>
-      <c r="J164" s="21" t="str">
+      <c r="A164" s="33" t="s">
+        <v>327</v>
+      </c>
+      <c r="B164" s="22"/>
+      <c r="C164" s="23" t="s">
+        <v>328</v>
+      </c>
+      <c r="D164" s="23"/>
+      <c r="E164" s="22"/>
+      <c r="F164" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="G164" s="22" t="s">
+        <v>327</v>
+      </c>
+      <c r="H164" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="I164" s="23"/>
+      <c r="J164" s="22" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G164)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#Person</v>
       </c>
-      <c r="K164" s="21"/>
-    </row>
-    <row r="165" s="30" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="23"/>
-      <c r="B165" s="10" t="s">
-        <v>303</v>
+      <c r="K164" s="22"/>
+    </row>
+    <row r="165" s="31" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="24"/>
+      <c r="B165" s="11" t="s">
+        <v>329</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="E165" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="F165" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="G165" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="H165" s="36" t="s">
+        <v>141</v>
+      </c>
+      <c r="E165" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="F165" s="31" t="s">
         <v>14</v>
+      </c>
+      <c r="G165" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="H165" s="37" t="s">
+        <v>15</v>
       </c>
       <c r="J165" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G165)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasIdentifier</v>
       </c>
     </row>
-    <row r="166" s="30" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="23"/>
-      <c r="B166" s="10" t="s">
-        <v>304</v>
+    <row r="166" s="31" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="24"/>
+      <c r="B166" s="11" t="s">
+        <v>330</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="E166" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="F166" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="G166" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="H166" s="36" t="s">
+        <v>331</v>
+      </c>
+      <c r="E166" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="F166" s="31" t="s">
         <v>14</v>
+      </c>
+      <c r="G166" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="H166" s="37" t="s">
+        <v>15</v>
       </c>
       <c r="J166" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G166)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasName</v>
       </c>
     </row>
-    <row r="167" s="30" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="23"/>
-      <c r="B167" s="10" t="s">
-        <v>306</v>
+    <row r="167" s="31" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="24"/>
+      <c r="B167" s="11" t="s">
+        <v>332</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="E167" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="F167" s="30" t="s">
-        <v>51</v>
-      </c>
-      <c r="G167" s="30" t="s">
-        <v>308</v>
-      </c>
-      <c r="H167" s="36" t="s">
-        <v>14</v>
+        <v>333</v>
+      </c>
+      <c r="E167" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="F167" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="G167" s="31" t="s">
+        <v>334</v>
+      </c>
+      <c r="H167" s="37" t="s">
+        <v>15</v>
       </c>
       <c r="J167" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G167)</f>
@@ -5109,25 +5314,25 @@
       </c>
     </row>
     <row r="168" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="23"/>
-      <c r="B168" s="10" t="s">
-        <v>309</v>
+      <c r="A168" s="24"/>
+      <c r="B168" s="11" t="s">
+        <v>335</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D168" s="30"/>
+        <v>336</v>
+      </c>
+      <c r="D168" s="31"/>
       <c r="E168" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="H168" s="11" t="s">
-        <v>14</v>
+        <v>337</v>
+      </c>
+      <c r="H168" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J168" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G168)</f>
@@ -5135,24 +5340,24 @@
       </c>
     </row>
     <row r="169" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="23"/>
-      <c r="B169" s="10" t="s">
-        <v>312</v>
+      <c r="A169" s="24"/>
+      <c r="B169" s="11" t="s">
+        <v>338</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="E169" s="24" t="s">
-        <v>312</v>
+        <v>339</v>
+      </c>
+      <c r="E169" s="25" t="s">
+        <v>338</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="H169" s="11" t="s">
-        <v>14</v>
+        <v>340</v>
+      </c>
+      <c r="H169" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J169" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G169)</f>
@@ -5160,24 +5365,24 @@
       </c>
     </row>
     <row r="170" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="23"/>
-      <c r="B170" s="10" t="s">
-        <v>315</v>
+      <c r="A170" s="24"/>
+      <c r="B170" s="11" t="s">
+        <v>341</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="E170" s="24" t="s">
-        <v>72</v>
+        <v>342</v>
+      </c>
+      <c r="E170" s="25" t="s">
+        <v>91</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="H170" s="11" t="s">
-        <v>14</v>
+        <v>343</v>
+      </c>
+      <c r="H170" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J170" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G170)</f>
@@ -5185,34 +5390,34 @@
       </c>
     </row>
     <row r="171" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="37" t="s">
-        <v>318</v>
-      </c>
-      <c r="B171" s="38"/>
-      <c r="C171" s="39" t="s">
-        <v>319</v>
-      </c>
-      <c r="D171" s="39"/>
-      <c r="E171" s="38"/>
-      <c r="F171" s="38"/>
-      <c r="G171" s="38"/>
-      <c r="H171" s="39"/>
-      <c r="I171" s="39"/>
-      <c r="J171" s="38" t="str">
+      <c r="A171" s="38" t="s">
+        <v>344</v>
+      </c>
+      <c r="B171" s="39"/>
+      <c r="C171" s="40" t="s">
+        <v>345</v>
+      </c>
+      <c r="D171" s="40"/>
+      <c r="E171" s="39"/>
+      <c r="F171" s="39"/>
+      <c r="G171" s="39"/>
+      <c r="H171" s="40"/>
+      <c r="I171" s="40"/>
+      <c r="J171" s="39" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G171)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
       </c>
-      <c r="K171" s="38" t="s">
-        <v>320</v>
+      <c r="K171" s="39" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="172" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="40"/>
+      <c r="A172" s="41"/>
       <c r="B172" s="14" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C172" s="13" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J172" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G172)</f>
@@ -5220,9 +5425,9 @@
       </c>
     </row>
     <row r="173" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="40"/>
+      <c r="A173" s="41"/>
       <c r="B173" s="14" t="s">
-        <v>321</v>
+        <v>347</v>
       </c>
       <c r="J173" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G173)</f>
@@ -5230,9 +5435,9 @@
       </c>
     </row>
     <row r="174" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="40"/>
+      <c r="A174" s="41"/>
       <c r="B174" s="14" t="s">
-        <v>322</v>
+        <v>348</v>
       </c>
       <c r="J174" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G174)</f>
@@ -5240,9 +5445,9 @@
       </c>
     </row>
     <row r="175" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="40"/>
+      <c r="A175" s="41"/>
       <c r="B175" s="14" t="s">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="J175" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G175)</f>
@@ -5250,9 +5455,9 @@
       </c>
     </row>
     <row r="176" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="40"/>
+      <c r="A176" s="41"/>
       <c r="B176" s="14" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="J176" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G176)</f>
@@ -5260,9 +5465,9 @@
       </c>
     </row>
     <row r="177" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="40"/>
+      <c r="A177" s="41"/>
       <c r="B177" s="14" t="s">
-        <v>323</v>
+        <v>349</v>
       </c>
       <c r="J177" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G177)</f>
@@ -5270,12 +5475,12 @@
       </c>
     </row>
     <row r="178" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="40"/>
+      <c r="A178" s="41"/>
       <c r="B178" s="14" t="s">
-        <v>324</v>
+        <v>350</v>
       </c>
       <c r="E178" s="13" t="s">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="J178" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G178)</f>
@@ -5283,37 +5488,37 @@
       </c>
     </row>
     <row r="179" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="37" t="s">
-        <v>326</v>
-      </c>
-      <c r="B179" s="38"/>
-      <c r="C179" s="39" t="s">
-        <v>327</v>
-      </c>
-      <c r="D179" s="39"/>
-      <c r="E179" s="38"/>
-      <c r="F179" s="38"/>
-      <c r="G179" s="38"/>
-      <c r="H179" s="39"/>
-      <c r="I179" s="39"/>
-      <c r="J179" s="38" t="str">
+      <c r="A179" s="38" t="s">
+        <v>352</v>
+      </c>
+      <c r="B179" s="39"/>
+      <c r="C179" s="40" t="s">
+        <v>353</v>
+      </c>
+      <c r="D179" s="40"/>
+      <c r="E179" s="39"/>
+      <c r="F179" s="39"/>
+      <c r="G179" s="39"/>
+      <c r="H179" s="40"/>
+      <c r="I179" s="40"/>
+      <c r="J179" s="39" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G179)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
       </c>
-      <c r="K179" s="38" t="s">
-        <v>175</v>
+      <c r="K179" s="39" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="40"/>
-      <c r="B180" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C180" s="11" t="s">
-        <v>122</v>
+      <c r="A180" s="41"/>
+      <c r="B180" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C180" s="10" t="s">
+        <v>141</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J180" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G180)</f>
@@ -5321,8 +5526,8 @@
       </c>
     </row>
     <row r="181" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="40"/>
-      <c r="B181" s="10"/>
+      <c r="A181" s="41"/>
+      <c r="B181" s="11"/>
       <c r="J181" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G181)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
@@ -5379,61 +5584,61 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="11" style="1" width="11.53"/>
   </cols>
   <sheetData>
-    <row r="1" s="24" customFormat="true" ht="36.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="C1" s="24" t="s">
+    <row r="1" s="25" customFormat="true" ht="36.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="F1" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="H1" s="24" t="s">
+      <c r="C1" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="I1" s="41" t="s">
+      <c r="F1" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="J1" s="24" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="2" s="35" customFormat="true" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="35" t="s">
-        <v>329</v>
-      </c>
-      <c r="B2" s="35" t="s">
-        <v>330</v>
-      </c>
-      <c r="C2" s="35" t="s">
-        <v>331</v>
-      </c>
-      <c r="D2" s="42" t="n">
+      <c r="G1" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="I1" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1" s="25" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="2" s="36" customFormat="true" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="36" t="s">
+        <v>355</v>
+      </c>
+      <c r="B2" s="36" t="s">
+        <v>356</v>
+      </c>
+      <c r="C2" s="36" t="s">
+        <v>357</v>
+      </c>
+      <c r="D2" s="43" t="n">
         <v>45644</v>
       </c>
-      <c r="E2" s="42" t="n">
+      <c r="E2" s="43" t="n">
         <v>45644</v>
       </c>
-      <c r="F2" s="35" t="s">
-        <v>332</v>
-      </c>
-      <c r="G2" s="35" t="n">
+      <c r="F2" s="36" t="s">
+        <v>358</v>
+      </c>
+      <c r="G2" s="36" t="n">
         <v>3.2</v>
       </c>
-      <c r="H2" s="35" t="n">
+      <c r="H2" s="36" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -5457,43 +5662,43 @@
   <dimension ref="A1:I1"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="30" width="20.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="30" width="14.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="30" width="19.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="30" width="14.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="30" width="13.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="30" width="17.04"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="30" width="18.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="30" width="21.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="31" width="20.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="31" width="14.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="31" width="19.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="31" width="14.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="31" width="13.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="31" width="17.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="31" width="18.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="31" width="21.79"/>
   </cols>
   <sheetData>
-    <row r="1" s="41" customFormat="true" ht="36.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="41" t="s">
-        <v>57</v>
-      </c>
-      <c r="B1" s="41" t="s">
-        <v>60</v>
-      </c>
-      <c r="C1" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="D1" s="41" t="s">
-        <v>64</v>
-      </c>
-      <c r="E1" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="F1" s="41" t="s">
-        <v>70</v>
-      </c>
-      <c r="G1" s="41" t="s">
-        <v>74</v>
-      </c>
-      <c r="H1" s="41" t="s">
+    <row r="1" s="42" customFormat="true" ht="36.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="B1" s="42" t="s">
         <v>77</v>
       </c>
-      <c r="I1" s="41" t="s">
-        <v>81</v>
+      <c r="C1" s="42" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1" s="42" t="s">
+        <v>83</v>
+      </c>
+      <c r="E1" s="42" t="s">
+        <v>86</v>
+      </c>
+      <c r="F1" s="42" t="s">
+        <v>89</v>
+      </c>
+      <c r="G1" s="42" t="s">
+        <v>93</v>
+      </c>
+      <c r="H1" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1" s="42" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -5515,34 +5720,34 @@
   <dimension ref="A1:F1"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="30" width="24.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="30" width="14.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="30" width="19.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="30" width="14.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="30" width="13.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="30" width="17.04"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="30" width="18.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="30" width="21.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="31" width="24.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="31" width="14.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="31" width="19.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="31" width="14.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="31" width="13.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="31" width="17.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="31" width="18.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="31" width="21.79"/>
   </cols>
   <sheetData>
-    <row r="1" s="41" customFormat="true" ht="36.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="41" t="s">
-        <v>303</v>
-      </c>
-      <c r="B1" s="41" t="s">
-        <v>304</v>
-      </c>
-      <c r="C1" s="41" t="s">
-        <v>306</v>
-      </c>
-      <c r="D1" s="41" t="s">
-        <v>309</v>
-      </c>
-      <c r="E1" s="41" t="s">
-        <v>312</v>
-      </c>
-      <c r="F1" s="41" t="s">
-        <v>315</v>
+    <row r="1" s="42" customFormat="true" ht="36.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="42" t="s">
+        <v>329</v>
+      </c>
+      <c r="B1" s="42" t="s">
+        <v>330</v>
+      </c>
+      <c r="C1" s="42" t="s">
+        <v>332</v>
+      </c>
+      <c r="D1" s="42" t="s">
+        <v>335</v>
+      </c>
+      <c r="E1" s="42" t="s">
+        <v>338</v>
+      </c>
+      <c r="F1" s="42" t="s">
+        <v>341</v>
       </c>
     </row>
   </sheetData>
@@ -5564,34 +5769,34 @@
   <dimension ref="A1:F1"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="30" width="20.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="30" width="14.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="30" width="19.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="30" width="20.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="30" width="13.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="30" width="17.04"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="30" width="18.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="30" width="21.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="31" width="20.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="31" width="14.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="31" width="19.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="31" width="20.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="31" width="13.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="31" width="17.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="31" width="18.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="31" width="21.79"/>
   </cols>
   <sheetData>
-    <row r="1" s="41" customFormat="true" ht="36.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="43" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" s="43" t="s">
-        <v>157</v>
-      </c>
-      <c r="C1" s="43" t="s">
-        <v>161</v>
-      </c>
-      <c r="D1" s="43" t="s">
-        <v>163</v>
-      </c>
-      <c r="E1" s="43" t="s">
-        <v>165</v>
-      </c>
-      <c r="F1" s="43" t="s">
-        <v>168</v>
+    <row r="1" s="42" customFormat="true" ht="36.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="44" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="44" t="s">
+        <v>176</v>
+      </c>
+      <c r="C1" s="44" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1" s="44" t="s">
+        <v>182</v>
+      </c>
+      <c r="E1" s="44" t="s">
+        <v>184</v>
+      </c>
+      <c r="F1" s="44" t="s">
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -5613,46 +5818,46 @@
   <dimension ref="A1:J1"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="30" width="20.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="30" width="14.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="30" width="19.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="30" width="14.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="30" width="13.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="30" width="17.04"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="30" width="18.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="30" width="21.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="31" width="20.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="31" width="14.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="31" width="19.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="31" width="14.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="31" width="13.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="31" width="17.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="31" width="18.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="31" width="21.79"/>
   </cols>
   <sheetData>
-    <row r="1" s="41" customFormat="true" ht="36.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" s="24" t="s">
-        <v>86</v>
-      </c>
-      <c r="C1" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="D1" s="24" t="s">
-        <v>92</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="F1" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="H1" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="I1" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="J1" s="24" t="s">
+    <row r="1" s="42" customFormat="true" ht="36.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="D1" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="E1" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="F1" s="25" t="s">
         <v>119</v>
+      </c>
+      <c r="G1" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="H1" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="I1" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="J1" s="25" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -5674,52 +5879,52 @@
   <dimension ref="A1:L1"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="30" width="20.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="30" width="14.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="30" width="19.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="30" width="14.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="30" width="13.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="30" width="17.04"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="30" width="18.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="30" width="21.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="31" width="20.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="31" width="14.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="31" width="19.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="31" width="14.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="31" width="13.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="31" width="17.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="31" width="18.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="31" width="21.79"/>
   </cols>
   <sheetData>
-    <row r="1" s="41" customFormat="true" ht="36.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="43" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" s="43" t="s">
-        <v>123</v>
-      </c>
-      <c r="C1" s="43" t="s">
-        <v>125</v>
-      </c>
-      <c r="D1" s="43" t="s">
-        <v>88</v>
-      </c>
-      <c r="E1" s="43" t="s">
-        <v>92</v>
-      </c>
-      <c r="F1" s="43" t="s">
-        <v>128</v>
-      </c>
-      <c r="G1" s="43" t="s">
-        <v>131</v>
-      </c>
-      <c r="H1" s="43" t="s">
-        <v>133</v>
-      </c>
-      <c r="I1" s="43" t="s">
-        <v>135</v>
-      </c>
-      <c r="J1" s="43" t="s">
-        <v>137</v>
-      </c>
-      <c r="K1" s="43" t="s">
-        <v>139</v>
-      </c>
-      <c r="L1" s="43" t="s">
-        <v>141</v>
+    <row r="1" s="42" customFormat="true" ht="36.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="44" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="44" t="s">
+        <v>142</v>
+      </c>
+      <c r="C1" s="44" t="s">
+        <v>144</v>
+      </c>
+      <c r="D1" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" s="44" t="s">
+        <v>111</v>
+      </c>
+      <c r="F1" s="44" t="s">
+        <v>147</v>
+      </c>
+      <c r="G1" s="44" t="s">
+        <v>150</v>
+      </c>
+      <c r="H1" s="44" t="s">
+        <v>152</v>
+      </c>
+      <c r="I1" s="44" t="s">
+        <v>154</v>
+      </c>
+      <c r="J1" s="44" t="s">
+        <v>156</v>
+      </c>
+      <c r="K1" s="44" t="s">
+        <v>158</v>
+      </c>
+      <c r="L1" s="44" t="s">
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -5741,31 +5946,31 @@
   <dimension ref="A1:E1"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="30" width="20.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="30" width="14.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="30" width="19.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="30" width="14.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="30" width="13.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="30" width="17.04"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="30" width="18.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="30" width="21.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="31" width="20.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="31" width="14.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="31" width="19.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="31" width="14.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="31" width="13.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="31" width="17.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="31" width="18.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="31" width="21.79"/>
   </cols>
   <sheetData>
-    <row r="1" s="41" customFormat="true" ht="36.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="43" t="s">
-        <v>144</v>
-      </c>
-      <c r="B1" s="43" t="s">
-        <v>145</v>
-      </c>
-      <c r="C1" s="43" t="s">
-        <v>147</v>
-      </c>
-      <c r="D1" s="43" t="s">
-        <v>149</v>
-      </c>
-      <c r="E1" s="43" t="s">
-        <v>152</v>
+    <row r="1" s="42" customFormat="true" ht="36.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="44" t="s">
+        <v>163</v>
+      </c>
+      <c r="B1" s="44" t="s">
+        <v>164</v>
+      </c>
+      <c r="C1" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1" s="44" t="s">
+        <v>168</v>
+      </c>
+      <c r="E1" s="44" t="s">
+        <v>171</v>
       </c>
     </row>
   </sheetData>

--- a/metadata/MIAFPE/MIAFPE_template_v1.1.xlsx
+++ b/metadata/MIAFPE/MIAFPE_template_v1.1.xlsx
@@ -18,6 +18,15 @@
     <sheet name="ExperimentalDesign" sheetId="8" state="visible" r:id="rId10"/>
     <sheet name="Observation" sheetId="9" state="visible" r:id="rId11"/>
     <sheet name="ObservationUnit" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="System" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="Platform" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="Sensor" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="ObservedVariable" sheetId="14" state="visible" r:id="rId16"/>
+    <sheet name="Factor" sheetId="15" state="visible" r:id="rId17"/>
+    <sheet name="Sample" sheetId="16" state="visible" r:id="rId18"/>
+    <sheet name="BiologicalMaterial" sheetId="17" state="visible" r:id="rId19"/>
+    <sheet name="Event" sheetId="18" state="visible" r:id="rId20"/>
+    <sheet name="Environment" sheetId="19" state="visible" r:id="rId21"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -29,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="401">
   <si>
     <t xml:space="preserve">Sheet Name</t>
   </si>
@@ -856,6 +865,9 @@
     <t xml:space="preserve">Spatial Distribution</t>
   </si>
   <si>
+    <t xml:space="preserve">Type and value of a spatial coordinate (georeference or relative) or level of observation (plot 45, subblock 7, block 2) provided as a key-value pair of the form type:value. Levels of observation must be consistent with those listed in the Study section.</t>
+  </si>
+  <si>
     <t xml:space="preserve">hasSpatialDistribution</t>
   </si>
   <si>
@@ -865,6 +877,9 @@
     <t xml:space="preserve">Spatial Distribution Type</t>
   </si>
   <si>
+    <t xml:space="preserve">Type of Spatial Detribution.</t>
+  </si>
+  <si>
     <t xml:space="preserve">hasSpatialDistributionType</t>
   </si>
   <si>
@@ -880,6 +895,9 @@
     <t xml:space="preserve">Experimental Factor</t>
   </si>
   <si>
+    <t xml:space="preserve">List of Experimental Factor Identifier (semi-colon separated) </t>
+  </si>
+  <si>
     <t xml:space="preserve">Observed Variable</t>
   </si>
   <si>
@@ -898,16 +916,133 @@
     <t xml:space="preserve">Variable Name</t>
   </si>
   <si>
+    <t xml:space="preserve">Name of the Variable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anthesis computed in growing degree days</t>
+  </si>
+  <si>
     <t xml:space="preserve">Variable Accession Number</t>
   </si>
   <si>
+    <t xml:space="preserve">URI of an Ontology Term (for example Crop Ontology).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO_322:0000794</t>
+  </si>
+  <si>
     <t xml:space="preserve">Trait</t>
   </si>
   <si>
+    <t xml:space="preserve">Name of the (plant or environmental) trait under observation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anthesis time;  Reproductive growth time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trait Entity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entity (part of the plant, whole plant, group of plant e.g. canopy) on which the trait has been measured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leaf</t>
+  </si>
+  <si>
     <t xml:space="preserve">Trait Entity Accession Number</t>
   </si>
   <si>
+    <t xml:space="preserve">Accession number of the trait entity in a suitable controlled vocabulary (Plant Ontology).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://purl.obolibrary.org/obo/PO_0025034</t>
+  </si>
+  <si>
     <t xml:space="preserve">Trait Characteristics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Characteristic measured. It can be a morphological characteristic (size, volume, surface), a molecular characteristic (sugar concentration), etc...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trait Characteristic Accession number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://purl.obolibrary.org/obo/PATO_0001323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trait accession number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accession number of the trait in a suitable controlled vocabulary (Crop Ontology, Trait Ontology).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO_322:0000030; TO:0000366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name of the method of observation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Growing degree days to anthesis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Method accession number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accession number of the method in a suitable controlled vocabulary (Crop Ontology, Trait Ontology).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO_322:0000189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Method description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Textual description of the method, which may extend a method defined in an external reference with specific parameters, e.g. growth stage, inoculation precise organ (leaf number)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days to anthesis for male flowering was measured in thermal time (GDD: growing degree-days) according to Ritchie J, NeSmith D (1991;Temperature and crop development. Modeling plant and soil systems American Society of Agronomy Madison, Wisconsin USA) with TBASE=8°C and T0=30°C. ; Plant height was measured at 5 years with a ruler, one year after Botritis inoculation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference associated to the method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URI/DOI of reference describing the method.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.2134/agronmonogr31.c2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name of the scale associated with the variable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">°C day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scale accession number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accession number of the scale in a suitable controlled vocabulary (Crop Ontology).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO_322:0000510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time scale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name of the scale or unit of time with which observations of this type were recorded in the data file (for time series studies).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Growing degree day (GDD); Date/Time</t>
   </si>
   <si>
     <t xml:space="preserve">The object of a study is to ascertain the impact of one or more factors on the biological material. Thus, a factor is, by definition a condition that varies between observation units, which may be biotic (pest, disease interaction) or abiotic (treatment and cultural practice) in nature. Depending on the level of the data, an experimental factor can be either  "what is the factor applied to the plant" (i.e. Unwatered), or the "environmental characterisation" (i.e. if no rain on unwatered plant : Drought ;  if rain on unwatered plant: Irrigated) </t>
@@ -1112,10 +1247,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="General"/>
-    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -1161,11 +1295,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b val="true"/>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1194,6 +1323,11 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -1317,7 +1451,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1378,10 +1512,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1390,7 +1520,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1398,7 +1528,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1418,11 +1548,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1434,7 +1564,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1450,7 +1580,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1458,7 +1588,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1486,15 +1624,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1681,7 +1819,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M181"/>
+  <dimension ref="A1:M189"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21.21"/>
@@ -1698,7 +1836,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="13" style="1" width="11.53"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="30.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1736,7 +1874,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="47.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
@@ -1768,7 +1906,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="36.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7"/>
       <c r="B3" s="8" t="s">
         <v>17</v>
@@ -1804,7 +1942,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="59.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7"/>
       <c r="B4" s="11" t="s">
         <v>23</v>
@@ -1840,7 +1978,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="105.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7"/>
       <c r="B5" s="11" t="s">
         <v>29</v>
@@ -1876,7 +2014,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="47.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7"/>
       <c r="B6" s="11" t="s">
         <v>35</v>
@@ -1912,7 +2050,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="47.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7"/>
       <c r="B7" s="11" t="s">
         <v>40</v>
@@ -1948,7 +2086,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="36.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7"/>
       <c r="B8" s="11" t="s">
         <v>44</v>
@@ -1984,7 +2122,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="34.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7"/>
       <c r="B9" s="14" t="s">
         <v>49</v>
@@ -2043,7 +2181,7 @@
       </c>
       <c r="K10" s="12"/>
     </row>
-    <row r="11" customFormat="false" ht="47.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7"/>
       <c r="B11" s="14" t="s">
         <v>57</v>
@@ -2051,7 +2189,7 @@
       <c r="C11" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="10" t="s">
         <v>59</v>
       </c>
       <c r="E11" s="1" t="s">
@@ -2081,71 +2219,71 @@
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7"/>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="D12" s="17"/>
-      <c r="E12" s="18" t="s">
+      <c r="D12" s="16"/>
+      <c r="E12" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="F12" s="17" t="s">
+      <c r="F12" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="G12" s="19" t="s">
+      <c r="G12" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="H12" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="I12" s="17" t="str">
+      <c r="H12" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="16" t="str">
         <f aca="false">_xlfn.CONCAT(H12, G12)</f>
         <v>http://purl.org/ppeo/ppeo.owl#hasDataFile</v>
       </c>
-      <c r="J12" s="20" t="str">
+      <c r="J12" s="19" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G12)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasDataFile</v>
       </c>
-      <c r="K12" s="20"/>
-    </row>
-    <row r="13" customFormat="false" ht="36.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="21" t="s">
+      <c r="K12" s="19"/>
+    </row>
+    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="B13" s="22"/>
-      <c r="C13" s="23" t="s">
+      <c r="B13" s="21"/>
+      <c r="C13" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="D13" s="23"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22" t="s">
+      <c r="D13" s="22"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="G13" s="22" t="s">
+      <c r="G13" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="H13" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="I13" s="23" t="str">
+      <c r="H13" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" s="22" t="str">
         <f aca="false">_xlfn.CONCAT(H13, LOWER(G13))</f>
         <v>http://purl.org/ppeo/ppeo.owl#study</v>
       </c>
-      <c r="J13" s="22" t="str">
+      <c r="J13" s="21" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G13)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#Study</v>
       </c>
-      <c r="K13" s="23" t="s">
+      <c r="K13" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="L13" s="23" t="s">
+      <c r="L13" s="22" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="24"/>
+      <c r="A14" s="23"/>
       <c r="B14" s="8" t="s">
         <v>73</v>
       </c>
@@ -2181,7 +2319,7 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="24"/>
+      <c r="A15" s="23"/>
       <c r="B15" s="11" t="s">
         <v>77</v>
       </c>
@@ -2214,7 +2352,7 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="24"/>
+      <c r="A16" s="23"/>
       <c r="B16" s="11" t="s">
         <v>80</v>
       </c>
@@ -2247,7 +2385,7 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="24"/>
+      <c r="A17" s="23"/>
       <c r="B17" s="11" t="s">
         <v>83</v>
       </c>
@@ -2277,7 +2415,7 @@
       <c r="K17" s="12"/>
     </row>
     <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="24"/>
+      <c r="A18" s="23"/>
       <c r="B18" s="11" t="s">
         <v>86</v>
       </c>
@@ -2307,14 +2445,14 @@
       <c r="K18" s="12"/>
     </row>
     <row r="19" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="24"/>
+      <c r="A19" s="23"/>
       <c r="B19" s="11" t="s">
         <v>89</v>
       </c>
       <c r="C19" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="E19" s="25" t="s">
+      <c r="E19" s="24" t="s">
         <v>91</v>
       </c>
       <c r="F19" s="1" t="s">
@@ -2337,14 +2475,14 @@
       <c r="K19" s="12"/>
     </row>
     <row r="20" customFormat="false" ht="34.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="24"/>
+      <c r="A20" s="23"/>
       <c r="B20" s="14" t="s">
         <v>93</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E20" s="25" t="s">
+      <c r="E20" s="24" t="s">
         <v>93</v>
       </c>
       <c r="F20" s="1" t="s">
@@ -2367,14 +2505,14 @@
       <c r="K20" s="12"/>
     </row>
     <row r="21" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="24"/>
+      <c r="A21" s="23"/>
       <c r="B21" s="14" t="s">
         <v>96</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E21" s="25" t="s">
+      <c r="E21" s="24" t="s">
         <v>98</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -2397,38 +2535,38 @@
       <c r="K21" s="12"/>
     </row>
     <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="24"/>
-      <c r="B22" s="16" t="s">
+      <c r="A22" s="23"/>
+      <c r="B22" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="C22" s="17" t="s">
+      <c r="C22" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="D22" s="17"/>
-      <c r="E22" s="18" t="s">
+      <c r="D22" s="16"/>
+      <c r="E22" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="F22" s="17" t="s">
+      <c r="F22" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="G22" s="19" t="s">
+      <c r="G22" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="H22" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="I22" s="17" t="str">
+      <c r="H22" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="I22" s="16" t="str">
         <f aca="false">_xlfn.CONCAT(H22, G22)</f>
         <v>http://purl.org/ppeo/ppeo.owl#hasDataFile</v>
       </c>
-      <c r="J22" s="20" t="str">
+      <c r="J22" s="19" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G22)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasDataFile</v>
       </c>
-      <c r="K22" s="20"/>
-    </row>
-    <row r="23" customFormat="false" ht="36.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="26" t="s">
+      <c r="K22" s="19"/>
+    </row>
+    <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="25" t="s">
         <v>93</v>
       </c>
       <c r="B23" s="4"/>
@@ -2520,34 +2658,34 @@
     </row>
     <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7"/>
-      <c r="B26" s="27" t="s">
+      <c r="B26" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="C26" s="28" t="s">
+      <c r="C26" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="D26" s="28"/>
-      <c r="E26" s="29" t="s">
+      <c r="D26" s="27"/>
+      <c r="E26" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="F26" s="28" t="s">
+      <c r="F26" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="G26" s="28" t="s">
+      <c r="G26" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="H26" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="I26" s="28" t="str">
+      <c r="H26" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="I26" s="27" t="str">
         <f aca="false">_xlfn.CONCAT(H26, G26)</f>
         <v>http://purl.org/ppeo/ppeo.owl#hasName</v>
       </c>
-      <c r="J26" s="28" t="str">
+      <c r="J26" s="27" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G26)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasName</v>
       </c>
-      <c r="K26" s="30"/>
+      <c r="K26" s="29"/>
       <c r="L26" s="1" t="s">
         <v>109</v>
       </c>
@@ -2557,34 +2695,34 @@
     </row>
     <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7"/>
-      <c r="B27" s="27" t="s">
+      <c r="B27" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="C27" s="28" t="s">
+      <c r="C27" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="D27" s="28"/>
-      <c r="E27" s="28" t="s">
+      <c r="D27" s="27"/>
+      <c r="E27" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="F27" s="28" t="s">
+      <c r="F27" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="G27" s="28" t="s">
+      <c r="G27" s="27" t="s">
         <v>113</v>
       </c>
-      <c r="H27" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="I27" s="28" t="str">
+      <c r="H27" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="I27" s="27" t="str">
         <f aca="false">_xlfn.CONCAT(H27, G27)</f>
         <v>http://purl.org/ppeo/ppeo.owl#hasCountryCode</v>
       </c>
-      <c r="J27" s="28" t="str">
+      <c r="J27" s="27" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G27)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasCountryCode</v>
       </c>
-      <c r="K27" s="30"/>
+      <c r="K27" s="29"/>
     </row>
     <row r="28" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7"/>
@@ -2684,34 +2822,34 @@
     </row>
     <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7"/>
-      <c r="B31" s="27" t="s">
+      <c r="B31" s="26" t="s">
         <v>127</v>
       </c>
-      <c r="C31" s="28" t="s">
+      <c r="C31" s="27" t="s">
         <v>128</v>
       </c>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28" t="s">
+      <c r="D31" s="27"/>
+      <c r="E31" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="F31" s="28" t="s">
+      <c r="F31" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="G31" s="28" t="s">
+      <c r="G31" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="H31" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="I31" s="28" t="str">
+      <c r="H31" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="I31" s="27" t="str">
         <f aca="false">_xlfn.CONCAT(H31,G31)</f>
         <v>http://purl.org/ppeo/ppeo.owl#hasDescription</v>
       </c>
-      <c r="J31" s="28" t="str">
+      <c r="J31" s="27" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G31)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasDescription</v>
       </c>
-      <c r="K31" s="28" t="s">
+      <c r="K31" s="27" t="s">
         <v>129</v>
       </c>
       <c r="L31" s="1" t="s">
@@ -2721,36 +2859,36 @@
         <v>131</v>
       </c>
     </row>
-    <row r="32" s="31" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" s="30" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7"/>
-      <c r="B32" s="27" t="s">
+      <c r="B32" s="26" t="s">
         <v>132</v>
       </c>
-      <c r="C32" s="28" t="s">
+      <c r="C32" s="27" t="s">
         <v>133</v>
       </c>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28" t="s">
+      <c r="D32" s="27"/>
+      <c r="E32" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="F32" s="28" t="s">
+      <c r="F32" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="G32" s="28" t="s">
+      <c r="G32" s="27" t="s">
         <v>134</v>
       </c>
-      <c r="H32" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="I32" s="28" t="str">
+      <c r="H32" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="I32" s="27" t="str">
         <f aca="false">_xlfn.CONCAT(H32,G32)</f>
         <v>http://purl.org/ppeo/ppeo.owl#hasGrowthFacilityType</v>
       </c>
-      <c r="J32" s="28" t="str">
+      <c r="J32" s="27" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G32)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasGrowthFacilityType</v>
       </c>
-      <c r="K32" s="28" t="s">
+      <c r="K32" s="27" t="s">
         <v>129</v>
       </c>
       <c r="L32" s="1"/>
@@ -2758,95 +2896,95 @@
     </row>
     <row r="33" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7"/>
-      <c r="B33" s="27" t="s">
+      <c r="B33" s="26" t="s">
         <v>135</v>
       </c>
-      <c r="C33" s="28" t="s">
+      <c r="C33" s="27" t="s">
         <v>136</v>
       </c>
-      <c r="D33" s="28"/>
-      <c r="E33" s="28" t="s">
+      <c r="D33" s="27"/>
+      <c r="E33" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="F33" s="28" t="s">
+      <c r="F33" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="G33" s="28" t="s">
+      <c r="G33" s="27" t="s">
         <v>137</v>
       </c>
-      <c r="H33" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="I33" s="28" t="str">
+      <c r="H33" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="I33" s="27" t="str">
         <f aca="false">_xlfn.CONCAT(H33,G33)</f>
         <v>http://purl.org/ppeo/ppeo.owl#hasExternalIdentifier</v>
       </c>
-      <c r="J33" s="28" t="str">
+      <c r="J33" s="27" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G33)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasExternalIdentifier</v>
       </c>
-      <c r="K33" s="28"/>
+      <c r="K33" s="27"/>
     </row>
     <row r="34" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7"/>
-      <c r="B34" s="32" t="s">
+      <c r="B34" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="C34" s="20" t="s">
+      <c r="C34" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="D34" s="20"/>
-      <c r="E34" s="18" t="s">
+      <c r="D34" s="19"/>
+      <c r="E34" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="F34" s="20" t="s">
+      <c r="F34" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="G34" s="20" t="s">
+      <c r="G34" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="H34" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="I34" s="17" t="str">
+      <c r="H34" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="I34" s="16" t="str">
         <f aca="false">_xlfn.CONCAT(H34, G34)</f>
         <v>http://purl.org/ppeo/ppeo.owl#hasDataFile</v>
       </c>
-      <c r="J34" s="20" t="str">
+      <c r="J34" s="19" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G34)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasDataFile</v>
       </c>
-      <c r="K34" s="20"/>
+      <c r="K34" s="19"/>
     </row>
     <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="33" t="s">
+      <c r="A35" s="32" t="s">
         <v>91</v>
       </c>
-      <c r="B35" s="22"/>
-      <c r="C35" s="23" t="s">
+      <c r="B35" s="21"/>
+      <c r="C35" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="D35" s="23"/>
-      <c r="E35" s="22"/>
-      <c r="F35" s="22"/>
-      <c r="G35" s="22" t="s">
+      <c r="D35" s="22"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="H35" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="I35" s="23" t="str">
+      <c r="H35" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="I35" s="22" t="str">
         <f aca="false">_xlfn.CONCAT(H35, LOWER(G35))</f>
         <v>http://purl.org/ppeo/ppeo.owl#institution</v>
       </c>
-      <c r="J35" s="22" t="str">
+      <c r="J35" s="21" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G35)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#Institution</v>
       </c>
-      <c r="K35" s="22"/>
+      <c r="K35" s="21"/>
     </row>
     <row r="36" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="24"/>
+      <c r="A36" s="23"/>
       <c r="B36" s="11" t="s">
         <v>20</v>
       </c>
@@ -2878,7 +3016,7 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="24"/>
+      <c r="A37" s="23"/>
       <c r="B37" s="11" t="s">
         <v>142</v>
       </c>
@@ -2907,7 +3045,7 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="24"/>
+      <c r="A38" s="23"/>
       <c r="B38" s="11" t="s">
         <v>144</v>
       </c>
@@ -2936,72 +3074,72 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="24"/>
-      <c r="B39" s="27" t="s">
+      <c r="A39" s="23"/>
+      <c r="B39" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="C39" s="28" t="s">
+      <c r="C39" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="D39" s="28"/>
-      <c r="E39" s="28" t="s">
+      <c r="D39" s="27"/>
+      <c r="E39" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="F39" s="28" t="s">
+      <c r="F39" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="G39" s="28" t="s">
+      <c r="G39" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="H39" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="I39" s="28" t="str">
+      <c r="H39" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="I39" s="27" t="str">
         <f aca="false">_xlfn.CONCAT(H39,G39)</f>
         <v>http://purl.org/ppeo/ppeo.owl#hasName</v>
       </c>
-      <c r="J39" s="28" t="str">
+      <c r="J39" s="27" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G39)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasName</v>
       </c>
-      <c r="K39" s="28"/>
+      <c r="K39" s="27"/>
       <c r="L39" s="1" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="24"/>
-      <c r="B40" s="27" t="s">
+      <c r="A40" s="23"/>
+      <c r="B40" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="C40" s="28" t="s">
+      <c r="C40" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="D40" s="28"/>
-      <c r="E40" s="28" t="s">
+      <c r="D40" s="27"/>
+      <c r="E40" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="F40" s="28" t="s">
+      <c r="F40" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="G40" s="28" t="s">
+      <c r="G40" s="27" t="s">
         <v>113</v>
       </c>
-      <c r="H40" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="I40" s="28" t="str">
+      <c r="H40" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="I40" s="27" t="str">
         <f aca="false">_xlfn.CONCAT(H40,G40)</f>
         <v>http://purl.org/ppeo/ppeo.owl#hasCountryCode</v>
       </c>
-      <c r="J40" s="28" t="str">
+      <c r="J40" s="27" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G40)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasCountryCode</v>
       </c>
-      <c r="K40" s="28"/>
+      <c r="K40" s="27"/>
     </row>
     <row r="41" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="24"/>
+      <c r="A41" s="23"/>
       <c r="B41" s="11" t="s">
         <v>147</v>
       </c>
@@ -3030,7 +3168,7 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="24"/>
+      <c r="A42" s="23"/>
       <c r="B42" s="11" t="s">
         <v>150</v>
       </c>
@@ -3052,7 +3190,7 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="24"/>
+      <c r="A43" s="23"/>
       <c r="B43" s="11" t="s">
         <v>152</v>
       </c>
@@ -3074,7 +3212,7 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="24"/>
+      <c r="A44" s="23"/>
       <c r="B44" s="11" t="s">
         <v>154</v>
       </c>
@@ -3096,7 +3234,7 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="24"/>
+      <c r="A45" s="23"/>
       <c r="B45" s="11" t="s">
         <v>156</v>
       </c>
@@ -3118,7 +3256,7 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="24"/>
+      <c r="A46" s="23"/>
       <c r="B46" s="11" t="s">
         <v>158</v>
       </c>
@@ -3140,7 +3278,7 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="24"/>
+      <c r="A47" s="23"/>
       <c r="B47" s="11" t="s">
         <v>160</v>
       </c>
@@ -3168,8 +3306,8 @@
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasExternalIdentifier</v>
       </c>
     </row>
-    <row r="48" s="31" customFormat="true" ht="45.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="26" t="s">
+    <row r="48" s="30" customFormat="true" ht="45.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="25" t="s">
         <v>96</v>
       </c>
       <c r="B48" s="4"/>
@@ -3261,7 +3399,7 @@
       <c r="C51" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="E51" s="25" t="s">
+      <c r="E51" s="24" t="s">
         <v>65</v>
       </c>
       <c r="F51" s="1" t="s">
@@ -3341,34 +3479,34 @@
       </c>
     </row>
     <row r="54" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="33" t="s">
+      <c r="A54" s="32" t="s">
         <v>174</v>
       </c>
-      <c r="B54" s="22"/>
-      <c r="C54" s="23" t="s">
+      <c r="B54" s="21"/>
+      <c r="C54" s="22" t="s">
         <v>175</v>
       </c>
-      <c r="D54" s="23"/>
-      <c r="E54" s="22"/>
-      <c r="F54" s="22"/>
-      <c r="G54" s="22" t="s">
+      <c r="D54" s="22"/>
+      <c r="E54" s="21"/>
+      <c r="F54" s="21"/>
+      <c r="G54" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="H54" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="I54" s="23" t="str">
+      <c r="H54" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="I54" s="22" t="str">
         <f aca="false">_xlfn.CONCAT(H54,"data_file")</f>
         <v>http://purl.org/ppeo/ppeo.owl#data_file</v>
       </c>
-      <c r="J54" s="22" t="str">
+      <c r="J54" s="21" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G54)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#DataFile</v>
       </c>
-      <c r="K54" s="22"/>
+      <c r="K54" s="21"/>
     </row>
     <row r="55" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="34"/>
+      <c r="A55" s="33"/>
       <c r="B55" s="14" t="s">
         <v>20</v>
       </c>
@@ -3397,7 +3535,7 @@
       </c>
     </row>
     <row r="56" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="34"/>
+      <c r="A56" s="33"/>
       <c r="B56" s="14" t="s">
         <v>176</v>
       </c>
@@ -3426,7 +3564,7 @@
       </c>
     </row>
     <row r="57" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="34"/>
+      <c r="A57" s="33"/>
       <c r="B57" s="14" t="s">
         <v>180</v>
       </c>
@@ -3455,7 +3593,7 @@
       </c>
     </row>
     <row r="58" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="34"/>
+      <c r="A58" s="33"/>
       <c r="B58" s="14" t="s">
         <v>182</v>
       </c>
@@ -3484,7 +3622,7 @@
       </c>
     </row>
     <row r="59" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="34"/>
+      <c r="A59" s="33"/>
       <c r="B59" s="14" t="s">
         <v>184</v>
       </c>
@@ -3513,14 +3651,14 @@
       </c>
     </row>
     <row r="60" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="34"/>
+      <c r="A60" s="33"/>
       <c r="B60" s="14" t="s">
         <v>187</v>
       </c>
       <c r="C60" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="E60" s="35" t="s">
+      <c r="E60" s="34" t="s">
         <v>189</v>
       </c>
       <c r="F60" s="13" t="s">
@@ -3542,7 +3680,7 @@
       </c>
     </row>
     <row r="61" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="26" t="s">
+      <c r="A61" s="25" t="s">
         <v>191</v>
       </c>
       <c r="B61" s="4"/>
@@ -3575,10 +3713,10 @@
       <c r="B62" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C62" s="36" t="s">
+      <c r="C62" s="35" t="s">
         <v>141</v>
       </c>
-      <c r="D62" s="36"/>
+      <c r="D62" s="35"/>
       <c r="E62" s="1" t="s">
         <v>20</v>
       </c>
@@ -3605,8 +3743,8 @@
       <c r="B63" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="C63" s="36"/>
-      <c r="D63" s="36"/>
+      <c r="C63" s="35"/>
+      <c r="D63" s="35"/>
       <c r="G63" s="13" t="s">
         <v>27</v>
       </c>
@@ -3627,8 +3765,8 @@
       <c r="B64" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="C64" s="36"/>
-      <c r="D64" s="36"/>
+      <c r="C64" s="35"/>
+      <c r="D64" s="35"/>
       <c r="G64" s="13" t="s">
         <v>33</v>
       </c>
@@ -3649,11 +3787,11 @@
       <c r="B65" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="C65" s="36" t="s">
+      <c r="C65" s="35" t="s">
         <v>198</v>
       </c>
-      <c r="D65" s="36"/>
-      <c r="G65" s="36" t="s">
+      <c r="D65" s="35"/>
+      <c r="G65" s="35" t="s">
         <v>199</v>
       </c>
       <c r="J65" s="1" t="str">
@@ -3666,8 +3804,8 @@
       <c r="B66" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="C66" s="36"/>
-      <c r="D66" s="36"/>
+      <c r="C66" s="35"/>
+      <c r="D66" s="35"/>
       <c r="E66" s="1" t="s">
         <v>191</v>
       </c>
@@ -3691,8 +3829,8 @@
       <c r="B67" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="C67" s="36"/>
-      <c r="D67" s="36"/>
+      <c r="C67" s="35"/>
+      <c r="D67" s="35"/>
       <c r="E67" s="1" t="s">
         <v>202</v>
       </c>
@@ -3716,17 +3854,17 @@
       <c r="B68" s="11" t="s">
         <v>205</v>
       </c>
-      <c r="C68" s="36" t="s">
+      <c r="C68" s="35" t="s">
         <v>206</v>
       </c>
-      <c r="D68" s="36"/>
+      <c r="D68" s="35"/>
       <c r="E68" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="G68" s="36" t="s">
+      <c r="G68" s="35" t="s">
         <v>208</v>
       </c>
-      <c r="H68" s="36" t="s">
+      <c r="H68" s="35" t="s">
         <v>204</v>
       </c>
       <c r="I68" s="1" t="str">
@@ -3743,8 +3881,8 @@
       <c r="B69" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="C69" s="36"/>
-      <c r="D69" s="36"/>
+      <c r="C69" s="35"/>
+      <c r="D69" s="35"/>
       <c r="E69" s="1" t="s">
         <v>93</v>
       </c>
@@ -3768,14 +3906,14 @@
       <c r="B70" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="C70" s="36" t="s">
+      <c r="C70" s="35" t="s">
         <v>210</v>
       </c>
-      <c r="D70" s="36"/>
+      <c r="D70" s="35"/>
       <c r="E70" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="G70" s="36" t="s">
+      <c r="G70" s="35" t="s">
         <v>212</v>
       </c>
       <c r="I70" s="1" t="str">
@@ -3792,14 +3930,14 @@
       <c r="B71" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="C71" s="36" t="s">
+      <c r="C71" s="35" t="s">
         <v>214</v>
       </c>
-      <c r="D71" s="36"/>
+      <c r="D71" s="35"/>
       <c r="E71" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="G71" s="36" t="s">
+      <c r="G71" s="35" t="s">
         <v>215</v>
       </c>
       <c r="I71" s="1" t="str">
@@ -3832,14 +3970,14 @@
       <c r="B73" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="C73" s="36" t="s">
+      <c r="C73" s="35" t="s">
         <v>220</v>
       </c>
-      <c r="D73" s="36"/>
+      <c r="D73" s="35"/>
       <c r="E73" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="G73" s="36"/>
+      <c r="G73" s="35"/>
       <c r="J73" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G73)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
@@ -3946,34 +4084,34 @@
       </c>
     </row>
     <row r="84" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="33" t="s">
+      <c r="A84" s="32" t="s">
         <v>202</v>
       </c>
-      <c r="B84" s="22"/>
-      <c r="C84" s="23" t="s">
+      <c r="B84" s="21"/>
+      <c r="C84" s="22" t="s">
         <v>232</v>
       </c>
-      <c r="D84" s="23"/>
-      <c r="E84" s="22"/>
-      <c r="F84" s="22"/>
-      <c r="G84" s="22" t="s">
+      <c r="D84" s="22"/>
+      <c r="E84" s="21"/>
+      <c r="F84" s="21"/>
+      <c r="G84" s="21" t="s">
         <v>202</v>
       </c>
-      <c r="H84" s="23" t="s">
+      <c r="H84" s="22" t="s">
         <v>193</v>
       </c>
-      <c r="I84" s="23" t="str">
+      <c r="I84" s="22" t="str">
         <f aca="false">_xlfn.CONCAT(H84, G84)</f>
         <v>http://www.w3.org/ns/ssn/Platform</v>
       </c>
-      <c r="J84" s="22" t="str">
+      <c r="J84" s="21" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G84)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#Platform</v>
       </c>
-      <c r="K84" s="22"/>
+      <c r="K84" s="21"/>
     </row>
     <row r="85" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="24"/>
+      <c r="A85" s="23"/>
       <c r="B85" s="11" t="s">
         <v>233</v>
       </c>
@@ -4002,7 +4140,7 @@
       </c>
     </row>
     <row r="86" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="24"/>
+      <c r="A86" s="23"/>
       <c r="B86" s="11" t="s">
         <v>234</v>
       </c>
@@ -4022,7 +4160,7 @@
       </c>
     </row>
     <row r="87" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="24"/>
+      <c r="A87" s="23"/>
       <c r="B87" s="11" t="s">
         <v>235</v>
       </c>
@@ -4042,7 +4180,7 @@
       </c>
     </row>
     <row r="88" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="24"/>
+      <c r="A88" s="23"/>
       <c r="B88" s="11" t="s">
         <v>236</v>
       </c>
@@ -4055,7 +4193,7 @@
       </c>
     </row>
     <row r="89" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="24"/>
+      <c r="A89" s="23"/>
       <c r="B89" s="11" t="s">
         <v>238</v>
       </c>
@@ -4068,7 +4206,7 @@
       </c>
     </row>
     <row r="90" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="24"/>
+      <c r="A90" s="23"/>
       <c r="B90" s="11" t="s">
         <v>240</v>
       </c>
@@ -4088,7 +4226,7 @@
       </c>
     </row>
     <row r="91" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="24"/>
+      <c r="A91" s="23"/>
       <c r="B91" s="11" t="s">
         <v>241</v>
       </c>
@@ -4101,7 +4239,7 @@
       </c>
     </row>
     <row r="92" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="26" t="s">
+      <c r="A92" s="25" t="s">
         <v>205</v>
       </c>
       <c r="B92" s="4"/>
@@ -4270,36 +4408,36 @@
       </c>
     </row>
     <row r="101" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="33" t="s">
+      <c r="A101" s="32" t="s">
         <v>248</v>
       </c>
-      <c r="B101" s="22"/>
-      <c r="C101" s="23" t="s">
+      <c r="B101" s="21"/>
+      <c r="C101" s="22" t="s">
         <v>250</v>
       </c>
-      <c r="D101" s="23"/>
-      <c r="E101" s="22"/>
-      <c r="F101" s="22"/>
-      <c r="G101" s="22" t="s">
+      <c r="D101" s="22"/>
+      <c r="E101" s="21"/>
+      <c r="F101" s="21"/>
+      <c r="G101" s="21" t="s">
         <v>251</v>
       </c>
-      <c r="H101" s="23" t="s">
+      <c r="H101" s="22" t="s">
         <v>204</v>
       </c>
-      <c r="I101" s="23" t="str">
+      <c r="I101" s="22" t="str">
         <f aca="false">_xlfn.CONCAT(H101, G101)</f>
         <v>http://www.w3.org/ns/sosa/Observation </v>
       </c>
-      <c r="J101" s="22" t="str">
+      <c r="J101" s="21" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G101)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#Observation </v>
       </c>
-      <c r="K101" s="22" t="s">
+      <c r="K101" s="21" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="36.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="24"/>
+    <row r="102" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="23"/>
       <c r="B102" s="11" t="s">
         <v>20</v>
       </c>
@@ -4315,7 +4453,7 @@
       <c r="G102" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H102" s="15" t="s">
+      <c r="H102" s="10" t="s">
         <v>15</v>
       </c>
       <c r="J102" s="1" t="str">
@@ -4323,15 +4461,15 @@
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasIdentifier</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="36.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="24"/>
+    <row r="103" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="23"/>
       <c r="B103" s="11" t="s">
         <v>252</v>
       </c>
       <c r="G103" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="H103" s="15" t="s">
+      <c r="H103" s="10" t="s">
         <v>15</v>
       </c>
       <c r="J103" s="1" t="str">
@@ -4340,7 +4478,7 @@
       </c>
     </row>
     <row r="104" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="24"/>
+      <c r="A104" s="23"/>
       <c r="B104" s="11" t="s">
         <v>254</v>
       </c>
@@ -4359,7 +4497,7 @@
       </c>
     </row>
     <row r="105" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="24"/>
+      <c r="A105" s="23"/>
       <c r="B105" s="11" t="s">
         <v>257</v>
       </c>
@@ -4375,7 +4513,7 @@
       </c>
     </row>
     <row r="106" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="24"/>
+      <c r="A106" s="23"/>
       <c r="B106" s="11" t="s">
         <v>259</v>
       </c>
@@ -4391,7 +4529,7 @@
       </c>
     </row>
     <row r="107" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="24"/>
+      <c r="A107" s="23"/>
       <c r="B107" s="11" t="s">
         <v>261</v>
       </c>
@@ -4407,7 +4545,7 @@
       </c>
     </row>
     <row r="108" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="26" t="s">
+      <c r="A108" s="25" t="s">
         <v>263</v>
       </c>
       <c r="B108" s="4"/>
@@ -4502,7 +4640,7 @@
       <c r="G111" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="H111" s="15" t="s">
+      <c r="H111" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I111" s="1" t="str">
@@ -4514,12 +4652,12 @@
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#partOf </v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="7"/>
       <c r="B112" s="11" t="s">
         <v>270</v>
       </c>
-      <c r="C112" s="15" t="s">
+      <c r="C112" s="10" t="s">
         <v>271</v>
       </c>
       <c r="G112" s="1" t="s">
@@ -4537,12 +4675,12 @@
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasDescription</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="47.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="7"/>
       <c r="B113" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="C113" s="15" t="s">
+      <c r="C113" s="10" t="s">
         <v>273</v>
       </c>
       <c r="G113" s="1" t="s">
@@ -4562,67 +4700,71 @@
     </row>
     <row r="114" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="7"/>
-      <c r="B114" s="27" t="s">
+      <c r="B114" s="26" t="s">
         <v>274</v>
       </c>
-      <c r="C114" s="28"/>
-      <c r="D114" s="28"/>
-      <c r="E114" s="28"/>
-      <c r="F114" s="28"/>
-      <c r="G114" s="28" t="s">
+      <c r="C114" s="27" t="s">
         <v>275</v>
       </c>
-      <c r="H114" s="28" t="s">
+      <c r="D114" s="27"/>
+      <c r="E114" s="27"/>
+      <c r="F114" s="27"/>
+      <c r="G114" s="27" t="s">
+        <v>276</v>
+      </c>
+      <c r="H114" s="27" t="s">
         <v>15</v>
       </c>
       <c r="I114" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H114,G114)</f>
         <v>http://purl.org/ppeo/ppeo.owl#hasSpatialDistribution</v>
       </c>
-      <c r="J114" s="28" t="str">
+      <c r="J114" s="27" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G114)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasSpatialDistribution</v>
       </c>
-      <c r="K114" s="28"/>
+      <c r="K114" s="27"/>
       <c r="L114" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="7"/>
-      <c r="B115" s="27" t="s">
-        <v>277</v>
-      </c>
-      <c r="C115" s="28"/>
-      <c r="D115" s="28"/>
-      <c r="E115" s="28"/>
-      <c r="F115" s="28"/>
-      <c r="G115" s="28" t="s">
+      <c r="B115" s="26" t="s">
         <v>278</v>
       </c>
-      <c r="H115" s="28" t="s">
+      <c r="C115" s="27" t="s">
+        <v>279</v>
+      </c>
+      <c r="D115" s="27"/>
+      <c r="E115" s="27"/>
+      <c r="F115" s="27"/>
+      <c r="G115" s="27" t="s">
+        <v>280</v>
+      </c>
+      <c r="H115" s="27" t="s">
         <v>15</v>
       </c>
       <c r="I115" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H115,G115)</f>
         <v>http://purl.org/ppeo/ppeo.owl#hasSpatialDistributionType</v>
       </c>
-      <c r="J115" s="28" t="str">
+      <c r="J115" s="27" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G115)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasSpatialDistributionType</v>
       </c>
-      <c r="K115" s="28"/>
+      <c r="K115" s="27"/>
     </row>
     <row r="116" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="7"/>
       <c r="B116" s="11" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="G116" s="1" t="s">
         <v>186</v>
@@ -4642,7 +4784,10 @@
     <row r="117" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="7"/>
       <c r="B117" s="11" t="s">
-        <v>282</v>
+        <v>284</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>285</v>
       </c>
       <c r="H117" s="10" t="s">
         <v>15</v>
@@ -4657,38 +4802,38 @@
       </c>
     </row>
     <row r="118" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="33" t="s">
-        <v>283</v>
-      </c>
-      <c r="B118" s="22"/>
-      <c r="C118" s="23" t="s">
-        <v>284</v>
-      </c>
-      <c r="D118" s="23"/>
-      <c r="E118" s="22"/>
-      <c r="F118" s="22"/>
-      <c r="G118" s="22" t="s">
-        <v>285</v>
-      </c>
-      <c r="H118" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="I118" s="23" t="str">
+      <c r="A118" s="32" t="s">
+        <v>286</v>
+      </c>
+      <c r="B118" s="21"/>
+      <c r="C118" s="22" t="s">
+        <v>287</v>
+      </c>
+      <c r="D118" s="22"/>
+      <c r="E118" s="21"/>
+      <c r="F118" s="21"/>
+      <c r="G118" s="21" t="s">
+        <v>288</v>
+      </c>
+      <c r="H118" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="I118" s="22" t="str">
         <f aca="false">_xlfn.CONCAT(H118,"observed_variable")</f>
         <v>http://purl.org/ppeo/ppeo.owl#observed_variable</v>
       </c>
-      <c r="J118" s="22" t="str">
+      <c r="J118" s="21" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G118)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#ObservedVariable</v>
       </c>
-      <c r="K118" s="22" t="s">
-        <v>286</v>
+      <c r="K118" s="21" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="24"/>
+      <c r="A119" s="23"/>
       <c r="B119" s="11" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C119" s="10" t="s">
         <v>141</v>
@@ -4704,10 +4849,16 @@
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasIdentifier</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="24"/>
+    <row r="120" customFormat="false" ht="35.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="23"/>
       <c r="B120" s="11" t="s">
-        <v>288</v>
+        <v>291</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="D120" s="10" t="s">
+        <v>293</v>
       </c>
       <c r="H120" s="10" t="s">
         <v>15</v>
@@ -4717,819 +4868,952 @@
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="24"/>
+    <row r="121" customFormat="false" ht="35.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="23"/>
       <c r="B121" s="11" t="s">
-        <v>289</v>
+        <v>294</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="D121" s="10" t="s">
+        <v>296</v>
       </c>
       <c r="J121" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G121)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="24"/>
+    <row r="122" customFormat="false" ht="35.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="23"/>
       <c r="B122" s="11" t="s">
-        <v>290</v>
+        <v>297</v>
+      </c>
+      <c r="C122" s="36" t="s">
+        <v>298</v>
+      </c>
+      <c r="D122" s="10" t="s">
+        <v>299</v>
       </c>
       <c r="J122" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G122)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="24"/>
+    <row r="123" customFormat="false" ht="24.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="23"/>
       <c r="B123" s="11" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="24"/>
+        <v>300</v>
+      </c>
+      <c r="C123" s="36" t="s">
+        <v>301</v>
+      </c>
+      <c r="D123" s="10" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="24.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="23"/>
       <c r="B124" s="11" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="24"/>
-      <c r="B125" s="11"/>
-    </row>
-    <row r="126" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="24"/>
-      <c r="B126" s="11"/>
-      <c r="J126" s="1" t="str">
-        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G126)</f>
+        <v>303</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="D124" s="10" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="24.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="23"/>
+      <c r="B125" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="C125" s="37" t="s">
+        <v>307</v>
+      </c>
+      <c r="D125" s="10" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="23"/>
+      <c r="B126" s="11" t="s">
+        <v>309</v>
+      </c>
+      <c r="D126" s="10" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="35.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="23"/>
+      <c r="B127" s="11" t="s">
+        <v>311</v>
+      </c>
+      <c r="C127" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="D127" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="J127" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G127)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="26" t="s">
-        <v>282</v>
-      </c>
-      <c r="B127" s="4"/>
-      <c r="C127" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="D127" s="5"/>
-      <c r="E127" s="4"/>
-      <c r="F127" s="4"/>
-      <c r="G127" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="H127" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I127" s="5" t="str">
-        <f aca="false">_xlfn.CONCAT(H127,LOWER(G127))</f>
+    <row r="128" customFormat="false" ht="12.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="23"/>
+      <c r="B128" s="11" t="s">
+        <v>314</v>
+      </c>
+      <c r="C128" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="D128" s="10" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="24.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="23"/>
+      <c r="B129" s="11" t="s">
+        <v>317</v>
+      </c>
+      <c r="C129" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="D129" s="10" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="105.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="23"/>
+      <c r="B130" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="C130" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="D130" s="10" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="24.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="23"/>
+      <c r="B131" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="C131" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="D131" s="10" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="12.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="23"/>
+      <c r="B132" s="11" t="s">
+        <v>326</v>
+      </c>
+      <c r="C132" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="D132" s="10" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="24.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="23"/>
+      <c r="B133" s="11" t="s">
+        <v>329</v>
+      </c>
+      <c r="C133" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="D133" s="10" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="24.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="23"/>
+      <c r="B134" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="C134" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="D134" s="10" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="25" t="s">
+        <v>284</v>
+      </c>
+      <c r="B135" s="4"/>
+      <c r="C135" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="D135" s="5"/>
+      <c r="E135" s="4"/>
+      <c r="F135" s="4"/>
+      <c r="G135" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="H135" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I135" s="5" t="str">
+        <f aca="false">_xlfn.CONCAT(H135,LOWER(G135))</f>
         <v>http://purl.org/ppeo/ppeo.owl#factor</v>
       </c>
-      <c r="J127" s="4" t="str">
-        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G127)</f>
+      <c r="J135" s="4" t="str">
+        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G135)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#Factor</v>
       </c>
-      <c r="K127" s="4"/>
-    </row>
-    <row r="128" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="7"/>
-      <c r="B128" s="11" t="s">
+      <c r="K135" s="4"/>
+    </row>
+    <row r="136" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="7"/>
+      <c r="B136" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C128" s="10" t="s">
+      <c r="C136" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="G128" s="1" t="s">
+      <c r="G136" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H128" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J128" s="1" t="str">
-        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G128)</f>
+      <c r="H136" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J136" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G136)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasIdentifier</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="7"/>
-      <c r="B129" s="11" t="s">
+    <row r="137" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="7"/>
+      <c r="B137" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="G129" s="1" t="s">
+      <c r="G137" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="J129" s="1" t="str">
-        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G129)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#partOf </v>
-      </c>
-    </row>
-    <row r="130" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="7"/>
-      <c r="B130" s="11" t="s">
-        <v>295</v>
-      </c>
-      <c r="J130" s="1" t="str">
-        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G130)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
-      </c>
-    </row>
-    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="7"/>
-      <c r="B131" s="11" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="7"/>
-      <c r="B132" s="11" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="133" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="7"/>
-      <c r="B133" s="11" t="s">
-        <v>298</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="134" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="33" t="s">
-        <v>300</v>
-      </c>
-      <c r="B134" s="22"/>
-      <c r="C134" s="23" t="s">
-        <v>301</v>
-      </c>
-      <c r="D134" s="23"/>
-      <c r="E134" s="22"/>
-      <c r="F134" s="22"/>
-      <c r="G134" s="22" t="s">
-        <v>300</v>
-      </c>
-      <c r="H134" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="I134" s="23"/>
-      <c r="J134" s="22" t="str">
-        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G134)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#Sample</v>
-      </c>
-      <c r="K134" s="22"/>
-    </row>
-    <row r="135" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="24"/>
-      <c r="B135" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C135" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="G135" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H135" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J135" s="1" t="str">
-        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G135)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasIdentifier</v>
-      </c>
-    </row>
-    <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="24"/>
-      <c r="B136" s="11"/>
-      <c r="C136" s="10"/>
-    </row>
-    <row r="137" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="24"/>
-      <c r="B137" s="11"/>
       <c r="J137" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G137)</f>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#partOf </v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="7"/>
+      <c r="B138" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="J138" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G138)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="26" t="s">
-        <v>302</v>
-      </c>
-      <c r="B138" s="4"/>
-      <c r="C138" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="D138" s="5"/>
-      <c r="E138" s="4"/>
-      <c r="F138" s="4"/>
-      <c r="G138" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="H138" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I138" s="5"/>
-      <c r="J138" s="4" t="str">
-        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G138)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#BiologicalMaterial</v>
-      </c>
-      <c r="K138" s="4"/>
-    </row>
-    <row r="139" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="7"/>
       <c r="B139" s="11" t="s">
-        <v>305</v>
-      </c>
-      <c r="C139" s="10" t="s">
-        <v>306</v>
-      </c>
-      <c r="G139" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H139" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J139" s="1" t="str">
-        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G139)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasIdentifier</v>
-      </c>
-    </row>
-    <row r="140" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="7"/>
       <c r="B140" s="11" t="s">
-        <v>307</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="J140" s="1" t="str">
-        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G140)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
+        <v>339</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="7"/>
       <c r="B141" s="11" t="s">
-        <v>309</v>
+        <v>340</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="7"/>
-      <c r="B142" s="11" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="7"/>
+        <v>341</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="32" t="s">
+        <v>342</v>
+      </c>
+      <c r="B142" s="21"/>
+      <c r="C142" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="D142" s="22"/>
+      <c r="E142" s="21"/>
+      <c r="F142" s="21"/>
+      <c r="G142" s="21" t="s">
+        <v>342</v>
+      </c>
+      <c r="H142" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="I142" s="22"/>
+      <c r="J142" s="21" t="str">
+        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G142)</f>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#Sample</v>
+      </c>
+      <c r="K142" s="21"/>
+    </row>
+    <row r="143" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="23"/>
       <c r="B143" s="11" t="s">
-        <v>312</v>
+        <v>20</v>
+      </c>
+      <c r="C143" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="G143" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H143" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J143" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G143)</f>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasIdentifier</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="7"/>
-      <c r="B144" s="11" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="7"/>
+      <c r="A144" s="23"/>
+      <c r="B144" s="11"/>
+      <c r="C144" s="10"/>
+    </row>
+    <row r="145" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="23"/>
       <c r="B145" s="11"/>
-    </row>
-    <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="7"/>
-      <c r="B146" s="11"/>
-    </row>
-    <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J145" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G145)</f>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="25" t="s">
+        <v>344</v>
+      </c>
+      <c r="B146" s="4"/>
+      <c r="C146" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="D146" s="5"/>
+      <c r="E146" s="4"/>
+      <c r="F146" s="4"/>
+      <c r="G146" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="H146" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I146" s="5"/>
+      <c r="J146" s="4" t="str">
+        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G146)</f>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#BiologicalMaterial</v>
+      </c>
+      <c r="K146" s="4"/>
+    </row>
+    <row r="147" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="7"/>
-      <c r="B147" s="11"/>
-    </row>
-    <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B147" s="11" t="s">
+        <v>347</v>
+      </c>
+      <c r="C147" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="G147" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H147" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J147" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G147)</f>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasIdentifier</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="7"/>
-      <c r="B148" s="11"/>
-    </row>
-    <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B148" s="11" t="s">
+        <v>349</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="J148" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G148)</f>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="7"/>
-      <c r="B149" s="11"/>
+      <c r="B149" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="7"/>
-      <c r="B150" s="11"/>
+      <c r="B150" s="11" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="7"/>
-      <c r="B151" s="11"/>
+      <c r="B151" s="11" t="s">
+        <v>354</v>
+      </c>
     </row>
     <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="7"/>
-      <c r="B152" s="11"/>
-    </row>
-    <row r="153" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="33" t="s">
-        <v>314</v>
-      </c>
-      <c r="B153" s="22"/>
-      <c r="C153" s="23" t="s">
-        <v>315</v>
-      </c>
-      <c r="D153" s="23"/>
-      <c r="E153" s="22"/>
-      <c r="F153" s="22"/>
-      <c r="G153" s="22" t="s">
-        <v>314</v>
-      </c>
-      <c r="H153" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="I153" s="23"/>
-      <c r="J153" s="22" t="str">
-        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G153)</f>
+      <c r="B152" s="11" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="7"/>
+      <c r="B153" s="11"/>
+    </row>
+    <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="7"/>
+      <c r="B154" s="11"/>
+    </row>
+    <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="7"/>
+      <c r="B155" s="11"/>
+    </row>
+    <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="7"/>
+      <c r="B156" s="11"/>
+    </row>
+    <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="7"/>
+      <c r="B157" s="11"/>
+    </row>
+    <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="7"/>
+      <c r="B158" s="11"/>
+    </row>
+    <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="7"/>
+      <c r="B159" s="11"/>
+    </row>
+    <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="7"/>
+      <c r="B160" s="11"/>
+    </row>
+    <row r="161" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="32" t="s">
+        <v>356</v>
+      </c>
+      <c r="B161" s="21"/>
+      <c r="C161" s="22" t="s">
+        <v>357</v>
+      </c>
+      <c r="D161" s="22"/>
+      <c r="E161" s="21"/>
+      <c r="F161" s="21"/>
+      <c r="G161" s="21" t="s">
+        <v>356</v>
+      </c>
+      <c r="H161" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="I161" s="22"/>
+      <c r="J161" s="21" t="str">
+        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G161)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#Event</v>
       </c>
-      <c r="K153" s="22"/>
-    </row>
-    <row r="154" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="24"/>
-      <c r="B154" s="11" t="s">
+      <c r="K161" s="21"/>
+    </row>
+    <row r="162" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="23"/>
+      <c r="B162" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C154" s="10" t="s">
+      <c r="C162" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="G154" s="1" t="s">
+      <c r="G162" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H154" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J154" s="1" t="str">
-        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G154)</f>
+      <c r="H162" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J162" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G162)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasIdentifier</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="24"/>
-      <c r="B155" s="11"/>
-      <c r="J155" s="1" t="str">
-        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G155)</f>
+    <row r="163" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="23"/>
+      <c r="B163" s="11"/>
+      <c r="J163" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G163)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="24"/>
-      <c r="B156" s="11"/>
-      <c r="J156" s="1" t="str">
-        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G156)</f>
+    <row r="164" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="23"/>
+      <c r="B164" s="11"/>
+      <c r="J164" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G164)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
       </c>
     </row>
-    <row r="157" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="24"/>
-      <c r="B157" s="11"/>
-      <c r="J157" s="1" t="str">
-        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G157)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
-      </c>
-    </row>
-    <row r="158" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="26" t="s">
-        <v>316</v>
-      </c>
-      <c r="B158" s="4"/>
-      <c r="C158" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="D158" s="5"/>
-      <c r="E158" s="4"/>
-      <c r="F158" s="4"/>
-      <c r="G158" s="4"/>
-      <c r="H158" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I158" s="5"/>
-      <c r="J158" s="4" t="str">
-        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G158)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
-      </c>
-      <c r="K158" s="4"/>
-    </row>
-    <row r="159" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="7"/>
-      <c r="B159" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C159" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="G159" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H159" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J159" s="1" t="str">
-        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G159)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasIdentifier</v>
-      </c>
-    </row>
-    <row r="160" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="7"/>
-      <c r="B160" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C160" s="10" t="s">
-        <v>318</v>
-      </c>
-      <c r="E160" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="G160" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="H160" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="K160" s="1" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="161" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="7"/>
-      <c r="B161" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="C161" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="E161" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G161" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="H161" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J161" s="1" t="str">
-        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G161)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasEnvironmentParameter</v>
-      </c>
-    </row>
-    <row r="162" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="7"/>
-      <c r="B162" s="11" t="s">
-        <v>324</v>
-      </c>
-      <c r="C162" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="E162" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G162" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="H162" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="163" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="7"/>
-      <c r="B163" s="11" t="s">
-        <v>298</v>
-      </c>
-      <c r="C163" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="E163" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="F163" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="G163" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="H163" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="164" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="33" t="s">
-        <v>327</v>
-      </c>
-      <c r="B164" s="22"/>
-      <c r="C164" s="23" t="s">
-        <v>328</v>
-      </c>
-      <c r="D164" s="23"/>
-      <c r="E164" s="22"/>
-      <c r="F164" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="G164" s="22" t="s">
-        <v>327</v>
-      </c>
-      <c r="H164" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="I164" s="23"/>
-      <c r="J164" s="22" t="str">
-        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G164)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#Person</v>
-      </c>
-      <c r="K164" s="22"/>
-    </row>
-    <row r="165" s="31" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="24"/>
-      <c r="B165" s="11" t="s">
-        <v>329</v>
-      </c>
-      <c r="C165" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="E165" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="F165" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="G165" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="H165" s="37" t="s">
-        <v>15</v>
-      </c>
+    <row r="165" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="23"/>
+      <c r="B165" s="11"/>
       <c r="J165" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G165)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasIdentifier</v>
-      </c>
-    </row>
-    <row r="166" s="31" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="24"/>
-      <c r="B166" s="11" t="s">
-        <v>330</v>
-      </c>
-      <c r="C166" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="E166" s="31" t="s">
-        <v>26</v>
-      </c>
-      <c r="F166" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="G166" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="H166" s="37" t="s">
-        <v>15</v>
-      </c>
-      <c r="J166" s="1" t="str">
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="25" t="s">
+        <v>358</v>
+      </c>
+      <c r="B166" s="4"/>
+      <c r="C166" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="D166" s="5"/>
+      <c r="E166" s="4"/>
+      <c r="F166" s="4"/>
+      <c r="G166" s="4"/>
+      <c r="H166" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I166" s="5"/>
+      <c r="J166" s="4" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G166)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasName</v>
-      </c>
-    </row>
-    <row r="167" s="31" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="24"/>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
+      </c>
+      <c r="K166" s="4"/>
+    </row>
+    <row r="167" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="7"/>
       <c r="B167" s="11" t="s">
-        <v>332</v>
-      </c>
-      <c r="C167" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="E167" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="F167" s="31" t="s">
-        <v>66</v>
-      </c>
-      <c r="G167" s="31" t="s">
-        <v>334</v>
-      </c>
-      <c r="H167" s="37" t="s">
+      <c r="C167" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="G167" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H167" s="10" t="s">
         <v>15</v>
       </c>
       <c r="J167" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G167)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasORCID</v>
-      </c>
-    </row>
-    <row r="168" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="24"/>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasIdentifier</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="7"/>
       <c r="B168" s="11" t="s">
-        <v>335</v>
-      </c>
-      <c r="C168" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="D168" s="31"/>
+        <v>68</v>
+      </c>
+      <c r="C168" s="10" t="s">
+        <v>360</v>
+      </c>
       <c r="E168" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="G168" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="H168" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="K168" s="1" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="7"/>
+      <c r="B169" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="E169" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F168" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="G168" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="H168" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J168" s="1" t="str">
-        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G168)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasEmailContact</v>
-      </c>
-    </row>
-    <row r="169" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="24"/>
-      <c r="B169" s="11" t="s">
-        <v>338</v>
-      </c>
-      <c r="C169" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="E169" s="25" t="s">
-        <v>338</v>
-      </c>
-      <c r="F169" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="G169" s="1" t="s">
-        <v>340</v>
+        <v>365</v>
       </c>
       <c r="H169" s="10" t="s">
         <v>15</v>
       </c>
       <c r="J169" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G169)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasRole</v>
-      </c>
-    </row>
-    <row r="170" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="24"/>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasEnvironmentParameter</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="7"/>
       <c r="B170" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="E170" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G170" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="H170" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="7"/>
+      <c r="B171" s="11" t="s">
+        <v>340</v>
+      </c>
+      <c r="C171" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="C170" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="E170" s="25" t="s">
-        <v>91</v>
-      </c>
-      <c r="F170" s="1" t="s">
+      <c r="E171" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="F171" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G171" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H171" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="32" t="s">
+        <v>369</v>
+      </c>
+      <c r="B172" s="21"/>
+      <c r="C172" s="22" t="s">
+        <v>370</v>
+      </c>
+      <c r="D172" s="22"/>
+      <c r="E172" s="21"/>
+      <c r="F172" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="G170" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="H170" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J170" s="1" t="str">
-        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G170)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasAffiliation</v>
-      </c>
-    </row>
-    <row r="171" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="38" t="s">
-        <v>344</v>
-      </c>
-      <c r="B171" s="39"/>
-      <c r="C171" s="40" t="s">
-        <v>345</v>
-      </c>
-      <c r="D171" s="40"/>
-      <c r="E171" s="39"/>
-      <c r="F171" s="39"/>
-      <c r="G171" s="39"/>
-      <c r="H171" s="40"/>
-      <c r="I171" s="40"/>
-      <c r="J171" s="39" t="str">
-        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G171)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
-      </c>
-      <c r="K171" s="39" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="172" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="41"/>
-      <c r="B172" s="14" t="s">
+      <c r="G172" s="21" t="s">
+        <v>369</v>
+      </c>
+      <c r="H172" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="I172" s="22"/>
+      <c r="J172" s="21" t="str">
+        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G172)</f>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#Person</v>
+      </c>
+      <c r="K172" s="21"/>
+    </row>
+    <row r="173" s="30" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="23"/>
+      <c r="B173" s="11" t="s">
+        <v>371</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E173" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="C172" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="J172" s="1" t="str">
-        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G172)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
-      </c>
-    </row>
-    <row r="173" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="41"/>
-      <c r="B173" s="14" t="s">
-        <v>347</v>
+      <c r="F173" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="G173" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="H173" s="38" t="s">
+        <v>15</v>
       </c>
       <c r="J173" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G173)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
-      </c>
-    </row>
-    <row r="174" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="41"/>
-      <c r="B174" s="14" t="s">
-        <v>348</v>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasIdentifier</v>
+      </c>
+    </row>
+    <row r="174" s="30" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="23"/>
+      <c r="B174" s="11" t="s">
+        <v>372</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="E174" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="F174" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="G174" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="H174" s="38" t="s">
+        <v>15</v>
       </c>
       <c r="J174" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G174)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
-      </c>
-    </row>
-    <row r="175" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="41"/>
-      <c r="B175" s="14" t="s">
-        <v>209</v>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasName</v>
+      </c>
+    </row>
+    <row r="175" s="30" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="23"/>
+      <c r="B175" s="11" t="s">
+        <v>374</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E175" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="F175" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="G175" s="30" t="s">
+        <v>376</v>
+      </c>
+      <c r="H175" s="38" t="s">
+        <v>15</v>
       </c>
       <c r="J175" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G175)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
-      </c>
-    </row>
-    <row r="176" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="41"/>
-      <c r="B176" s="14" t="s">
-        <v>213</v>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasORCID</v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="23"/>
+      <c r="B176" s="11" t="s">
+        <v>377</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D176" s="30"/>
+      <c r="E176" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F176" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G176" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="H176" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J176" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G176)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
-      </c>
-    </row>
-    <row r="177" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="41"/>
-      <c r="B177" s="14" t="s">
-        <v>349</v>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasEmailContact</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="23"/>
+      <c r="B177" s="11" t="s">
+        <v>380</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="E177" s="24" t="s">
+        <v>380</v>
+      </c>
+      <c r="F177" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G177" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="H177" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J177" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G177)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
-      </c>
-    </row>
-    <row r="178" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="41"/>
-      <c r="B178" s="14" t="s">
-        <v>350</v>
-      </c>
-      <c r="E178" s="13" t="s">
-        <v>351</v>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasRole</v>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A178" s="23"/>
+      <c r="B178" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="E178" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="F178" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G178" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="H178" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J178" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G178)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
-      </c>
-    </row>
-    <row r="179" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="38" t="s">
-        <v>352</v>
-      </c>
-      <c r="B179" s="39"/>
-      <c r="C179" s="40" t="s">
-        <v>353</v>
-      </c>
-      <c r="D179" s="40"/>
-      <c r="E179" s="39"/>
-      <c r="F179" s="39"/>
-      <c r="G179" s="39"/>
-      <c r="H179" s="40"/>
-      <c r="I179" s="40"/>
-      <c r="J179" s="39" t="str">
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasAffiliation</v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A179" s="39" t="s">
+        <v>386</v>
+      </c>
+      <c r="B179" s="40"/>
+      <c r="C179" s="41" t="s">
+        <v>387</v>
+      </c>
+      <c r="D179" s="41"/>
+      <c r="E179" s="40"/>
+      <c r="F179" s="40"/>
+      <c r="G179" s="40"/>
+      <c r="H179" s="41"/>
+      <c r="I179" s="41"/>
+      <c r="J179" s="40" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G179)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
       </c>
-      <c r="K179" s="39" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="180" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="41"/>
-      <c r="B180" s="11" t="s">
+      <c r="K179" s="40" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="180" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="42"/>
+      <c r="B180" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C180" s="10" t="s">
+      <c r="C180" s="13" t="s">
         <v>141</v>
-      </c>
-      <c r="G180" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="J180" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G180)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasIdentifier</v>
-      </c>
-    </row>
-    <row r="181" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="41"/>
-      <c r="B181" s="11"/>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
+      </c>
+    </row>
+    <row r="181" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A181" s="42"/>
+      <c r="B181" s="14" t="s">
+        <v>389</v>
+      </c>
       <c r="J181" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G181)</f>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
+      </c>
+    </row>
+    <row r="182" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A182" s="42"/>
+      <c r="B182" s="14" t="s">
+        <v>390</v>
+      </c>
+      <c r="J182" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G182)</f>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
+      </c>
+    </row>
+    <row r="183" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A183" s="42"/>
+      <c r="B183" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="J183" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G183)</f>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
+      </c>
+    </row>
+    <row r="184" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A184" s="42"/>
+      <c r="B184" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="J184" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G184)</f>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
+      </c>
+    </row>
+    <row r="185" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A185" s="42"/>
+      <c r="B185" s="14" t="s">
+        <v>391</v>
+      </c>
+      <c r="J185" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G185)</f>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
+      </c>
+    </row>
+    <row r="186" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="42"/>
+      <c r="B186" s="14" t="s">
+        <v>392</v>
+      </c>
+      <c r="E186" s="13" t="s">
+        <v>393</v>
+      </c>
+      <c r="J186" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G186)</f>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A187" s="39" t="s">
+        <v>394</v>
+      </c>
+      <c r="B187" s="40"/>
+      <c r="C187" s="41" t="s">
+        <v>395</v>
+      </c>
+      <c r="D187" s="41"/>
+      <c r="E187" s="40"/>
+      <c r="F187" s="40"/>
+      <c r="G187" s="40"/>
+      <c r="H187" s="41"/>
+      <c r="I187" s="41"/>
+      <c r="J187" s="40" t="str">
+        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G187)</f>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
+      </c>
+      <c r="K187" s="40" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="188" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="42"/>
+      <c r="B188" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C188" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="G188" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J188" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G188)</f>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasIdentifier</v>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="42"/>
+      <c r="B189" s="11"/>
+      <c r="J189" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G189)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
       </c>
     </row>
@@ -5545,6 +5829,168 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -5584,61 +6030,61 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="11" style="1" width="11.53"/>
   </cols>
   <sheetData>
-    <row r="1" s="25" customFormat="true" ht="36.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="25" t="s">
+    <row r="1" s="24" customFormat="true" ht="36.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="E1" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="F1" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="25" t="s">
+      <c r="G1" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="H1" s="25" t="s">
+      <c r="H1" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="I1" s="42" t="s">
+      <c r="I1" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="J1" s="25" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="2" s="36" customFormat="true" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="36" t="s">
-        <v>355</v>
-      </c>
-      <c r="B2" s="36" t="s">
-        <v>356</v>
-      </c>
-      <c r="C2" s="36" t="s">
-        <v>357</v>
-      </c>
-      <c r="D2" s="43" t="n">
+      <c r="J1" s="24" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="2" s="35" customFormat="true" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="35" t="s">
+        <v>397</v>
+      </c>
+      <c r="B2" s="35" t="s">
+        <v>398</v>
+      </c>
+      <c r="C2" s="35" t="s">
+        <v>399</v>
+      </c>
+      <c r="D2" s="44" t="n">
         <v>45644</v>
       </c>
-      <c r="E2" s="43" t="n">
+      <c r="E2" s="44" t="n">
         <v>45644</v>
       </c>
-      <c r="F2" s="36" t="s">
-        <v>358</v>
-      </c>
-      <c r="G2" s="36" t="n">
+      <c r="F2" s="35" t="s">
+        <v>400</v>
+      </c>
+      <c r="G2" s="35" t="n">
         <v>3.2</v>
       </c>
-      <c r="H2" s="36" t="n">
+      <c r="H2" s="35" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -5662,42 +6108,42 @@
   <dimension ref="A1:I1"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="31" width="20.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="31" width="14.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="31" width="19.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="31" width="14.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="31" width="13.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="31" width="17.04"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="31" width="18.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="31" width="21.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="30" width="20.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="30" width="14.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="30" width="19.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="30" width="14.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="30" width="13.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="30" width="17.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="30" width="18.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="30" width="21.79"/>
   </cols>
   <sheetData>
-    <row r="1" s="42" customFormat="true" ht="36.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="42" t="s">
+    <row r="1" s="43" customFormat="true" ht="36.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="42" t="s">
+      <c r="B1" s="43" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="42" t="s">
+      <c r="C1" s="43" t="s">
         <v>80</v>
       </c>
-      <c r="D1" s="42" t="s">
+      <c r="D1" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="E1" s="42" t="s">
+      <c r="E1" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="F1" s="42" t="s">
+      <c r="F1" s="43" t="s">
         <v>89</v>
       </c>
-      <c r="G1" s="42" t="s">
+      <c r="G1" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="H1" s="42" t="s">
+      <c r="H1" s="43" t="s">
         <v>96</v>
       </c>
-      <c r="I1" s="42" t="s">
+      <c r="I1" s="43" t="s">
         <v>100</v>
       </c>
     </row>
@@ -5720,34 +6166,34 @@
   <dimension ref="A1:F1"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="31" width="24.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="31" width="14.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="31" width="19.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="31" width="14.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="31" width="13.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="31" width="17.04"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="31" width="18.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="31" width="21.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="30" width="24.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="30" width="14.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="30" width="19.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="30" width="14.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="30" width="13.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="30" width="17.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="30" width="18.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="30" width="21.79"/>
   </cols>
   <sheetData>
-    <row r="1" s="42" customFormat="true" ht="36.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="42" t="s">
-        <v>329</v>
-      </c>
-      <c r="B1" s="42" t="s">
-        <v>330</v>
-      </c>
-      <c r="C1" s="42" t="s">
-        <v>332</v>
-      </c>
-      <c r="D1" s="42" t="s">
-        <v>335</v>
-      </c>
-      <c r="E1" s="42" t="s">
-        <v>338</v>
-      </c>
-      <c r="F1" s="42" t="s">
-        <v>341</v>
+    <row r="1" s="43" customFormat="true" ht="36.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="43" t="s">
+        <v>371</v>
+      </c>
+      <c r="B1" s="43" t="s">
+        <v>372</v>
+      </c>
+      <c r="C1" s="43" t="s">
+        <v>374</v>
+      </c>
+      <c r="D1" s="43" t="s">
+        <v>377</v>
+      </c>
+      <c r="E1" s="43" t="s">
+        <v>380</v>
+      </c>
+      <c r="F1" s="43" t="s">
+        <v>383</v>
       </c>
     </row>
   </sheetData>
@@ -5769,33 +6215,33 @@
   <dimension ref="A1:F1"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="31" width="20.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="31" width="14.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="31" width="19.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="31" width="20.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="31" width="13.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="31" width="17.04"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="31" width="18.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="31" width="21.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="30" width="20.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="30" width="14.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="30" width="19.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="30" width="20.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="30" width="13.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="30" width="17.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="30" width="18.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="30" width="21.79"/>
   </cols>
   <sheetData>
-    <row r="1" s="42" customFormat="true" ht="36.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="44" t="s">
+    <row r="1" s="43" customFormat="true" ht="36.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="45" t="s">
         <v>176</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="C1" s="45" t="s">
         <v>180</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="D1" s="45" t="s">
         <v>182</v>
       </c>
-      <c r="E1" s="44" t="s">
+      <c r="E1" s="45" t="s">
         <v>184</v>
       </c>
-      <c r="F1" s="44" t="s">
+      <c r="F1" s="45" t="s">
         <v>187</v>
       </c>
     </row>
@@ -5818,45 +6264,45 @@
   <dimension ref="A1:J1"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="31" width="20.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="31" width="14.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="31" width="19.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="31" width="14.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="31" width="13.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="31" width="17.04"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="31" width="18.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="31" width="21.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="30" width="20.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="30" width="14.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="30" width="19.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="30" width="14.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="30" width="13.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="30" width="17.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="30" width="18.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="30" width="21.79"/>
   </cols>
   <sheetData>
-    <row r="1" s="42" customFormat="true" ht="36.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="25" t="s">
+    <row r="1" s="43" customFormat="true" ht="36.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="24" t="s">
         <v>107</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="E1" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="F1" s="24" t="s">
         <v>119</v>
       </c>
-      <c r="G1" s="25" t="s">
+      <c r="G1" s="24" t="s">
         <v>123</v>
       </c>
-      <c r="H1" s="25" t="s">
+      <c r="H1" s="24" t="s">
         <v>132</v>
       </c>
-      <c r="I1" s="25" t="s">
+      <c r="I1" s="24" t="s">
         <v>135</v>
       </c>
-      <c r="J1" s="25" t="s">
+      <c r="J1" s="24" t="s">
         <v>138</v>
       </c>
     </row>
@@ -5879,51 +6325,51 @@
   <dimension ref="A1:L1"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="31" width="20.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="31" width="14.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="31" width="19.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="31" width="14.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="31" width="13.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="31" width="17.04"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="31" width="18.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="31" width="21.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="30" width="20.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="30" width="14.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="30" width="19.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="30" width="14.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="30" width="13.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="30" width="17.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="30" width="18.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="30" width="21.79"/>
   </cols>
   <sheetData>
-    <row r="1" s="42" customFormat="true" ht="36.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="44" t="s">
+    <row r="1" s="43" customFormat="true" ht="36.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="45" t="s">
         <v>142</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="C1" s="45" t="s">
         <v>144</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="D1" s="45" t="s">
         <v>107</v>
       </c>
-      <c r="E1" s="44" t="s">
+      <c r="E1" s="45" t="s">
         <v>111</v>
       </c>
-      <c r="F1" s="44" t="s">
+      <c r="F1" s="45" t="s">
         <v>147</v>
       </c>
-      <c r="G1" s="44" t="s">
+      <c r="G1" s="45" t="s">
         <v>150</v>
       </c>
-      <c r="H1" s="44" t="s">
+      <c r="H1" s="45" t="s">
         <v>152</v>
       </c>
-      <c r="I1" s="44" t="s">
+      <c r="I1" s="45" t="s">
         <v>154</v>
       </c>
-      <c r="J1" s="44" t="s">
+      <c r="J1" s="45" t="s">
         <v>156</v>
       </c>
-      <c r="K1" s="44" t="s">
+      <c r="K1" s="45" t="s">
         <v>158</v>
       </c>
-      <c r="L1" s="44" t="s">
+      <c r="L1" s="45" t="s">
         <v>160</v>
       </c>
     </row>
@@ -5946,30 +6392,30 @@
   <dimension ref="A1:E1"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="31" width="20.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="31" width="14.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="31" width="19.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="31" width="14.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="31" width="13.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="31" width="17.04"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="31" width="18.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="31" width="21.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="30" width="20.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="30" width="14.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="30" width="19.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="30" width="14.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="30" width="13.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="30" width="17.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="30" width="18.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="30" width="21.79"/>
   </cols>
   <sheetData>
-    <row r="1" s="42" customFormat="true" ht="36.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="44" t="s">
+    <row r="1" s="43" customFormat="true" ht="36.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="45" t="s">
         <v>163</v>
       </c>
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="45" t="s">
         <v>164</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="C1" s="45" t="s">
         <v>166</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="D1" s="45" t="s">
         <v>168</v>
       </c>
-      <c r="E1" s="44" t="s">
+      <c r="E1" s="45" t="s">
         <v>171</v>
       </c>
     </row>

--- a/metadata/MIAFPE/MIAFPE_template_v1.1.xlsx
+++ b/metadata/MIAFPE/MIAFPE_template_v1.1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Information" sheetId="1" state="visible" r:id="rId3"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1079" uniqueCount="515">
   <si>
     <t xml:space="preserve">Sheet Name</t>
   </si>
@@ -625,6 +625,9 @@
     <t xml:space="preserve">Acts as Port</t>
   </si>
   <si>
+    <t xml:space="preserve">System Unique Identifier</t>
+  </si>
+  <si>
     <t xml:space="preserve">System Name</t>
   </si>
   <si>
@@ -673,9 +676,6 @@
     <t xml:space="preserve">equivalent to implements + hasInput</t>
   </si>
   <si>
-    <t xml:space="preserve">Data_File</t>
-  </si>
-  <si>
     <t xml:space="preserve">hasImplementedInput</t>
   </si>
   <si>
@@ -688,54 +688,93 @@
     <t xml:space="preserve">hasImplementedOutput</t>
   </si>
   <si>
-    <t xml:space="preserve">Conditions</t>
-  </si>
-  <si>
     <t xml:space="preserve">Condition</t>
   </si>
   <si>
+    <t xml:space="preserve">Condition - Used to specify ranges for qualities that act as Conditions on a Systems' operation. Example  For example, wind speed of 10-60m/s may be used as the Condition on a SystemProperty, for example, to state that a Sensor has a particular Accuracy under that Condition.</t>
+  </si>
+  <si>
     <t xml:space="preserve">inCondition</t>
   </si>
   <si>
+    <t xml:space="preserve">http://www.w3.org/ns/ssn/systems/</t>
+  </si>
+  <si>
     <t xml:space="preserve">Measurement Range</t>
   </si>
   <si>
-    <t xml:space="preserve">equivalent to ssn-system:hasSystemCapability + hasSystemCapability to class XXX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Measurement_Range</t>
+    <t xml:space="preserve"> Measurement Range - The set of values that the Sensor can return as the Result of an Observation under the defined Conditions with the defined system properties.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MeasurementRange</t>
   </si>
   <si>
     <t xml:space="preserve">Accuracy</t>
   </si>
   <si>
+    <t xml:space="preserve"> Accuracy - The closeness of agreement between the Result of an Observation (resp. the command of an Actuation) and the true value of the observed ObservableProperty (resp. of the acted on ActuatableProperty) under the defined Conditions.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Detection Limit</t>
   </si>
   <si>
+    <t xml:space="preserve">Detection Limit - An observed value for which the probability of falsely claiming the absence of a component in a material is beta, given a probability alpha of falsely claiming its presence.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DetectionLimit</t>
+  </si>
+  <si>
     <t xml:space="preserve">Drift</t>
   </si>
   <si>
+    <t xml:space="preserve">Drift - As a Sensor Property: a continuous or incremental change in the reported values of Observations over time for an unchanging Property under the defined Conditions. As an Actuator Property: a continuous or incremental change in the true value of the acted on ActuatableProperty over time for an unchanging command under the defined Conditions.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Frequency</t>
   </si>
   <si>
+    <t xml:space="preserve">Frequency - The smallest possible time between one Observation, Actuation, or Sampling and the next, under the defined Conditions.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Latency</t>
   </si>
   <si>
+    <t xml:space="preserve"> Latency - The time between a command for an Observation (resp. Actuation) and the Sensor providing a Result (resp. the Actuator operating the Actuation), under the defined Conditions.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Precision</t>
   </si>
   <si>
+    <t xml:space="preserve">Precision - As a sensor capability: The closeness of agreement between replicate Observations on an unchanged or similar quality value: i.e., a measure of a Sensor's ability to consistently reproduce an Observation, under the defined Conditions. As an actuator capability: The closeness of agreement between replicate Actuations for an unchanged or similar command: i.e., a measure of an Actuator's ability to consistently reproduce an Actuations, under the defined Conditions.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Resolution</t>
   </si>
   <si>
+    <t xml:space="preserve">Resolution - As a Sensor Property: the smallest difference in the value of a ObservableProperty being observed that would result in perceptably different values of Observation Results, under the defined Conditions. As an Actuator Property: the smallest difference in the value of an Actuation command that would result in a value change of the ActuatableProperty being acted on, under the defined Conditions. </t>
+  </si>
+  <si>
     <t xml:space="preserve">Response Time</t>
   </si>
   <si>
+    <t xml:space="preserve">Response time - As a Sensor Property: the time between a (step) change in the value of an observed ObservableProperty and a Sensor (possibly with specified error) 'settling' on an observed value, under the defined Conditions. As an Actuator Property: the time between a (step) change in the command of an Actuator and the 'settling' of the value of the acted on ActuatableProperty, under the defined Conditions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ResponseTime</t>
+  </si>
+  <si>
     <t xml:space="preserve">Selectivity</t>
   </si>
   <si>
+    <t xml:space="preserve">Selectivity - As a Sensor Property: Selectivity is a Property of a Sensor whereby it provides observed values for one or more ObservableProperties such that the Result for each ObservableProperty are independent of other Properties in the FeatureOfInterest being investigated, under the defined Conditions. As an Actuator Property: Selectivity is a Property of an Actuator whereby it acts on one or more ActuatableProperties such as the Results for each ActuatableProperty are independent of other Properties in the FeatureOfInterest being acted on, under the defined Conditions.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sensitivity</t>
   </si>
   <si>
+    <t xml:space="preserve">Sensitivity - As a Sensor Property: Sensitivity is the quotient of the change in a Result of Observations and the corresponding change in a value of an ObservableProperty being observed, under the defined Conditions. As an Actuator Property: Sensitivity is the quotient of the change in a command of Actuation and the corresponding change in a value of an ActuatableProperty being acted on, under the defined Conditions.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Platform - A Platform is an entity that hosts other entities, particularly Sensors, Actuators, Samplers, and other Platforms. Examples: A post, buoy, vehicle, ship, aircraft, satellite, cell-phone, human or animal may act as Platforms for (technical or biological) Sensors or Actuators.</t>
   </si>
   <si>
@@ -823,10 +862,10 @@
     <t xml:space="preserve">analog to hasResult</t>
   </si>
   <si>
-    <t xml:space="preserve">observed Property</t>
-  </si>
-  <si>
-    <t xml:space="preserve">observedProperty</t>
+    <t xml:space="preserve">Observed Property</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ObservedProperty</t>
   </si>
   <si>
     <t xml:space="preserve">Observation Unit</t>
@@ -1072,6 +1111,75 @@
     <t xml:space="preserve">A sample is a portion of plant tissue harvested, non-harvested or extracted from an observation unit for the purpose of sub-plant observations and/or molecular studies. A sample must be used when there is a physical sample that needs to be stored and traced. Otherwise, observations made at the sub-plant level should be recorded as plant level observations using the observed variables to characterize the object of the observation (e.g. Berry sugar content, Fruit weight, Grain Protein content, Leaf 1 width, Leaf 2 width, Leaf 2 length).</t>
   </si>
   <si>
+    <t xml:space="preserve">Sample ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unique identifier for the sample.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CEA:BE00034067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unique identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plant structure development stage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The stage in the life of a plant structure during which the sample was taken, in the form of an accession number to a suitable controlled vocabulary (Plant Ontology, BBCH scale)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PO:0025094; BBCH-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plant Ontology term (subclass or PO:0009012) or BBCH scale term</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plant anatomical entity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A description of  the plant part (e.g. leaf) or the plant product (e.g. resin) from which the sample was taken, in the form of an accession number to a suitable controlled vocabulary (Plant Ontology).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PO:0000003 ; PO:0025161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plant Ontology term (subclass of PO:0025131)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sample description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Any information not captured by the other sample fields, including quantification, sample treatments and processing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distal part of the leaf ; 100 mg of roots taken from 10 roots at 20°C, conserved in vacuum at 20 mM NaCl salinity, stored at -60 °C to -85 °C.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collection date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The date and time when the sample was collected / harvested</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2005-08-15T15:52:01+00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date/Time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sample external ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An identifier for the sample in a persistent repository, comprising the name of the repository and the accession number of the observation unit therein. Submission to the EBI Biosamples repository is recommended. URI are recommended when possible.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biosamples:SAMEA4202911</t>
+  </si>
+  <si>
     <t xml:space="preserve">Biological Material</t>
   </si>
   <si>
@@ -1081,37 +1189,271 @@
     <t xml:space="preserve">BiologicalMaterial</t>
   </si>
   <si>
-    <t xml:space="preserve">Biological Material ID</t>
+    <t xml:space="preserve">Biological material ID</t>
   </si>
   <si>
     <t xml:space="preserve">Code used to identify the biological material in the data file. Should be unique within the Investigation. Can correspond to experimental plant ID, seed lot ID, etc… This material identification is different from a BiosampleID which corresponds to Observation Unit or Samples sections below.</t>
   </si>
   <si>
-    <t xml:space="preserve">Biological Material External ID</t>
+    <t xml:space="preserve">INRA:W95115_inra_2001 ; INRA:inra_kernel_2351 ; Rothamsted:rres_GK090847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biological material external ID</t>
   </si>
   <si>
     <t xml:space="preserve">One to many identifiers for the biological material. Can include EBI Biosamples ID. URI are recommended when possible.</t>
   </si>
   <si>
+    <t xml:space="preserve">AGENT_project:AGENT_ID; Kernel_ID; experimentalPlateformID; GERMPLASM_DB_ID; Biosamples:SAMEA001234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Semicolon-separated list of unique identifiers, possibly prefixed by repository name</t>
+  </si>
+  <si>
     <t xml:space="preserve">Organism</t>
   </si>
   <si>
     <t xml:space="preserve">An identifier for the organism at the species level. Use of the NCBI taxon ID is recommended. </t>
   </si>
   <si>
+    <t xml:space="preserve">NCBITAXON:4577</t>
+  </si>
+  <si>
     <t xml:space="preserve">Genus</t>
   </si>
   <si>
+    <t xml:space="preserve">Genus name for the organism under study, according to standard scientific nomenclature.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zea ; Solanum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genus name</t>
+  </si>
+  <si>
     <t xml:space="preserve">Species</t>
   </si>
   <si>
+    <t xml:space="preserve">Species name (formally: specific epithet) for the organism under study, according to standard scientific nomenclature.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mays ; lycosperium x pennellii</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Species name</t>
+  </si>
+  <si>
     <t xml:space="preserve">Infraspecific name</t>
   </si>
   <si>
+    <t xml:space="preserve">Name of any subtaxa level, including variety, crossing name, etc. It can be used to store any additional taxonomic identifier. To be filled as key-value pair list format (the key is the name of the rank/category and the value is the value of  the rank/category). Ranks/categories can be among the following terms: subspecies, cultivar, variety, subvariety, convariety, group, subgroup, hybrid, line, form, subform. For MCPD compliance, the following abbreviations are allowed: "subsp." (subspecies); "convar." (convariety); "var." (variety); "f." (form); "Group" (cultivar group). MIAPPE adds "cv." (cultivar).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">subspecies:vinifera, cultivar:Pinot noir ; subsp.:aestivum, cv.:Weneda, Group:winter ; subsp. vinifera cv. Pinot Noir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Key-value pair list, or MCPD-compliant format</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biological material latitude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latitude of the studied biological material. [Alternative identifier for in situ material]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biological material longitude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Longitude of the studied biological material. [Alternative identifier for in situ material]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biological material altitude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Altitude of the studied biological material, provided in meters (m). [Alternative identifier for in situ material]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Numeric + unit abbreviation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biological material coordinates uncertainty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Circular uncertainty of the coordinates, preferably provided in meters (m). [Alternative identifier for in situ material]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200 m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Numeric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biological material preprocessing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Description of any process or treatment applied uniformly to the biological material, prior to the study itself. Can be provided as free text or as an accession number from a suitable controlled vocabulary.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EO:0007210 – PVY(NTN) ; transplanted from study http://phenome-fppn.fr/maugio/2013/t2351 ; observation unit ID: pot:894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plant Environment Ontology and/or free text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Material source ID (Holding institute/stock centre, accession)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An identifier for the source of the biological material, in the form of a key-value pair comprising the name/identifier of the repository from which the material was sourced plus the accession number of the repository for that material. Where an accession number has not been assigned, but the material has been derived from the crossing of known accessions, the material can be defined as follows: "mother_accession X father_accession", or, if father is unknown, as "mother_accession X UNKNOWN". For in situ material, the region of provenance may be used when an accession is not available. The Material source is commonly called germplasm, accession, genotype and even variety for commercial varieties. For the latest, keep in mind that a variety is commonly ambiguously identified and polysemous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INRA:W95115_inra ; ICNF:PNB-RPI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Material source DOI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digital Object Identifier (DOI) of the material source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">doi:10.15454/1.4658436467893904E12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Material source accession number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unique identifier for accessions within a genebank. If material source is not from a genebank, use a laboratory ID. In the case of a commercial variety, use the variety code, or name if no code available.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W95115_inra; SYNTHETICS R93</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Material source accession name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Can be: (i)genebank accession registered name or other designation given to the material, other than the donor"s accession number or collecting number. (ii) Variety name.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rheinische Vorgebirgstrauben; APACHE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free text (short)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Material source institute code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAO WIEWS code of the institute where the accession is maintained. The current set of institute codes is available from https://www.fao.org/wiews. If no institute code is available, create your own (Laboratory acronym or research institute acronym ...).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRA09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Material source institute name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name of the material source institute.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Institute name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Material source other identifiers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Any other identifiers known to exist in other collections for this material source. Use key:value pairs, separated by semicolons.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGENT_ID:AB_06024; Yet_Another_ID:YAID_123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Key:Value pairs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Material source latitude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latitude of the material source. [Alternative identifier for in situ material]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Material source longitude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Longitude of the material source. [Alternative identifier for in situ material]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Material source altitude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Altitude of the material source, provided in metres (m). [Alternative identifier for in situ material]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Material source coordinates uncertainty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Circular uncertainty of the coordinates, provided in meters (m). [Alternative identifier for in situ material]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Material source description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Description of the material source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Branches were collected from a 10-year-old tree growing in a progeny trial established in a loamy brown earth soil.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Event</t>
   </si>
   <si>
     <t xml:space="preserve">An event is discrete occurrence at a particular time in the experiment (which can be natural, such as rain, or unnatural, such as planting, watering, etc). Events may be the realization of Factors or parts of Factors, or may be confounding to Factors. Can be applied at the whole study level or to only a subset of observation units.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Event ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Event type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Short name of the event.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planting; Fertilizing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Event accession number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accession number of the event type in a suitable controlled vocabulary (Crop Ontology).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO_715:0000007 ; CO_715:0000011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Event description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Description of the event, including details such as amount applied and possibly duration of the event. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sowing using seed drill ; Fertilizer application: Ammonium nitrate at 3 kg/m2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Event date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date and time of the event.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2006-09-27T10:23:21+00:00 ; 2006-10-27, 2006-11-13, 2016-11-21</t>
   </si>
   <si>
     <t xml:space="preserve">Environment</t>
@@ -1247,9 +1589,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="General"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -1326,8 +1669,10 @@
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="7">
@@ -1451,7 +1796,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="45">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1528,7 +1873,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1596,10 +1941,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1628,7 +1969,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1819,7 +2160,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M189"/>
+  <dimension ref="A1:M202"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21.21"/>
@@ -3711,7 +4052,7 @@
     <row r="62" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="7"/>
       <c r="B62" s="11" t="s">
-        <v>20</v>
+        <v>195</v>
       </c>
       <c r="C62" s="35" t="s">
         <v>141</v>
@@ -3741,10 +4082,13 @@
     <row r="63" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="7"/>
       <c r="B63" s="11" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C63" s="35"/>
       <c r="D63" s="35"/>
+      <c r="E63" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="G63" s="13" t="s">
         <v>27</v>
       </c>
@@ -3763,7 +4107,7 @@
     <row r="64" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="7"/>
       <c r="B64" s="11" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C64" s="35"/>
       <c r="D64" s="35"/>
@@ -3785,32 +4129,32 @@
     <row r="65" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="7"/>
       <c r="B65" s="11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C65" s="35" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D65" s="35"/>
       <c r="G65" s="35" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J65" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G65)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#isSystemType</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="35.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="7"/>
       <c r="B66" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C66" s="35"/>
       <c r="D66" s="35"/>
-      <c r="E66" s="1" t="s">
+      <c r="E66" s="24" t="s">
         <v>191</v>
       </c>
       <c r="G66" s="13" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H66" s="1" t="s">
         <v>193</v>
@@ -3824,21 +4168,21 @@
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasSubsystem</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="35.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="7"/>
       <c r="B67" s="11" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C67" s="35"/>
       <c r="D67" s="35"/>
-      <c r="E67" s="1" t="s">
-        <v>202</v>
+      <c r="E67" s="24" t="s">
+        <v>203</v>
       </c>
       <c r="G67" s="13" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I67" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H67, G67)</f>
@@ -3849,23 +4193,23 @@
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#isHostedBy</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="35.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="7"/>
       <c r="B68" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="C68" s="35" t="s">
+        <v>207</v>
+      </c>
+      <c r="D68" s="35"/>
+      <c r="E68" s="24" t="s">
+        <v>208</v>
+      </c>
+      <c r="G68" s="35" t="s">
+        <v>209</v>
+      </c>
+      <c r="H68" s="35" t="s">
         <v>205</v>
-      </c>
-      <c r="C68" s="35" t="s">
-        <v>206</v>
-      </c>
-      <c r="D68" s="35"/>
-      <c r="E68" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="G68" s="35" t="s">
-        <v>208</v>
-      </c>
-      <c r="H68" s="35" t="s">
-        <v>204</v>
       </c>
       <c r="I68" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H68, G68)</f>
@@ -3876,14 +4220,14 @@
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hosts</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="35.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="7"/>
       <c r="B69" s="11" t="s">
         <v>93</v>
       </c>
       <c r="C69" s="35"/>
       <c r="D69" s="35"/>
-      <c r="E69" s="1" t="s">
+      <c r="E69" s="24" t="s">
         <v>93</v>
       </c>
       <c r="G69" s="13" t="s">
@@ -3901,31 +4245,34 @@
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasLocation</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="46" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="47.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="7"/>
       <c r="B70" s="11" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C70" s="35" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D70" s="35"/>
-      <c r="E70" s="1" t="s">
-        <v>211</v>
+      <c r="E70" s="24" t="s">
+        <v>65</v>
       </c>
       <c r="G70" s="35" t="s">
         <v>212</v>
       </c>
+      <c r="H70" s="1" t="s">
+        <v>193</v>
+      </c>
       <c r="I70" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H70, G70)</f>
-        <v>hasImplementedInput</v>
+        <v>http://www.w3.org/ns/ssn/hasImplementedInput</v>
       </c>
       <c r="J70" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G70)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasImplementedInput</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="46" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="7"/>
       <c r="B71" s="11" t="s">
         <v>213</v>
@@ -3934,31 +4281,40 @@
         <v>214</v>
       </c>
       <c r="D71" s="35"/>
-      <c r="E71" s="1" t="s">
-        <v>211</v>
+      <c r="E71" s="24" t="s">
+        <v>65</v>
       </c>
       <c r="G71" s="35" t="s">
         <v>215</v>
       </c>
+      <c r="H71" s="1" t="s">
+        <v>193</v>
+      </c>
       <c r="I71" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H71, G71)</f>
-        <v>hasImplementedOutput</v>
+        <v>http://www.w3.org/ns/ssn/hasImplementedOutput</v>
       </c>
       <c r="J71" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G71)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasImplementedOutput</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="47.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="7"/>
       <c r="B72" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="E72" s="1" t="s">
+      <c r="C72" s="1" t="s">
         <v>217</v>
+      </c>
+      <c r="E72" s="24" t="s">
+        <v>216</v>
       </c>
       <c r="G72" s="1" t="s">
         <v>218</v>
+      </c>
+      <c r="H72" s="36" t="s">
+        <v>219</v>
       </c>
       <c r="J72" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G72)</f>
@@ -3968,25 +4324,37 @@
     <row r="73" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="7"/>
       <c r="B73" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="C73" s="35" t="s">
+        <v>221</v>
+      </c>
+      <c r="D73" s="35"/>
+      <c r="E73" s="24" t="s">
+        <v>222</v>
+      </c>
+      <c r="G73" s="35"/>
+      <c r="H73" s="36" t="s">
         <v>219</v>
       </c>
-      <c r="C73" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="D73" s="35"/>
-      <c r="E73" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="G73" s="35"/>
       <c r="J73" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G73)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="7"/>
       <c r="B74" s="11" t="s">
-        <v>222</v>
+        <v>223</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="H74" s="36" t="s">
+        <v>219</v>
       </c>
       <c r="J74" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G74)</f>
@@ -3996,17 +4364,35 @@
     <row r="75" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="7"/>
       <c r="B75" s="11" t="s">
-        <v>223</v>
+        <v>225</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="H75" s="36" t="s">
+        <v>219</v>
       </c>
       <c r="J75" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G75)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="7"/>
       <c r="B76" s="11" t="s">
-        <v>224</v>
+        <v>228</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="H76" s="36" t="s">
+        <v>219</v>
       </c>
       <c r="J76" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G76)</f>
@@ -4016,7 +4402,16 @@
     <row r="77" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="7"/>
       <c r="B77" s="11" t="s">
-        <v>225</v>
+        <v>230</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="H77" s="36" t="s">
+        <v>219</v>
       </c>
       <c r="J77" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G77)</f>
@@ -4026,57 +4421,111 @@
     <row r="78" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="7"/>
       <c r="B78" s="11" t="s">
-        <v>226</v>
+        <v>232</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="H78" s="36" t="s">
+        <v>219</v>
       </c>
       <c r="J78" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G78)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="7"/>
       <c r="B79" s="11" t="s">
-        <v>227</v>
+        <v>234</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="H79" s="36" t="s">
+        <v>219</v>
       </c>
       <c r="J79" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G79)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="7"/>
       <c r="B80" s="11" t="s">
-        <v>228</v>
+        <v>236</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="H80" s="36" t="s">
+        <v>219</v>
       </c>
       <c r="J80" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G80)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="7"/>
       <c r="B81" s="11" t="s">
-        <v>229</v>
+        <v>238</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="H81" s="36" t="s">
+        <v>219</v>
       </c>
       <c r="J81" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G81)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="7"/>
       <c r="B82" s="11" t="s">
-        <v>230</v>
+        <v>241</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="H82" s="36" t="s">
+        <v>219</v>
       </c>
       <c r="J82" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G82)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="7"/>
       <c r="B83" s="11" t="s">
-        <v>231</v>
+        <v>243</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="H83" s="36" t="s">
+        <v>219</v>
       </c>
       <c r="J83" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G83)</f>
@@ -4085,17 +4534,17 @@
     </row>
     <row r="84" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="32" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B84" s="21"/>
       <c r="C84" s="22" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="D84" s="22"/>
       <c r="E84" s="21"/>
       <c r="F84" s="21"/>
       <c r="G84" s="21" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H84" s="22" t="s">
         <v>193</v>
@@ -4113,7 +4562,7 @@
     <row r="85" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="23"/>
       <c r="B85" s="11" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="C85" s="10" t="s">
         <v>141</v>
@@ -4142,7 +4591,7 @@
     <row r="86" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="23"/>
       <c r="B86" s="11" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>27</v>
@@ -4162,7 +4611,7 @@
     <row r="87" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="23"/>
       <c r="B87" s="11" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="G87" s="1" t="s">
         <v>33</v>
@@ -4182,10 +4631,10 @@
     <row r="88" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="23"/>
       <c r="B88" s="11" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="J88" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G88)</f>
@@ -4195,10 +4644,10 @@
     <row r="89" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="23"/>
       <c r="B89" s="11" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="J89" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G89)</f>
@@ -4208,7 +4657,7 @@
     <row r="90" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="23"/>
       <c r="B90" s="11" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>52</v>
@@ -4228,7 +4677,7 @@
     <row r="91" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="23"/>
       <c r="B91" s="11" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="G91" s="1" t="s">
         <v>67</v>
@@ -4240,20 +4689,20 @@
     </row>
     <row r="92" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="25" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B92" s="4"/>
       <c r="C92" s="5" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="D92" s="5"/>
       <c r="E92" s="4"/>
       <c r="F92" s="4"/>
       <c r="G92" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="H92" s="5" t="s">
         <v>205</v>
-      </c>
-      <c r="H92" s="5" t="s">
-        <v>204</v>
       </c>
       <c r="I92" s="5" t="str">
         <f aca="false">_xlfn.CONCAT(H92, G92)</f>
@@ -4268,7 +4717,7 @@
     <row r="93" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="7"/>
       <c r="B93" s="11" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="C93" s="10" t="s">
         <v>141</v>
@@ -4291,7 +4740,7 @@
     <row r="94" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="7"/>
       <c r="B94" s="11" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="G94" s="1" t="s">
         <v>27</v>
@@ -4311,7 +4760,7 @@
     <row r="95" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="7"/>
       <c r="B95" s="11" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="G95" s="1" t="s">
         <v>33</v>
@@ -4331,10 +4780,10 @@
     <row r="96" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="7"/>
       <c r="B96" s="11" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="J96" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G96)</f>
@@ -4344,10 +4793,10 @@
     <row r="97" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="7"/>
       <c r="B97" s="11" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="J97" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G97)</f>
@@ -4357,7 +4806,7 @@
     <row r="98" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="7"/>
       <c r="B98" s="11" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="G98" s="1" t="s">
         <v>52</v>
@@ -4377,13 +4826,13 @@
     <row r="99" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="7"/>
       <c r="B99" s="11" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I99" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H99, G99)</f>
@@ -4397,7 +4846,7 @@
     <row r="100" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="7"/>
       <c r="B100" s="11" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="G100" s="1" t="s">
         <v>67</v>
@@ -4409,20 +4858,20 @@
     </row>
     <row r="101" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="32" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="B101" s="21"/>
       <c r="C101" s="22" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="D101" s="22"/>
       <c r="E101" s="21"/>
       <c r="F101" s="21"/>
       <c r="G101" s="21" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="H101" s="22" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I101" s="22" t="str">
         <f aca="false">_xlfn.CONCAT(H101, G101)</f>
@@ -4464,10 +4913,10 @@
     <row r="103" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="23"/>
       <c r="B103" s="11" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="H103" s="10" t="s">
         <v>15</v>
@@ -4480,16 +4929,16 @@
     <row r="104" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="23"/>
       <c r="B104" s="11" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="H104" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J104" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G104)</f>
@@ -4499,13 +4948,13 @@
     <row r="105" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="23"/>
       <c r="B105" s="11" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J105" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G105)</f>
@@ -4515,10 +4964,10 @@
     <row r="106" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="23"/>
       <c r="B106" s="11" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="G106" s="1" t="s">
         <v>67</v>
@@ -4531,32 +4980,32 @@
     <row r="107" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="23"/>
       <c r="B107" s="11" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J107" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G107)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#observedProperty</v>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#ObservedProperty</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="25" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="B108" s="4"/>
       <c r="C108" s="5" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="D108" s="5"/>
       <c r="E108" s="4"/>
       <c r="F108" s="4"/>
       <c r="G108" s="4" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="H108" s="5" t="s">
         <v>15</v>
@@ -4600,10 +5049,10 @@
     <row r="110" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="7"/>
       <c r="B110" s="11" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>66</v>
@@ -4623,22 +5072,22 @@
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#partOf</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="7"/>
       <c r="B111" s="11" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>66</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="H111" s="10" t="s">
         <v>15</v>
@@ -4655,10 +5104,10 @@
     <row r="112" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="7"/>
       <c r="B112" s="11" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C112" s="10" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="G112" s="1" t="s">
         <v>33</v>
@@ -4678,10 +5127,10 @@
     <row r="113" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="7"/>
       <c r="B113" s="11" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="C113" s="10" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="G113" s="1" t="s">
         <v>137</v>
@@ -4701,16 +5150,16 @@
     <row r="114" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="7"/>
       <c r="B114" s="26" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="C114" s="27" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="D114" s="27"/>
       <c r="E114" s="27"/>
       <c r="F114" s="27"/>
       <c r="G114" s="27" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="H114" s="27" t="s">
         <v>15</v>
@@ -4725,22 +5174,22 @@
       </c>
       <c r="K114" s="27"/>
       <c r="L114" s="1" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="7"/>
       <c r="B115" s="26" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="C115" s="27" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="D115" s="27"/>
       <c r="E115" s="27"/>
       <c r="F115" s="27"/>
       <c r="G115" s="27" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="H115" s="27" t="s">
         <v>15</v>
@@ -4758,13 +5207,13 @@
     <row r="116" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="7"/>
       <c r="B116" s="11" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>282</v>
+        <v>295</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="G116" s="1" t="s">
         <v>186</v>
@@ -4784,10 +5233,10 @@
     <row r="117" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="7"/>
       <c r="B117" s="11" t="s">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="H117" s="10" t="s">
         <v>15</v>
@@ -4803,17 +5252,17 @@
     </row>
     <row r="118" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="32" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="B118" s="21"/>
       <c r="C118" s="22" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="D118" s="22"/>
       <c r="E118" s="21"/>
       <c r="F118" s="21"/>
       <c r="G118" s="21" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="H118" s="22" t="s">
         <v>15</v>
@@ -4827,13 +5276,13 @@
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#ObservedVariable</v>
       </c>
       <c r="K118" s="21" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="23"/>
       <c r="B119" s="11" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="C119" s="10" t="s">
         <v>141</v>
@@ -4849,16 +5298,16 @@
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasIdentifier</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="35.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="23"/>
       <c r="B120" s="11" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="D120" s="10" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="H120" s="10" t="s">
         <v>15</v>
@@ -4868,93 +5317,93 @@
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="35.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="23"/>
       <c r="B121" s="11" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="D121" s="10" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="J121" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G121)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="35.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="23"/>
       <c r="B122" s="11" t="s">
-        <v>297</v>
-      </c>
-      <c r="C122" s="36" t="s">
-        <v>298</v>
+        <v>310</v>
+      </c>
+      <c r="C122" s="10" t="s">
+        <v>311</v>
       </c>
       <c r="D122" s="10" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="J122" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G122)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="24.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="23"/>
       <c r="B123" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="C123" s="36" t="s">
-        <v>301</v>
+        <v>313</v>
+      </c>
+      <c r="C123" s="10" t="s">
+        <v>314</v>
       </c>
       <c r="D123" s="10" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="124" customFormat="false" ht="24.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="23"/>
       <c r="B124" s="11" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="D124" s="10" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="125" customFormat="false" ht="24.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="23"/>
       <c r="B125" s="11" t="s">
-        <v>306</v>
-      </c>
-      <c r="C125" s="37" t="s">
-        <v>307</v>
+        <v>319</v>
+      </c>
+      <c r="C125" s="10" t="s">
+        <v>320</v>
       </c>
       <c r="D125" s="10" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="23"/>
       <c r="B126" s="11" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="D126" s="10" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="127" customFormat="false" ht="35.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="23"/>
       <c r="B127" s="11" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="C127" s="10" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="D127" s="10" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="J127" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G127)</f>
@@ -4964,100 +5413,100 @@
     <row r="128" customFormat="false" ht="12.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="23"/>
       <c r="B128" s="11" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="C128" s="10" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="D128" s="10" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="129" customFormat="false" ht="24.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="23"/>
       <c r="B129" s="11" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="C129" s="10" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="D129" s="10" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="130" customFormat="false" ht="105.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="23"/>
       <c r="B130" s="11" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
       <c r="C130" s="10" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="D130" s="10" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="131" customFormat="false" ht="24.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="23"/>
       <c r="B131" s="11" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="C131" s="10" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="D131" s="10" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="12.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="23"/>
       <c r="B132" s="11" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="C132" s="10" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="D132" s="10" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="133" customFormat="false" ht="24.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="23"/>
       <c r="B133" s="11" t="s">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="C133" s="10" t="s">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="D133" s="10" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="134" customFormat="false" ht="24.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="23"/>
       <c r="B134" s="11" t="s">
-        <v>332</v>
+        <v>345</v>
       </c>
       <c r="C134" s="10" t="s">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="D134" s="10" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="25" t="s">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="B135" s="4"/>
       <c r="C135" s="5" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="D135" s="5"/>
       <c r="E135" s="4"/>
       <c r="F135" s="4"/>
       <c r="G135" s="4" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="H135" s="5" t="s">
         <v>15</v>
@@ -5094,10 +5543,10 @@
     <row r="137" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="7"/>
       <c r="B137" s="11" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="J137" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G137)</f>
@@ -5107,7 +5556,7 @@
     <row r="138" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="7"/>
       <c r="B138" s="11" t="s">
-        <v>337</v>
+        <v>350</v>
       </c>
       <c r="J138" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G138)</f>
@@ -5117,37 +5566,37 @@
     <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="7"/>
       <c r="B139" s="11" t="s">
-        <v>338</v>
+        <v>351</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="7"/>
       <c r="B140" s="11" t="s">
-        <v>339</v>
+        <v>352</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="7"/>
       <c r="B141" s="11" t="s">
-        <v>340</v>
+        <v>353</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>341</v>
+        <v>354</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="32" t="s">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="B142" s="21"/>
       <c r="C142" s="22" t="s">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="D142" s="22"/>
       <c r="E142" s="21"/>
       <c r="F142" s="21"/>
       <c r="G142" s="21" t="s">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="H142" s="22" t="s">
         <v>15</v>
@@ -5159,13 +5608,19 @@
       </c>
       <c r="K142" s="21"/>
     </row>
-    <row r="143" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="35.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="23"/>
       <c r="B143" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C143" s="10" t="s">
-        <v>141</v>
+        <v>357</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="G143" s="1" t="s">
         <v>21</v>
@@ -5178,646 +5633,1034 @@
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasIdentifier</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="47.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="23"/>
-      <c r="B144" s="11"/>
-      <c r="C144" s="10"/>
-    </row>
-    <row r="145" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B144" s="11" t="s">
+        <v>361</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="H144" s="10"/>
+    </row>
+    <row r="145" customFormat="false" ht="35.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="23"/>
-      <c r="B145" s="11"/>
-      <c r="J145" s="1" t="str">
-        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G145)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
-      </c>
-    </row>
-    <row r="146" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="25" t="s">
-        <v>344</v>
-      </c>
-      <c r="B146" s="4"/>
-      <c r="C146" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="D146" s="5"/>
-      <c r="E146" s="4"/>
-      <c r="F146" s="4"/>
-      <c r="G146" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="H146" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I146" s="5"/>
-      <c r="J146" s="4" t="str">
-        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G146)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#BiologicalMaterial</v>
-      </c>
-      <c r="K146" s="4"/>
-    </row>
-    <row r="147" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="7"/>
+      <c r="B145" s="11" t="s">
+        <v>365</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="H145" s="10"/>
+    </row>
+    <row r="146" customFormat="false" ht="35.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="23"/>
+      <c r="B146" s="11" t="s">
+        <v>369</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="H146" s="10"/>
+    </row>
+    <row r="147" customFormat="false" ht="12.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="23"/>
       <c r="B147" s="11" t="s">
-        <v>347</v>
-      </c>
-      <c r="C147" s="10" t="s">
-        <v>348</v>
-      </c>
-      <c r="G147" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H147" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J147" s="1" t="str">
-        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G147)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasIdentifier</v>
-      </c>
-    </row>
-    <row r="148" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="7"/>
+        <v>373</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="47.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="23"/>
       <c r="B148" s="11" t="s">
-        <v>349</v>
+        <v>377</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>350</v>
+        <v>378</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="J148" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G148)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="7"/>
-      <c r="B149" s="11" t="s">
-        <v>351</v>
-      </c>
-      <c r="C149" s="1" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="25" t="s">
+        <v>380</v>
+      </c>
+      <c r="B149" s="4"/>
+      <c r="C149" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="D149" s="5"/>
+      <c r="E149" s="4"/>
+      <c r="F149" s="4"/>
+      <c r="G149" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="H149" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I149" s="5"/>
+      <c r="J149" s="4" t="str">
+        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G149)</f>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#BiologicalMaterial</v>
+      </c>
+      <c r="K149" s="4"/>
+    </row>
+    <row r="150" customFormat="false" ht="47.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="7"/>
-      <c r="B150" s="11" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B150" s="10" t="s">
+        <v>383</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="G150" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H150" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J150" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G150)</f>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasIdentifier</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="47.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="7"/>
-      <c r="B151" s="11" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B151" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="J151" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G151)</f>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="24.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="7"/>
-      <c r="B152" s="11" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B152" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="24.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="7"/>
-      <c r="B153" s="11"/>
-    </row>
-    <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B153" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="24.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="7"/>
-      <c r="B154" s="11"/>
-    </row>
-    <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B154" s="10" t="s">
+        <v>397</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="93.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="7"/>
-      <c r="B155" s="11"/>
-    </row>
-    <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B155" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="24.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="7"/>
-      <c r="B156" s="11"/>
-    </row>
-    <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B156" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="D156" s="1" t="n">
+        <v>39.067</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="24.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="7"/>
-      <c r="B157" s="11"/>
-    </row>
-    <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B157" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="D157" s="1" t="n">
+        <v>-8.73</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="24.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="7"/>
-      <c r="B158" s="11"/>
-    </row>
-    <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B158" s="10" t="s">
+        <v>409</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="24.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="7"/>
-      <c r="B159" s="11"/>
-    </row>
-    <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B159" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="47.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="7"/>
-      <c r="B160" s="11"/>
-    </row>
-    <row r="161" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="32" t="s">
-        <v>356</v>
-      </c>
-      <c r="B161" s="21"/>
-      <c r="C161" s="22" t="s">
-        <v>357</v>
-      </c>
-      <c r="D161" s="22"/>
-      <c r="E161" s="21"/>
-      <c r="F161" s="21"/>
-      <c r="G161" s="21" t="s">
-        <v>356</v>
-      </c>
-      <c r="H161" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="I161" s="22"/>
-      <c r="J161" s="21" t="str">
-        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G161)</f>
+      <c r="B160" s="10" t="s">
+        <v>417</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="127.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="7"/>
+      <c r="B161" s="10" t="s">
+        <v>421</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="12.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="7"/>
+      <c r="B162" s="10" t="s">
+        <v>424</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="E162" s="1" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="35.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="7"/>
+      <c r="B163" s="10" t="s">
+        <v>428</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="35.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="7"/>
+      <c r="B164" s="10" t="s">
+        <v>431</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="E164" s="1" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="47.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="7"/>
+      <c r="B165" s="10" t="s">
+        <v>435</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="12.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="7"/>
+      <c r="B166" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="E166" s="1" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="24.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="7"/>
+      <c r="B167" s="10" t="s">
+        <v>442</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="E167" s="1" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="24.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="7"/>
+      <c r="B168" s="10" t="s">
+        <v>446</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="D168" s="1" t="n">
+        <v>39.067</v>
+      </c>
+      <c r="E168" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="24.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="7"/>
+      <c r="B169" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="D169" s="1" t="n">
+        <v>-8.73</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="24.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="7"/>
+      <c r="B170" s="10" t="s">
+        <v>450</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="E170" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="24.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="7"/>
+      <c r="B171" s="10" t="s">
+        <v>452</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="E171" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="35.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="7"/>
+      <c r="B172" s="10" t="s">
+        <v>454</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="32" t="s">
+        <v>457</v>
+      </c>
+      <c r="B173" s="21"/>
+      <c r="C173" s="22" t="s">
+        <v>458</v>
+      </c>
+      <c r="D173" s="22"/>
+      <c r="E173" s="21"/>
+      <c r="F173" s="21"/>
+      <c r="G173" s="21" t="s">
+        <v>457</v>
+      </c>
+      <c r="H173" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="I173" s="22"/>
+      <c r="J173" s="21" t="str">
+        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G173)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#Event</v>
       </c>
-      <c r="K161" s="21"/>
-    </row>
-    <row r="162" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="23"/>
-      <c r="B162" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C162" s="10" t="s">
+      <c r="K173" s="21"/>
+    </row>
+    <row r="174" customFormat="false" ht="35.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="23"/>
+      <c r="B174" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="C174" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="G162" s="1" t="s">
+      <c r="G174" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H162" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J162" s="1" t="str">
-        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G162)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasIdentifier</v>
-      </c>
-    </row>
-    <row r="163" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="23"/>
-      <c r="B163" s="11"/>
-      <c r="J163" s="1" t="str">
-        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G163)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
-      </c>
-    </row>
-    <row r="164" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="23"/>
-      <c r="B164" s="11"/>
-      <c r="J164" s="1" t="str">
-        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G164)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
-      </c>
-    </row>
-    <row r="165" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="23"/>
-      <c r="B165" s="11"/>
-      <c r="J165" s="1" t="str">
-        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G165)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
-      </c>
-    </row>
-    <row r="166" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="25" t="s">
-        <v>358</v>
-      </c>
-      <c r="B166" s="4"/>
-      <c r="C166" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="D166" s="5"/>
-      <c r="E166" s="4"/>
-      <c r="F166" s="4"/>
-      <c r="G166" s="4"/>
-      <c r="H166" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I166" s="5"/>
-      <c r="J166" s="4" t="str">
-        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G166)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
-      </c>
-      <c r="K166" s="4"/>
-    </row>
-    <row r="167" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="7"/>
-      <c r="B167" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C167" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="G167" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H167" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J167" s="1" t="str">
-        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G167)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasIdentifier</v>
-      </c>
-    </row>
-    <row r="168" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="7"/>
-      <c r="B168" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C168" s="10" t="s">
-        <v>360</v>
-      </c>
-      <c r="E168" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="G168" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="H168" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="K168" s="1" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="169" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="7"/>
-      <c r="B169" s="11" t="s">
-        <v>363</v>
-      </c>
-      <c r="C169" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="E169" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G169" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="H169" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J169" s="1" t="str">
-        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G169)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasEnvironmentParameter</v>
-      </c>
-    </row>
-    <row r="170" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="7"/>
-      <c r="B170" s="11" t="s">
-        <v>366</v>
-      </c>
-      <c r="C170" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="E170" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G170" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H170" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="171" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="7"/>
-      <c r="B171" s="11" t="s">
-        <v>340</v>
-      </c>
-      <c r="C171" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="E171" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="F171" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="G171" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="H171" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="172" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="32" t="s">
-        <v>369</v>
-      </c>
-      <c r="B172" s="21"/>
-      <c r="C172" s="22" t="s">
-        <v>370</v>
-      </c>
-      <c r="D172" s="22"/>
-      <c r="E172" s="21"/>
-      <c r="F172" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="G172" s="21" t="s">
-        <v>369</v>
-      </c>
-      <c r="H172" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="I172" s="22"/>
-      <c r="J172" s="21" t="str">
-        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G172)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#Person</v>
-      </c>
-      <c r="K172" s="21"/>
-    </row>
-    <row r="173" s="30" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="23"/>
-      <c r="B173" s="11" t="s">
-        <v>371</v>
-      </c>
-      <c r="C173" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="E173" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="F173" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="G173" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="H173" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="J173" s="1" t="str">
-        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G173)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasIdentifier</v>
-      </c>
-    </row>
-    <row r="174" s="30" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="23"/>
-      <c r="B174" s="11" t="s">
-        <v>372</v>
-      </c>
-      <c r="C174" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="E174" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="F174" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="G174" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="H174" s="38" t="s">
+      <c r="H174" s="10" t="s">
         <v>15</v>
       </c>
       <c r="J174" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G174)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasName</v>
-      </c>
-    </row>
-    <row r="175" s="30" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasIdentifier</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="12.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="23"/>
-      <c r="B175" s="11" t="s">
-        <v>374</v>
+      <c r="B175" s="10" t="s">
+        <v>460</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="E175" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="F175" s="30" t="s">
-        <v>66</v>
-      </c>
-      <c r="G175" s="30" t="s">
-        <v>376</v>
-      </c>
-      <c r="H175" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="J175" s="1" t="str">
-        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G175)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasORCID</v>
-      </c>
-    </row>
-    <row r="176" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>461</v>
+      </c>
+      <c r="D175" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="H175" s="10"/>
+    </row>
+    <row r="176" customFormat="false" ht="35.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="23"/>
-      <c r="B176" s="11" t="s">
-        <v>377</v>
+      <c r="B176" s="10" t="s">
+        <v>463</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="D176" s="30"/>
-      <c r="E176" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F176" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="G176" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="H176" s="10" t="s">
-        <v>15</v>
+        <v>464</v>
+      </c>
+      <c r="D176" s="1" t="s">
+        <v>465</v>
       </c>
       <c r="J176" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G176)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasEmailContact</v>
-      </c>
-    </row>
-    <row r="177" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="35.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="23"/>
-      <c r="B177" s="11" t="s">
-        <v>380</v>
+      <c r="B177" s="10" t="s">
+        <v>466</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="E177" s="24" t="s">
-        <v>380</v>
-      </c>
-      <c r="F177" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="G177" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="H177" s="10" t="s">
-        <v>15</v>
+        <v>467</v>
+      </c>
+      <c r="D177" s="1" t="s">
+        <v>468</v>
       </c>
       <c r="J177" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G177)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasRole</v>
-      </c>
-    </row>
-    <row r="178" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="35.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="23"/>
-      <c r="B178" s="11" t="s">
-        <v>383</v>
+      <c r="B178" s="10" t="s">
+        <v>469</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E178" s="24" t="s">
-        <v>91</v>
-      </c>
-      <c r="F178" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="G178" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="H178" s="10" t="s">
-        <v>15</v>
+        <v>470</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>471</v>
       </c>
       <c r="J178" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G178)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasAffiliation</v>
-      </c>
-    </row>
-    <row r="179" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="39" t="s">
-        <v>386</v>
-      </c>
-      <c r="B179" s="40"/>
-      <c r="C179" s="41" t="s">
-        <v>387</v>
-      </c>
-      <c r="D179" s="41"/>
-      <c r="E179" s="40"/>
-      <c r="F179" s="40"/>
-      <c r="G179" s="40"/>
-      <c r="H179" s="41"/>
-      <c r="I179" s="41"/>
-      <c r="J179" s="40" t="str">
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A179" s="25" t="s">
+        <v>472</v>
+      </c>
+      <c r="B179" s="4"/>
+      <c r="C179" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="D179" s="5"/>
+      <c r="E179" s="4"/>
+      <c r="F179" s="4"/>
+      <c r="G179" s="4"/>
+      <c r="H179" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I179" s="5"/>
+      <c r="J179" s="4" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G179)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
       </c>
-      <c r="K179" s="40" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="180" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="42"/>
-      <c r="B180" s="14" t="s">
+      <c r="K179" s="4"/>
+    </row>
+    <row r="180" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="7"/>
+      <c r="B180" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C180" s="13" t="s">
+      <c r="C180" s="10" t="s">
         <v>141</v>
+      </c>
+      <c r="G180" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H180" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J180" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G180)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
-      </c>
-    </row>
-    <row r="181" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="42"/>
-      <c r="B181" s="14" t="s">
-        <v>389</v>
-      </c>
-      <c r="J181" s="1" t="str">
-        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G181)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
-      </c>
-    </row>
-    <row r="182" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="42"/>
-      <c r="B182" s="14" t="s">
-        <v>390</v>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasIdentifier</v>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A181" s="7"/>
+      <c r="B181" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C181" s="10" t="s">
+        <v>474</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="G181" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="H181" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="K181" s="1" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A182" s="7"/>
+      <c r="B182" s="11" t="s">
+        <v>477</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G182" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="H182" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J182" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G182)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
-      </c>
-    </row>
-    <row r="183" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="42"/>
-      <c r="B183" s="14" t="s">
-        <v>209</v>
-      </c>
-      <c r="J183" s="1" t="str">
-        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G183)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
-      </c>
-    </row>
-    <row r="184" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="42"/>
-      <c r="B184" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="J184" s="1" t="str">
-        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G184)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
-      </c>
-    </row>
-    <row r="185" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="42"/>
-      <c r="B185" s="14" t="s">
-        <v>391</v>
-      </c>
-      <c r="J185" s="1" t="str">
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasEnvironmentParameter</v>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A183" s="7"/>
+      <c r="B183" s="11" t="s">
+        <v>480</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G183" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="H183" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A184" s="7"/>
+      <c r="B184" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G184" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H184" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A185" s="32" t="s">
+        <v>483</v>
+      </c>
+      <c r="B185" s="21"/>
+      <c r="C185" s="22" t="s">
+        <v>484</v>
+      </c>
+      <c r="D185" s="22"/>
+      <c r="E185" s="21"/>
+      <c r="F185" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="G185" s="21" t="s">
+        <v>483</v>
+      </c>
+      <c r="H185" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="I185" s="22"/>
+      <c r="J185" s="21" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G185)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
-      </c>
-    </row>
-    <row r="186" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="42"/>
-      <c r="B186" s="14" t="s">
-        <v>392</v>
-      </c>
-      <c r="E186" s="13" t="s">
-        <v>393</v>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#Person</v>
+      </c>
+      <c r="K185" s="21"/>
+    </row>
+    <row r="186" s="30" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="23"/>
+      <c r="B186" s="11" t="s">
+        <v>485</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E186" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="F186" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="G186" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="H186" s="37" t="s">
+        <v>15</v>
       </c>
       <c r="J186" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G186)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
-      </c>
-    </row>
-    <row r="187" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="39" t="s">
-        <v>394</v>
-      </c>
-      <c r="B187" s="40"/>
-      <c r="C187" s="41" t="s">
-        <v>395</v>
-      </c>
-      <c r="D187" s="41"/>
-      <c r="E187" s="40"/>
-      <c r="F187" s="40"/>
-      <c r="G187" s="40"/>
-      <c r="H187" s="41"/>
-      <c r="I187" s="41"/>
-      <c r="J187" s="40" t="str">
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasIdentifier</v>
+      </c>
+    </row>
+    <row r="187" s="30" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A187" s="23"/>
+      <c r="B187" s="11" t="s">
+        <v>486</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="E187" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="F187" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="G187" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="H187" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="J187" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G187)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
-      </c>
-      <c r="K187" s="40" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="188" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="42"/>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasName</v>
+      </c>
+    </row>
+    <row r="188" s="30" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="23"/>
       <c r="B188" s="11" t="s">
+        <v>488</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="E188" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="C188" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="G188" s="1" t="s">
-        <v>21</v>
+      <c r="F188" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="G188" s="30" t="s">
+        <v>490</v>
+      </c>
+      <c r="H188" s="37" t="s">
+        <v>15</v>
       </c>
       <c r="J188" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G188)</f>
-        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasIdentifier</v>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasORCID</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="42"/>
-      <c r="B189" s="11"/>
+      <c r="A189" s="23"/>
+      <c r="B189" s="11" t="s">
+        <v>491</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="D189" s="30"/>
+      <c r="E189" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F189" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G189" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="H189" s="10" t="s">
+        <v>15</v>
+      </c>
       <c r="J189" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G189)</f>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasEmailContact</v>
+      </c>
+    </row>
+    <row r="190" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A190" s="23"/>
+      <c r="B190" s="11" t="s">
+        <v>494</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="E190" s="24" t="s">
+        <v>494</v>
+      </c>
+      <c r="F190" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G190" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="H190" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J190" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G190)</f>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasRole</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A191" s="23"/>
+      <c r="B191" s="11" t="s">
+        <v>497</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="E191" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="F191" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G191" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="H191" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J191" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G191)</f>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasAffiliation</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="38" t="s">
+        <v>500</v>
+      </c>
+      <c r="B192" s="39"/>
+      <c r="C192" s="40" t="s">
+        <v>501</v>
+      </c>
+      <c r="D192" s="40"/>
+      <c r="E192" s="39"/>
+      <c r="F192" s="39"/>
+      <c r="G192" s="39"/>
+      <c r="H192" s="40"/>
+      <c r="I192" s="40"/>
+      <c r="J192" s="39" t="str">
+        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G192)</f>
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
       </c>
+      <c r="K192" s="39" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="193" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="41"/>
+      <c r="B193" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C193" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J193" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G193)</f>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
+      </c>
+    </row>
+    <row r="194" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="41"/>
+      <c r="B194" s="14" t="s">
+        <v>503</v>
+      </c>
+      <c r="J194" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G194)</f>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
+      </c>
+    </row>
+    <row r="195" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="41"/>
+      <c r="B195" s="14" t="s">
+        <v>504</v>
+      </c>
+      <c r="J195" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G195)</f>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
+      </c>
+    </row>
+    <row r="196" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="41"/>
+      <c r="B196" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="J196" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G196)</f>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
+      </c>
+    </row>
+    <row r="197" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="41"/>
+      <c r="B197" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="J197" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G197)</f>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
+      </c>
+    </row>
+    <row r="198" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="41"/>
+      <c r="B198" s="14" t="s">
+        <v>505</v>
+      </c>
+      <c r="J198" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G198)</f>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
+      </c>
+    </row>
+    <row r="199" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A199" s="41"/>
+      <c r="B199" s="14" t="s">
+        <v>506</v>
+      </c>
+      <c r="E199" s="13" t="s">
+        <v>507</v>
+      </c>
+      <c r="J199" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G199)</f>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A200" s="38" t="s">
+        <v>508</v>
+      </c>
+      <c r="B200" s="39"/>
+      <c r="C200" s="40" t="s">
+        <v>509</v>
+      </c>
+      <c r="D200" s="40"/>
+      <c r="E200" s="39"/>
+      <c r="F200" s="39"/>
+      <c r="G200" s="39"/>
+      <c r="H200" s="40"/>
+      <c r="I200" s="40"/>
+      <c r="J200" s="39" t="str">
+        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G200)</f>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
+      </c>
+      <c r="K200" s="39" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="201" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A201" s="41"/>
+      <c r="B201" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C201" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="G201" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J201" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G201)</f>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasIdentifier</v>
+      </c>
+    </row>
+    <row r="202" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A202" s="41"/>
+      <c r="B202" s="11"/>
+      <c r="J202" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G202)</f>
+        <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H72" r:id="rId1" display="http://www.w3.org/ns/ssn/systems/"/>
+    <hyperlink ref="H73" r:id="rId2" display="http://www.w3.org/ns/ssn/systems/"/>
+    <hyperlink ref="H74" r:id="rId3" display="http://www.w3.org/ns/ssn/systems/"/>
+    <hyperlink ref="H75" r:id="rId4" display="http://www.w3.org/ns/ssn/systems/"/>
+    <hyperlink ref="H76" r:id="rId5" display="http://www.w3.org/ns/ssn/systems/"/>
+    <hyperlink ref="H77" r:id="rId6" display="http://www.w3.org/ns/ssn/systems/"/>
+    <hyperlink ref="H78" r:id="rId7" display="http://www.w3.org/ns/ssn/systems/"/>
+    <hyperlink ref="H79" r:id="rId8" display="http://www.w3.org/ns/ssn/systems/"/>
+    <hyperlink ref="H80" r:id="rId9" display="http://www.w3.org/ns/ssn/systems/"/>
+    <hyperlink ref="H81" r:id="rId10" display="http://www.w3.org/ns/ssn/systems/"/>
+    <hyperlink ref="H82" r:id="rId11" display="http://www.w3.org/ns/ssn/systems/"/>
+    <hyperlink ref="H83" r:id="rId12" display="http://www.w3.org/ns/ssn/systems/"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -5833,9 +6676,39 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="35.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="44" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="44" t="s">
+        <v>279</v>
+      </c>
+      <c r="C1" s="44" t="s">
+        <v>265</v>
+      </c>
+      <c r="D1" s="44" t="s">
+        <v>283</v>
+      </c>
+      <c r="E1" s="44" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1" s="44" t="s">
+        <v>287</v>
+      </c>
+      <c r="G1" s="44" t="s">
+        <v>291</v>
+      </c>
+      <c r="H1" s="44" t="s">
+        <v>294</v>
+      </c>
+      <c r="I1" s="44" t="s">
+        <v>297</v>
+      </c>
+    </row>
+  </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -5851,9 +6724,78 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:V1"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="35.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="44" t="s">
+        <v>195</v>
+      </c>
+      <c r="B1" s="44" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1" s="44" t="s">
+        <v>197</v>
+      </c>
+      <c r="D1" s="44" t="s">
+        <v>198</v>
+      </c>
+      <c r="E1" s="44" t="s">
+        <v>201</v>
+      </c>
+      <c r="F1" s="44" t="s">
+        <v>203</v>
+      </c>
+      <c r="G1" s="44" t="s">
+        <v>206</v>
+      </c>
+      <c r="H1" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="I1" s="44" t="s">
+        <v>210</v>
+      </c>
+      <c r="J1" s="44" t="s">
+        <v>213</v>
+      </c>
+      <c r="K1" s="44" t="s">
+        <v>216</v>
+      </c>
+      <c r="L1" s="44" t="s">
+        <v>220</v>
+      </c>
+      <c r="M1" s="44" t="s">
+        <v>223</v>
+      </c>
+      <c r="N1" s="44" t="s">
+        <v>225</v>
+      </c>
+      <c r="O1" s="44" t="s">
+        <v>228</v>
+      </c>
+      <c r="P1" s="44" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q1" s="44" t="s">
+        <v>232</v>
+      </c>
+      <c r="R1" s="44" t="s">
+        <v>234</v>
+      </c>
+      <c r="S1" s="44" t="s">
+        <v>236</v>
+      </c>
+      <c r="T1" s="44" t="s">
+        <v>238</v>
+      </c>
+      <c r="U1" s="44" t="s">
+        <v>241</v>
+      </c>
+      <c r="V1" s="44" t="s">
+        <v>243</v>
+      </c>
+    </row>
+  </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -5869,9 +6811,33 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="24.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="44" t="s">
+        <v>246</v>
+      </c>
+      <c r="B1" s="44" t="s">
+        <v>247</v>
+      </c>
+      <c r="C1" s="44" t="s">
+        <v>248</v>
+      </c>
+      <c r="D1" s="44" t="s">
+        <v>249</v>
+      </c>
+      <c r="E1" s="44" t="s">
+        <v>251</v>
+      </c>
+      <c r="F1" s="44" t="s">
+        <v>253</v>
+      </c>
+      <c r="G1" s="44" t="s">
+        <v>254</v>
+      </c>
+    </row>
+  </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -5887,9 +6853,36 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="24.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="44" t="s">
+        <v>256</v>
+      </c>
+      <c r="B1" s="44" t="s">
+        <v>257</v>
+      </c>
+      <c r="C1" s="44" t="s">
+        <v>258</v>
+      </c>
+      <c r="D1" s="44" t="s">
+        <v>259</v>
+      </c>
+      <c r="E1" s="44" t="s">
+        <v>251</v>
+      </c>
+      <c r="F1" s="44" t="s">
+        <v>253</v>
+      </c>
+      <c r="G1" s="44" t="s">
+        <v>261</v>
+      </c>
+      <c r="H1" s="44" t="s">
+        <v>254</v>
+      </c>
+    </row>
+  </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -5905,9 +6898,60 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="58.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="44" t="s">
+        <v>303</v>
+      </c>
+      <c r="B1" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="C1" s="44" t="s">
+        <v>307</v>
+      </c>
+      <c r="D1" s="44" t="s">
+        <v>310</v>
+      </c>
+      <c r="E1" s="44" t="s">
+        <v>313</v>
+      </c>
+      <c r="F1" s="44" t="s">
+        <v>316</v>
+      </c>
+      <c r="G1" s="44" t="s">
+        <v>319</v>
+      </c>
+      <c r="H1" s="44" t="s">
+        <v>322</v>
+      </c>
+      <c r="I1" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="J1" s="44" t="s">
+        <v>327</v>
+      </c>
+      <c r="K1" s="44" t="s">
+        <v>330</v>
+      </c>
+      <c r="L1" s="44" t="s">
+        <v>333</v>
+      </c>
+      <c r="M1" s="44" t="s">
+        <v>336</v>
+      </c>
+      <c r="N1" s="44" t="s">
+        <v>339</v>
+      </c>
+      <c r="O1" s="44" t="s">
+        <v>342</v>
+      </c>
+      <c r="P1" s="44" t="s">
+        <v>345</v>
+      </c>
+    </row>
+  </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -5923,9 +6967,30 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="35.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="44" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="44" t="s">
+        <v>265</v>
+      </c>
+      <c r="C1" s="44" t="s">
+        <v>350</v>
+      </c>
+      <c r="D1" s="44" t="s">
+        <v>351</v>
+      </c>
+      <c r="E1" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="F1" s="44" t="s">
+        <v>353</v>
+      </c>
+    </row>
+  </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -5941,9 +7006,30 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="47.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="44" t="s">
+        <v>357</v>
+      </c>
+      <c r="B1" s="44" t="s">
+        <v>361</v>
+      </c>
+      <c r="C1" s="44" t="s">
+        <v>365</v>
+      </c>
+      <c r="D1" s="44" t="s">
+        <v>369</v>
+      </c>
+      <c r="E1" s="44" t="s">
+        <v>373</v>
+      </c>
+      <c r="F1" s="44" t="s">
+        <v>377</v>
+      </c>
+    </row>
+  </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -5959,9 +7045,81 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:W1"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="70.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="24" t="s">
+        <v>383</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>386</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>390</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>393</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>397</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>401</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>405</v>
+      </c>
+      <c r="H1" s="24" t="s">
+        <v>407</v>
+      </c>
+      <c r="I1" s="24" t="s">
+        <v>409</v>
+      </c>
+      <c r="J1" s="24" t="s">
+        <v>413</v>
+      </c>
+      <c r="K1" s="24" t="s">
+        <v>417</v>
+      </c>
+      <c r="L1" s="24" t="s">
+        <v>421</v>
+      </c>
+      <c r="M1" s="24" t="s">
+        <v>424</v>
+      </c>
+      <c r="N1" s="24" t="s">
+        <v>428</v>
+      </c>
+      <c r="O1" s="24" t="s">
+        <v>431</v>
+      </c>
+      <c r="P1" s="24" t="s">
+        <v>435</v>
+      </c>
+      <c r="Q1" s="24" t="s">
+        <v>438</v>
+      </c>
+      <c r="R1" s="24" t="s">
+        <v>442</v>
+      </c>
+      <c r="S1" s="24" t="s">
+        <v>446</v>
+      </c>
+      <c r="T1" s="24" t="s">
+        <v>448</v>
+      </c>
+      <c r="U1" s="24" t="s">
+        <v>450</v>
+      </c>
+      <c r="V1" s="24" t="s">
+        <v>452</v>
+      </c>
+      <c r="W1" s="24" t="s">
+        <v>454</v>
+      </c>
+    </row>
+  </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -5977,9 +7135,27 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="35.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="24" t="s">
+        <v>459</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>460</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>463</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>466</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>469</v>
+      </c>
+    </row>
+  </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -5995,9 +7171,27 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="35.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="44" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="44" t="s">
+        <v>477</v>
+      </c>
+      <c r="D1" s="44" t="s">
+        <v>480</v>
+      </c>
+      <c r="E1" s="44" t="s">
+        <v>353</v>
+      </c>
+    </row>
+  </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -6055,31 +7249,31 @@
       <c r="H1" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="I1" s="43" t="s">
+      <c r="I1" s="42" t="s">
         <v>57</v>
       </c>
       <c r="J1" s="24" t="s">
-        <v>396</v>
+        <v>510</v>
       </c>
     </row>
     <row r="2" s="35" customFormat="true" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="35" t="s">
-        <v>397</v>
+        <v>511</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>398</v>
+        <v>512</v>
       </c>
       <c r="C2" s="35" t="s">
-        <v>399</v>
-      </c>
-      <c r="D2" s="44" t="n">
+        <v>513</v>
+      </c>
+      <c r="D2" s="43" t="n">
         <v>45644</v>
       </c>
-      <c r="E2" s="44" t="n">
+      <c r="E2" s="43" t="n">
         <v>45644</v>
       </c>
       <c r="F2" s="35" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="G2" s="35" t="n">
         <v>3.2</v>
@@ -6118,32 +7312,32 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="30" width="21.79"/>
   </cols>
   <sheetData>
-    <row r="1" s="43" customFormat="true" ht="36.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="43" t="s">
+    <row r="1" s="42" customFormat="true" ht="36.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="43" t="s">
+      <c r="B1" s="42" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="43" t="s">
+      <c r="C1" s="42" t="s">
         <v>80</v>
       </c>
-      <c r="D1" s="43" t="s">
+      <c r="D1" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="E1" s="43" t="s">
+      <c r="E1" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="F1" s="43" t="s">
+      <c r="F1" s="42" t="s">
         <v>89</v>
       </c>
-      <c r="G1" s="43" t="s">
+      <c r="G1" s="42" t="s">
         <v>93</v>
       </c>
-      <c r="H1" s="43" t="s">
+      <c r="H1" s="42" t="s">
         <v>96</v>
       </c>
-      <c r="I1" s="43" t="s">
+      <c r="I1" s="42" t="s">
         <v>100</v>
       </c>
     </row>
@@ -6176,24 +7370,24 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="30" width="21.79"/>
   </cols>
   <sheetData>
-    <row r="1" s="43" customFormat="true" ht="36.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="43" t="s">
-        <v>371</v>
-      </c>
-      <c r="B1" s="43" t="s">
-        <v>372</v>
-      </c>
-      <c r="C1" s="43" t="s">
-        <v>374</v>
-      </c>
-      <c r="D1" s="43" t="s">
-        <v>377</v>
-      </c>
-      <c r="E1" s="43" t="s">
-        <v>380</v>
-      </c>
-      <c r="F1" s="43" t="s">
-        <v>383</v>
+    <row r="1" s="42" customFormat="true" ht="36.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="42" t="s">
+        <v>485</v>
+      </c>
+      <c r="B1" s="42" t="s">
+        <v>486</v>
+      </c>
+      <c r="C1" s="42" t="s">
+        <v>488</v>
+      </c>
+      <c r="D1" s="42" t="s">
+        <v>491</v>
+      </c>
+      <c r="E1" s="42" t="s">
+        <v>494</v>
+      </c>
+      <c r="F1" s="42" t="s">
+        <v>497</v>
       </c>
     </row>
   </sheetData>
@@ -6225,23 +7419,23 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="30" width="21.79"/>
   </cols>
   <sheetData>
-    <row r="1" s="43" customFormat="true" ht="36.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="45" t="s">
+    <row r="1" s="42" customFormat="true" ht="36.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="45" t="s">
+      <c r="B1" s="44" t="s">
         <v>176</v>
       </c>
-      <c r="C1" s="45" t="s">
+      <c r="C1" s="44" t="s">
         <v>180</v>
       </c>
-      <c r="D1" s="45" t="s">
+      <c r="D1" s="44" t="s">
         <v>182</v>
       </c>
-      <c r="E1" s="45" t="s">
+      <c r="E1" s="44" t="s">
         <v>184</v>
       </c>
-      <c r="F1" s="45" t="s">
+      <c r="F1" s="44" t="s">
         <v>187</v>
       </c>
     </row>
@@ -6274,7 +7468,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="30" width="21.79"/>
   </cols>
   <sheetData>
-    <row r="1" s="43" customFormat="true" ht="36.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" s="42" customFormat="true" ht="36.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="24" t="s">
         <v>20</v>
       </c>
@@ -6335,41 +7529,41 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="30" width="21.79"/>
   </cols>
   <sheetData>
-    <row r="1" s="43" customFormat="true" ht="36.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="45" t="s">
+    <row r="1" s="42" customFormat="true" ht="36.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="45" t="s">
+      <c r="B1" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="C1" s="45" t="s">
+      <c r="C1" s="44" t="s">
         <v>144</v>
       </c>
-      <c r="D1" s="45" t="s">
+      <c r="D1" s="44" t="s">
         <v>107</v>
       </c>
-      <c r="E1" s="45" t="s">
+      <c r="E1" s="44" t="s">
         <v>111</v>
       </c>
-      <c r="F1" s="45" t="s">
+      <c r="F1" s="44" t="s">
         <v>147</v>
       </c>
-      <c r="G1" s="45" t="s">
+      <c r="G1" s="44" t="s">
         <v>150</v>
       </c>
-      <c r="H1" s="45" t="s">
+      <c r="H1" s="44" t="s">
         <v>152</v>
       </c>
-      <c r="I1" s="45" t="s">
+      <c r="I1" s="44" t="s">
         <v>154</v>
       </c>
-      <c r="J1" s="45" t="s">
+      <c r="J1" s="44" t="s">
         <v>156</v>
       </c>
-      <c r="K1" s="45" t="s">
+      <c r="K1" s="44" t="s">
         <v>158</v>
       </c>
-      <c r="L1" s="45" t="s">
+      <c r="L1" s="44" t="s">
         <v>160</v>
       </c>
     </row>
@@ -6402,20 +7596,20 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="30" width="21.79"/>
   </cols>
   <sheetData>
-    <row r="1" s="43" customFormat="true" ht="36.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="45" t="s">
+    <row r="1" s="42" customFormat="true" ht="36.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="44" t="s">
         <v>163</v>
       </c>
-      <c r="B1" s="45" t="s">
+      <c r="B1" s="44" t="s">
         <v>164</v>
       </c>
-      <c r="C1" s="45" t="s">
+      <c r="C1" s="44" t="s">
         <v>166</v>
       </c>
-      <c r="D1" s="45" t="s">
+      <c r="D1" s="44" t="s">
         <v>168</v>
       </c>
-      <c r="E1" s="45" t="s">
+      <c r="E1" s="44" t="s">
         <v>171</v>
       </c>
     </row>
@@ -6435,9 +7629,30 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="24.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="44" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="44" t="s">
+        <v>265</v>
+      </c>
+      <c r="C1" s="44" t="s">
+        <v>267</v>
+      </c>
+      <c r="D1" s="44" t="s">
+        <v>270</v>
+      </c>
+      <c r="E1" s="44" t="s">
+        <v>272</v>
+      </c>
+      <c r="F1" s="44" t="s">
+        <v>274</v>
+      </c>
+    </row>
+  </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
